--- a/datos/casos_corrupcion_chile.xlsx
+++ b/datos/casos_corrupcion_chile.xlsx
@@ -1,17 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moyarzo/code/corrupcion_chile/datos/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18CA72B-E9E8-B74D-B537-CFFF61519C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="34340" yWindow="800" windowWidth="32160" windowHeight="22520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="579">
   <si>
     <t>Caso</t>
   </si>
@@ -114,10 +136,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.ciperchile.cl/2023/05/26/escandalo-de-cuentas-corrientes-municipales-de-nuble-golpea-en-la-region-metropolitana-contraloria-obliga-a-san-bernardo-a-terminar-contrato/</t>
     </r>
@@ -143,10 +166,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-valparaiso/2022/09/23/auditoria-revela-caos-municipal-en-administracion-reginato-100-mil-millones-en-perdidas.shtml</t>
     </r>
@@ -154,10 +178,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.publimetro.cl/noticias/2022/09/23/100-mil-millones-las-perdidas-de-virginia-reginato-en-municipalidad-de-vina-del-mar/</t>
     </r>
@@ -165,10 +190,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.fastcheck.cl/2023/05/16/misterio-sin-resolver-ocho-escandalos-de-corrupcion-municipal-pendientes-de-justicia/</t>
     </r>
@@ -191,10 +217,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://radio.uchile.cl/2024/01/17/en-suspenso-prision-preventiva-para-cathy-barriga-tribunal-dictara-cautelar-este-jueves/</t>
     </r>
@@ -202,10 +229,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://lavozdemaipu.cl/cathy-barriga-ultimo-informe-con-peras-y-manzanas/</t>
     </r>
@@ -213,10 +241,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.tvn.cl/programas/buenos-dias-a-todos/actualidad/caso-cathy-barriga-los-41-mil-millones-de-pesos-que-no-se-saben-donde</t>
     </r>
@@ -239,10 +268,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://es.wikipedia.org/wiki/Pacogate#Investigación_y_sentencias</t>
     </r>
@@ -280,10 +310,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://interferencia.cl/articulos/tres-graves-casos-de-corrupcion-en-que-latam-se-ha-visto-envuelta-en-su-historia-reciente</t>
     </r>
@@ -303,10 +334,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://es.wikipedia.org/wiki/Pinocheques</t>
     </r>
@@ -326,10 +358,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://es.wikipedia.org/wiki/Milicogate</t>
     </r>
@@ -337,10 +370,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/la-tercera-domingo/noticia/el-metodo-rutherford-como-fueron-cayendo-uno-a-uno-los-comandantes-en-jefe-por-el-fraude-en-el-ejercito/IVKUSHEYJBDYHMSYZ4R3KZXQE4/</t>
     </r>
@@ -354,10 +388,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.chiletransparente.cl/caso-sqm/</t>
     </r>
@@ -377,10 +412,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.ciperchile.cl/2018/04/02/los-negocios-ilicitos-de-juan-castro-el-ex-alcalde-de-talca-que-llego-al-senado/</t>
     </r>
@@ -409,10 +445,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.meganoticias.cl/nacional/402950-malversacion-10-mil-millones-educacion-sergio-echeverria-exalcalde-san-joaquin-19-01-2023.html</t>
     </r>
@@ -429,10 +466,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elciudadano.com/politica/los-18-emblematicos-alcaldes-corruptos-de-la-derecha-historias-de-un-tsunami-delictual/06/22/</t>
     </r>
@@ -446,10 +484,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.aduana.cl/megafraude-tributario-investigacion-de-aduanas-fue-clave-para/aduana/2023-12-21/174405.html</t>
     </r>
@@ -469,10 +508,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/la-tercera-pm/noticia/estafa-fraude-y-falsificacion-el-avance-en-la-investigacion-penal-en-las-condes-que-remece-a-la-administracion-penaloza/X7ZBPJAYLRA47LINUR5COTA5HY/</t>
     </r>
@@ -480,10 +520,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/nacional/noticia/las-investigaciones-que-envuelven-al-municipio-de-las-condes-y-a-su-alcaldesa-daniela-penaloza/GYYWEXRFXNGJVKFJPOEWRQUB7I/</t>
     </r>
@@ -503,10 +544,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-metropolitana/2022/01/31/presentan-querella-contra-exalcaldesa-de-lampa-por-millonaria-deuda-de-cotizaciones.shtml</t>
     </r>
@@ -529,10 +571,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.diarioconstitucional.cl/2021/04/17/detalles-del-caso-corpesca-tercer-tribunal-de-juicio-oral-en-lo-penal-de-santiago-condeno-al-exsenador-jaime-orpis-a-la-pena-unica-de-5-anos-y-un-dia-de-presidio-efectivo-en-calidad-de-autor-de-seis/</t>
     </r>
@@ -540,10 +583,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://contracarga.cl/reportajes/caso-corpesca-explicado/</t>
     </r>
@@ -551,10 +595,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.ciperchile.cl/2016/08/17/el-articulo-de-la-ley-de-pesca-que-le-ahorro-4-670-millones-a-corpesca/</t>
     </r>
@@ -574,10 +619,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/la-tercera-sabado/noticia/cientos-de-depositos-en-efectivo-y-una-cuenta-con-2300-millones-las-pruebas-que-complican-al-tronco-torrealba/LH674LXDYVBR3J5IDIFUCMRIXE/</t>
     </r>
@@ -585,10 +631,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.ciperchile.cl/2023/05/20/caso-torrealba-detalles-de-gastos-de-campana-de-rn-que-fueron-financiados-con-dineros-de-vitacura/</t>
     </r>
@@ -596,10 +643,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elmostrador.cl/noticias/pais/2023/08/08/53-dias-tras-las-rejas-rechazan-solicitud-de-raul-torrealba-y-seguira-en-prision-preventiva/</t>
     </r>
@@ -607,10 +655,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/nacional/noticia/vitacura-contraloria-objeta-mas-de-4500-millones-a-administracion-de-alcalde-torrealba-en-dos-anos/GK3X6GQBOVB5BFGOV4N52T3PXI/</t>
     </r>
@@ -630,10 +679,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://interferencia.cl/articulos/contraloria-realiza-sumario-en-estacion-central-por-deficit-de-4300-millones-detectado</t>
     </r>
@@ -656,10 +706,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elrancaguino.cl/2024/01/18/hasta-35-anos-de-carcel-y-el-pago-de-2-mil-millones-de-pesos-en-multas-arriesga-el-ex-alcalde-san-fernando-luis-berwart/</t>
     </r>
@@ -685,10 +736,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.diarioantofagasta.cl/investigacion/198120/caso-canastas-las-claves-del-que-podria-ser-uno-de-los-mayores-casos-de-corrupcion-en-la-historia-reciente-de-antofagasta/</t>
     </r>
@@ -696,10 +748,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://estapasando.cl/caso-canasta-el-caso-de-corrupcion-que-sacude-antofagasta/</t>
     </r>
@@ -713,10 +766,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/2015/01/24/cinco-casos-de-corrupcion-que-mancharon-la-politica-antes-de-penta-en-los-ultimos-15-anos.shtml</t>
     </r>
@@ -724,10 +778,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.df.cl/aniversario/caso-inverlink-el-escandalo-que-amenazo-la-estabilidad-del-mercado</t>
     </r>
@@ -744,10 +799,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/</t>
     </r>
@@ -755,10 +811,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.emol.com/noticias/Nacional/2023/07/06/1100220/fundacion-el-desarrollo-de-organizaciones.html</t>
     </r>
@@ -778,10 +835,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elmostrador.cl/destacado/2023/02/06/los-2-500-millones-de-la-corporacion-municipal-de-la-florida-que-carter-no-termina-de-explicar/</t>
     </r>
@@ -789,10 +847,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/especial/bbcl-investiga/noticias/articulos/2023/01/27/detectan-diferencias-por-mas-de-4-600-millones-en-cuentas-bancarias-de-educacion-de-la-florida.shtml</t>
     </r>
@@ -800,10 +859,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.adnradio.cl/2024/09/14/denuncian-a-alcalde-carter-por-asociacion-ilicita-apropiacion-indebida-y-fraude-habria-entregado-millonaria-suma-sin-licitacion/</t>
     </r>
@@ -829,10 +889,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/earlyaccess/noticia/las-millonarias-transacciones-que-complican-al-alcalde-de-rancagua/GY4SPWLFPJDODKTTXDN7FR74B4/</t>
     </r>
@@ -840,10 +901,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://radio.uchile.cl/2023/03/04/tras-allanamiento-a-alcalde-de-rancagua-expertos-en-transparencia-llaman-a-fortalecer-los-mecanismos-para-perseguir-la-corrupcion/</t>
     </r>
@@ -851,10 +913,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.meganoticias.cl/nacional/442934-alcalde-rancagua-formalizacion-abril-delitos-corrupcion-juan-ramon-godoy-21-03-2024.html</t>
     </r>
@@ -862,10 +925,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.cde.cl/cde-interpone-querella-criminal-contra-el-alcalde-de-rancagua-por-delitos-asociados-a-hechos-de-corrupcion/</t>
     </r>
@@ -894,10 +958,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-la-araucania/2024/01/07/imputado-en-arista-caso-convenios-gobernador-de-la-araucania-luciano-rivas-confirma-su-repostulacion.shtml</t>
     </r>
@@ -905,10 +970,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.cnnchile.com/pais/caso-convenios-fundacion-la-araucania-sueldo_20240901/</t>
     </r>
@@ -928,10 +994,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.cnnchile.com/pais/destitucion-alcalde-rinconada-contraloria-irregularidades_20230606/</t>
     </r>
@@ -939,10 +1006,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://munirinconada.cl/alcalde-juan-galdames-se-refiere-a-juicio-de-cuentas-que-ordena-la-restitucion-de-300-millones/</t>
     </r>
@@ -962,10 +1030,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.chiletransparente.cl/caso-larrainvial/</t>
     </r>
@@ -982,10 +1051,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elcomunal.cl/comunales/2024/03/25/15-demandas-1-querella-y-17-solicitudes-de-arresto-por-deudas-de-1500-millones-del-municipio-de-la-higuera-sacuden-a-yerko-galleguillos/</t>
     </r>
@@ -993,10 +1063,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elcomunal.cl/comunales/2024/10/04/contraloria-detecta-graves-irregularidades-en-municipalidad-de-la-higuera-y-envia-antecedentes-a-fiscalia/</t>
     </r>
@@ -1016,10 +1087,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.ovejeronoticias.cl/2023/12/puerto-natales-ex-alcalde-udi-fernando-paredes-continua-con-reclusion-domiciliaria-total/</t>
     </r>
@@ -1027,10 +1099,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elciudadano.com/justicia/trama-de-corrupcion-en-puerto-natales-envian-a-prision-al-exalcalde-jose-fernando-paredes-mansilla-por-red-de-cohecho/02/22/</t>
     </r>
@@ -1047,10 +1120,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.chiletransparente.cl/caso-luminarias/</t>
     </r>
@@ -1067,10 +1141,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.malaespinacheck.cl/pais/2023/08/04/fundacion-kimun-el-incumplido-contrato-por-1-200-millones/</t>
     </r>
@@ -1102,10 +1177,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.t13.cl/noticia/politica/decretan-suspension-condicional-causa-malversacion-fondos-fundador-rd-21-12-2022</t>
     </r>
@@ -1116,10 +1192,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elciudadano.com/justicia/caso-riggs-corte-confirma-fraude-fiscal-de-pinochet-y-multa-millonaria-para-su-familia/10/02/</t>
     </r>
@@ -1127,10 +1204,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/especial/bbcl-investiga/noticias/articulos/2024/10/01/reves-para-los-pinochet-corte-confirma-declaracion-maliciosa-de-impuestos-por-operaciones-en-el-riggs.shtml</t>
     </r>
@@ -1150,10 +1228,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.cooperativa.cl/noticias/pais/judicial/denuncias-de-corrupcion/de-que-se-acusa-exactamente-a-daniel-jadue/2024-06-03/202306.html</t>
     </r>
@@ -1161,10 +1240,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.cooperativa.cl/noticias/pais/politica/municipales/jadue-sospecha-de-doble-intencionalidad-de-proveedor-que-litiga-contra/2022-02-18/092208.html</t>
     </r>
@@ -1172,10 +1252,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.pjud.cl/prensa-y-comunicaciones/noticias-del-poder-judicial/110088</t>
     </r>
@@ -1189,10 +1270,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://es.wikipedia.org/wiki/Corrupción_en_Chile#El_caso_MOP-GATE</t>
     </r>
@@ -1212,10 +1294,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.malaespinacheck.cl/pais/2024/01/03/los-14-detenidos-en-todo-chile-por-el-caso-convenios/</t>
     </r>
@@ -1235,10 +1318,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.meganoticias.cl/amp/nacional/442953-mantencion-de-areas-verdes-alcalde-de-arica-firmo-trato-directo-por-1100-millones-con-empresa-creada-14-dias-antes.html</t>
     </r>
@@ -1246,10 +1330,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://conecta2tv.cl/denuncian-ante-la-fiscalia-al-alcalde-de-arica-gerardo-espindola-por-posible-malversacion-de-caudales-publicos/</t>
     </r>
@@ -1269,10 +1354,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2023/12/10/justicia-admite-querella-contra-alcaldesa-de-rio-bueno-por-malversacion-de-caudales-y-fraude-al-fisco.shtml</t>
     </r>
@@ -1295,10 +1381,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://cooperativa.cl/noticias/pais/judicial/denuncias-de-corrupcion/detenido-el-alcalde-de-algarrobo-se-entrego-frente-a-un-motel/2023-11-23/072824.html</t>
     </r>
@@ -1306,10 +1393,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-valparaiso/2024/06/04/desfalco-algarrobo-criptomonedas-propiedaes-estados-unidos.shtml</t>
     </r>
@@ -1326,10 +1414,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/chile/2024/03/19/milicogate-dictan-procesamiento-contra-general-y-coroneles-r-por-presunto-fraude-de-519-millones.shtml</t>
     </r>
@@ -1373,10 +1462,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://radio.uchile.cl/2023/11/18/cde-se-querello-contra-fundaciones-en-la-araucania-por-fraude-al-gore/</t>
     </r>
@@ -1384,10 +1474,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.malaespinacheck.cl/pais/2023/12/29/caso-manicure/</t>
     </r>
@@ -1395,10 +1486,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.cnnchile.com/pais/caso-convenios-corte-suprema-confirma-desafuero-de-diputado-mauricio-ojeda_20240930/</t>
     </r>
@@ -1415,10 +1507,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.meganoticias.cl/nacional/403342-contraloria-cifra-en-680-millones-posible-fraude-al-fisco-bajo-el-mandato-del-exintendente-guevara.html</t>
     </r>
@@ -1426,10 +1519,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://cronicas.americatransparente.org/los-otros-programas-vita-41-mil-millones-transferidos-a-entidades-privadas-de-lo-barnechea/</t>
     </r>
@@ -1437,10 +1531,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://cooperativa.cl/noticias/pais/politica/contraloria-envio-a-fiscalia-caso-de-millonarios-contratos-con/2023-01-23/152629.html</t>
     </r>
@@ -1457,10 +1552,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-del-maule/2024/03/11/pdi-allano-gobernacion-del-maule-en-medio-de-investigaciones-por-traspasos-a-urbanismo-social.shtml</t>
     </r>
@@ -1468,10 +1564,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-del-maule/2024/03/12/caso-convenios-jefe-de-control-interno-del-gore-maule-declaro-por-traspasos-a-urbanismo-social.shtml</t>
     </r>
@@ -1506,10 +1603,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/campuslt/noticia/luminarias-juzgado-de-garantia-de-iquique-condena-a-exconcejal-felipe-arenas-por-fraude-al-fisco-y-cohecho/OR3BBHZLARCULI7J5A22A66CSU/</t>
     </r>
@@ -1517,10 +1615,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://iquiquetv.cl/2024/07/02/caso-luminarias-led-condenan-a-ex-concejal-felipe-arenas-por-cohecho-y-fraude-al-fisco/</t>
     </r>
@@ -1537,10 +1636,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/earlyaccess/noticia/pintar-fachadas-turismo-creativo-y-ayuda-contra-el-suicidio-los-diversos-rubros-de-procultura-la-fundacion-con-mas-convenios-en-la-mira-de-fiscalia/PE7YFQCVMBAOTPHJPTUBEHVPUU/</t>
     </r>
@@ -1548,10 +1648,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.ex-ante.cl/perfil-lo-que-hay-que-saber-de-alberto-larrain-sus-vinculos-politicos-y-las-indagaciones-a-la-fundacion-procultura-que-creo/</t>
     </r>
@@ -1568,10 +1669,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.eldesconcierto.cl/reportajes/2024/01/23/municipio-se-querella-por-multa-de-500-millones-acusan-a-exalcalde-de-melipilla-por-fraude-al-fisco.html</t>
     </r>
@@ -1579,10 +1681,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/nacional/noticia/municipalidad-de-melipilla-presenta-querella-por-fraude-al-fisco-contra-el-exalcalde-ivan-campos/P6XRT2X73NAHJIEMIZWPRX6VEU/</t>
     </r>
@@ -1599,10 +1702,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elmostrador.cl/noticias/pais/2019/05/05/las-vueltas-de-la-vida-rn-elige-a-claudio-eguiluz-condenado-por-caso-sqm-como-su-presidente-regional-en-el-biobio/</t>
     </r>
@@ -1619,10 +1723,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-antofagasta/2024/09/03/caso-convenios-formalizan-a-carlos-contreras-por-tres-delitos-de-fraude-al-fisco.shtml</t>
     </r>
@@ -1647,10 +1752,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://radionuevomundo.cl/2023/07/18/gobernador-rivas-suma-al-caso-fundacion-local-traspasos-arbitrarios-a-coihue-y-a-universidades-de-la-araucania/</t>
     </r>
@@ -1658,10 +1764,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elciudadano.com/actualidad/el-entramado-de-ilicitos-de-platas-que-exploto-en-el-gore-araucania-y-que-repercute-en-renovacion-nacional/12/29/</t>
     </r>
@@ -1669,10 +1776,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://resumen.cl/articulos/la-derecha-de-la-araucania-en-el-caso-fundaciones-las-irregularidades-de-espacio-coigue-que-llevaron-al-ministerio-de-justicia-a-solicitar-su-cierre</t>
     </r>
@@ -1689,10 +1797,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elmostrador.cl/dia/2023/03/31/exsubsecretaria-martorell-declaro-como-imputada-por-corrupcion-en-caso-motorola/</t>
     </r>
@@ -1712,10 +1821,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.chilevision.cl/noticias/nacional/golborne-paga-11-4-millones-y-logra-salida-alternativa-del-caso-penta</t>
     </r>
@@ -1723,10 +1833,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/la-tercera-pm/noticia/golborne-sale-del-caso-penta-tras-pagar-114-millones/906364/</t>
     </r>
@@ -1746,10 +1857,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-del-bio-bio/2024/03/13/caso-convenios-allanan-empresa-que-facturo-356-millones-en-convenios-del-gore-bio-bio-y-bonhomia.shtml</t>
     </r>
@@ -1757,10 +1869,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://resumen.cl/articulos/fundacion-contrato-con-dineros-del-gore-biobio-a-empresas-de-coordinador-de-programa-y-a-firma-donde-trabaja-su-hermano-y-su-madre-excandidata-republicana</t>
     </r>
@@ -1768,10 +1881,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://cooperativa.cl/noticias/pais/region-del-biobio/detienen-a-lider-de-empresa-en-allanamiento-por-caso-convenios-pdi/2024-03-13/123002.html</t>
     </r>
@@ -1794,10 +1908,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>http://www.fiscaliadechile.cl/Fiscalia/sala_prensa/noticias_regional_det.do?id=22739</t>
     </r>
@@ -1805,10 +1920,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://resumen.cl/articulos/exalcalde-pasara-10-anos-en-carcel-por-apropiarse-de-351-millones-de-la-municipalidad-y-de-empresa-electrica</t>
     </r>
@@ -1828,10 +1944,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.24horas.cl/actualidad/politica/que-se-le-acusa-a-karina-oliva-emitir-boletas-falsas-defraudar-290-millones</t>
     </r>
@@ -1848,10 +1965,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.fastcheck.cl/2021/11/18/yasna-provoste-se-robo-600-millones-de-dolares-del-ministerio-de-educacion-falso/</t>
     </r>
@@ -1898,10 +2016,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://radio.uchile.cl/2021/04/16/a-la-carcel-ex-senador-udi-jaime-orpis-es-condenado-a-prision-por-cohecho-y-fraude-al-fisco/</t>
     </r>
@@ -1921,10 +2040,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://radio.uchile.cl/2023/11/28/755094/</t>
     </r>
@@ -1932,10 +2052,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://elpais.com/chile/2023-08-05/caso-lenceria-la-telenovelesca-arista-de-la-trama-de-corrupcion-que-hace-temblar-la-politica-chilena.html</t>
     </r>
@@ -1952,10 +2073,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/opinion/noticia/columna-de-daniel-matamala-cual-elefante/EOAKP2PXWJHSFDBAKRXGVVS5ZA/</t>
     </r>
@@ -1972,10 +2094,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.ciperchile.cl/2023/05/10/caso-itelecom-detectan-66-pagos-en-efectivo-a-principal-asesor-de-german-codina-por-203-millones/</t>
     </r>
@@ -1992,10 +2115,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://eltipografo.cl/2022/08/presentan-nueva-querella-por-fraude-al-fisco-contra-ex-alcalde-de-mostazal-sergio-medel-a</t>
     </r>
@@ -2003,10 +2127,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://eltipografo.cl/2023/03/deficit-de-8-mil-millones-en-el-municipio-y-querellas-por-fraude-al-fisco-enfrenta-ex-alcalde-de-mostazal</t>
     </r>
@@ -2014,10 +2139,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-ohiggins/2022/08/11/municipio-prepara-querellas-tras-millonarias-irregularidades-en-san-francisco-de-mostazal.shtml</t>
     </r>
@@ -2034,10 +2160,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/nacional/noticia/mas-de-200-millones-para-sanar-deudas-de-achifarp-y-pagos-a-funcionarios-fantasma-los-hitos-que-marcaron-el-primer-dia-de-formalizacion-del-alcalde-de-recoleta/YGFDCRRVJNFSXAA7KWM3YEIIUQ/</t>
     </r>
@@ -2054,10 +2181,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.malaespinacheck.cl/pais/2024/01/29/quien-es-daniel-agusto-perez-el-exalcalde-formalizado-por-fraude-al-fisco/</t>
     </r>
@@ -2065,10 +2193,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-antofagasta/2024/01/24/son-11-casos-de-karen-rojo-formalizaron-a-exdelegado-de-pinera-en-antofagasta-por-fraude-al-fisco.shtml</t>
     </r>
@@ -2103,10 +2232,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/nacional/noticia/exalcalde-de-nunoa-andres-zarhi-queda-con-arresto-domiciliario-nocturno-tras-formalizacion-por-fraude-al-fisco/64LJ53FVUJA4BIGCC4DMKIJWRU/</t>
     </r>
@@ -2114,10 +2244,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.emol.com/noticias/Nacional/2024/02/27/1123065/decretan-arresto-domiciliario-nocturno-andreszarhi.html</t>
     </r>
@@ -2137,10 +2268,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/nacional/noticia/formalizan-a-exdirector-general-de-la-pdi-hector-espinosa-fiscalia-le-imputa-apropiacion-de-dineros-de-gastos-reservados-de-la-institucion/IBGS7P3IPVGU3MQU4A7GJDH4UA/</t>
     </r>
@@ -2148,10 +2280,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.chvnoticias.cl/exclusivo-chv/todas-las-pruebas-fiscalia-hector-espinosa-pdi_20220828/</t>
     </r>
@@ -2168,10 +2301,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://cooperativa.cl/noticias/pais/region-del-maule/contraloria-ordeno-sumarios-contra-municipio-de-linares-rincon-acusa/2022-06-22/174906.html</t>
     </r>
@@ -2194,10 +2328,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.meganoticias.cl/nacional/420687-nexos-politicos-gore-arica-fundacion-comprometidos-280-millones-25-7-2023.html</t>
     </r>
@@ -2217,10 +2352,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-la-araucania/2024/01/25/caso-cuentas-corrientes-contraloria-ordena-al-municipio-de-lautaro-restituir-cerca-de-80-millones.shtml</t>
     </r>
@@ -2234,10 +2370,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.theclinic.cl/2024/02/27/pdi-acorrala-al-circulo-de-virginia-reginato-udi-acusa-a-exadministrador-municipal-de-millonarios-gastos-en-restaurantes-y-licorerias/</t>
     </r>
@@ -2245,10 +2382,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.soychile.cl/valparaiso/sociedad/2024/01/22/844669/formalizacion-vina-boisier-fisco-reacciones.html</t>
     </r>
@@ -2265,10 +2403,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/nacional/noticia/contraloria-detecta-dos-nuevos-municipios-involucrados-en-el-caso-cuentas-corrientes-y-deriva-antecedentes-a-la-fiscalia/5C3ZRUU3WFF4BFYSN4BG4GD7QE/</t>
     </r>
@@ -2276,10 +2415,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.elsancarlino.cl/2024/06/contraloria-detecta-dos-nuevos.html</t>
     </r>
@@ -2299,10 +2439,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-atacama/2020/08/01/alcalde-suplente-tierra-amarilla-quedo-prision-preventiva-tras-formalizacion-fraudes.shtml</t>
     </r>
@@ -2322,10 +2463,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.diarioconstitucional.cl/2023/06/20/ex-administrador-municipal-que-aprobo-el-financiamiento-para-que-alcalde-concejales-y-funcionarios-publicos-de-tierra-amarilla-emprendieran-viaje-turistico-a-la-habana-y-varadero-incurre-en-el-delit/</t>
     </r>
@@ -2333,10 +2475,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.cde.cl/cde-valora-condena-a-exadministrador-municipal-de-tierra-amarilla-en-caso-concejales-on-tour/#:~:text=(23.03.2023)</t>
     </r>
@@ -2345,6 +2488,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> El Tribunal,el marco del caso denominado</t>
     </r>
@@ -2364,10 +2508,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2024/02/15/cuentas-corrientes-rio-bueno-debera-restituir-76-millones-por-pagos-improcedentes-a-gestion-global.shtml</t>
     </r>
@@ -2375,10 +2520,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2023/09/24/caso-cuentas-corrientes-exalcalde-de-rio-bueno-declara-en-fiscalia-por-contratacion-de-gestion-global.shtml</t>
     </r>
@@ -2398,10 +2544,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.canal9.cl/episodios/noticias/2024/07/26/alcalde-de-coronel-y-concejal-araya-seran-formalizados-por-caso-puerto-coronel</t>
     </r>
@@ -2409,10 +2556,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.cooperativa.cl/noticias/pais/region-del-biobio/formalizaran-por-delitos-de-corrupcion-al-alcalde-de-coronel-y-a-otras/2024-07-26/084551.html</t>
     </r>
@@ -2420,10 +2568,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.meganoticias.cl/nacional/459252-querella-alcalde-coronel-boris-chamorro-cohecho-pago-coimas-17-09-2024.html</t>
     </r>
@@ -2431,10 +2580,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://sabes.cl/2024/09/17/cde-se-suma-al-caso-puerto-coronel-se-querella-contra-alcalde-boris-chamorro-por-delitos-ligados-a-corrupcion/</t>
     </r>
@@ -2451,10 +2601,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/politica/noticia/caso-penta-ex-subsecretario-pablo-wagner-condenado-delitos-tributarios-absuelto-cohecho/233126/</t>
     </r>
@@ -2483,10 +2634,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.chiletransparente.cl/caso-ceresita/</t>
     </r>
@@ -2503,10 +2655,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.diarioviregion.cl/index.php/noticias/27551-ex-alcalde-de-san-fernando-juan-paulo-molina-condenado-por-fraude-al-fisco-reiterado</t>
     </r>
@@ -2529,10 +2682,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://es.wikipedia.org/wiki/Caso_Coimas</t>
     </r>
@@ -2558,10 +2712,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.latercera.com/reportajes/noticia/la-excesiva-demora-contraloria-salvo-josefa-errazuriz/613135/</t>
     </r>
@@ -2590,10 +2745,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://cooperativa.cl/noticias/pais/region-de-antofagasta/ex-alcaldesa-karen-rojo-condenada-a-cinco-anos-de-carcel-por-fraude-al/2022-03-24/135330.html</t>
     </r>
@@ -2601,10 +2757,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://cooperativa.cl/noticias/pais/region-de-antofagasta/suprema-rechazo-recurso-de-nulidad-y-karen-rojo-debera-cumplir-pena-en/2022-03-23/155942.html</t>
     </r>
@@ -2612,10 +2769,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://chile.as.com/actualidad/detencion-de-karen-rojo-a-que-partido-pertenecia-cuanto-dinero-robo-y-por-que-estaba-en-holanda-n/</t>
     </r>
@@ -2629,10 +2787,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.emol.com/noticias/nacional/2014/10/23/686503/caso-efe-corte-ratifica-condena-en-contra-de-luis-ajenjo-por-fraude-al-fisco.html</t>
     </r>
@@ -2652,10 +2811,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.eldinamo.cl/pais/2013/08/28/sol-letelier-uso-23-millones-de-pesos-de-recoleta-para-su-campana-municipal/</t>
     </r>
@@ -2675,10 +2835,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-los-lagos/2023/09/13/causa-por-corrupcion-y-lavado-de-activos-fiscal-explica-allanamiento-en-municipio-de-puerto-montt.shtml</t>
     </r>
@@ -2686,10 +2847,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.diariodepuertomontt.cl/noticia/politica/2024/08/ter-ordena-la-remocion-del-alcalde-de-puerto-montt</t>
     </r>
@@ -2697,10 +2859,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.emol.com/noticias/Nacional/2024/08/23/1140650/remueven-alcalde-de-puerto-montt.html</t>
     </r>
@@ -2708,10 +2871,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.24horas.cl/regiones/zona-sur/los-lagos/alcalde-de-puerto-montt-destituido-notable-abandono-deberes</t>
     </r>
@@ -2725,10 +2889,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.emol.com/noticias/Nacional/2023/11/15/1112897/daniel-jadue-declaracion-farmacias-populares.html</t>
     </r>
@@ -2736,10 +2901,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/chile/2024/04/02/fiscalia-formalizara-a-daniel-jadue-por-cohecho-administracion-desleal-fraude-al-fisco-y-estafa.shtml</t>
     </r>
@@ -2783,10 +2949,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://elperiodico.cl/contraloria-corrobora-participacion-de-exfuncionaria-del-gore-araucania-en-comision-que-aprobo-proyecto-de-fundacion-que-posteriormente-la-contrato/</t>
     </r>
@@ -2806,10 +2973,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.emol.com/noticias/Nacional/2024/07/10/1136142/suprema-revoca-prision-preventiva.html</t>
     </r>
@@ -2817,10 +2985,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.emol.com/noticias/Nacional/2024/06/07/1133101/cronologia-delitos-fiscal-puerto-natales.html</t>
     </r>
@@ -2834,10 +3003,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.emol.com/noticias/Nacional/2024/02/20/1122268/contraloria-caso-convenios-minvu-serviu.html</t>
     </r>
@@ -2845,10 +3015,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.ex-ante.cl/confidencial-las-47-fundaciones-indagadas-por-justicia-en-el-caso-convenios/</t>
     </r>
@@ -2874,10 +3045,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/10/15/cuentas-corrientes-tesorero-municipal-acusado-de-cohecho-logra-salida-alternativa-tras-donar-200-mil.shtml</t>
     </r>
@@ -2885,10 +3057,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/25/causa-por-corrupcion-mantienen-prision-preventiva-para-alcalde-de-san-ignacio-y-un-operador-politico.shtml</t>
     </r>
@@ -2911,10 +3084,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.emol.com/noticias/Nacional/2024/02/15/1121826/caso-cuentas-corrientes.html</t>
     </r>
@@ -2937,10 +3111,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://radio.uchile.cl/2024/02/13/caso-cuentas-corrientes-detienen-a-alcalde-de-bulnes-por-delitos-economicos/</t>
     </r>
@@ -2957,61 +3132,83 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica"/>
+        <family val="2"/>
       </rPr>
       <t>https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/19/ex-udi-y-exasesor-de-sauerbaum-quien-es-el-operador-politico-investigado-por-corrupcion-en-nuble.shtml</t>
     </r>
+  </si>
+  <si>
+    <t>Andres Chadwick</t>
+  </si>
+  <si>
+    <t>Marcela Cubillos</t>
+  </si>
+  <si>
+    <t>Corrupción, soborno, cohecho, financiamiento irregular de la política</t>
+  </si>
+  <si>
+    <t>https://radio.uchile.cl/2024/09/30/marcela-cubillos-como-rostro-le-cobra-17-millones-mensuales-a-una-universidad/</t>
+  </si>
+  <si>
+    <t>https://www.elmostrador.cl/noticias/opinion/columnas/2024/09/27/los-17-millones-de-marcela-cubillos-un-caso-de-contratacion-politica/</t>
+  </si>
+  <si>
+    <t>Caso Cubillos - Universidad San Sebastián</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3155,112 +3352,118 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+  <cellXfs count="36">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3269,7 +3472,18 @@
   <dxfs count="2">
     <dxf>
       <font>
-        <color rgb="ff000000"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="12"/>
+          <bgColor indexed="14"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3278,45 +3492,89 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="ff000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="12"/>
-          <bgColor indexed="14"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffbdc0bf"/>
-      <rgbColor rgb="ffa5a5a5"/>
-      <rgbColor rgb="ff3f3f3f"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFBDC0BF"/>
+      <rgbColor rgb="FFA5A5A5"/>
+      <rgbColor rgb="FF3F3F3F"/>
       <rgbColor rgb="00000000"/>
-      <rgbColor rgb="7fff9781"/>
-      <rgbColor rgb="7f88ccff"/>
-      <rgbColor rgb="ff919191"/>
-      <rgbColor rgb="ffdbdbdb"/>
+      <rgbColor rgb="7FFF9781"/>
+      <rgbColor rgb="7F88CCFF"/>
+      <rgbColor rgb="FF919191"/>
+      <rgbColor rgb="FFDBDBDB"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Blank">
   <a:themeElements>
     <a:clrScheme name="Blank">
       <a:dk1>
@@ -3515,7 +3773,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -3533,7 +3791,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1200" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3562,7 +3820,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3587,7 +3845,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3612,7 +3870,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3637,7 +3895,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3662,7 +3920,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3687,7 +3945,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3712,7 +3970,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3737,7 +3995,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3762,7 +4020,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3775,9 +4033,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -3794,7 +4058,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -3812,7 +4076,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3837,7 +4101,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3862,7 +4126,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3887,7 +4151,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3912,7 +4176,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3937,7 +4201,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3962,7 +4226,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3987,7 +4251,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4012,7 +4276,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4037,7 +4301,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4050,9 +4314,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -4066,7 +4336,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -4084,7 +4354,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4113,7 +4383,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4138,7 +4408,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4163,7 +4433,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4188,7 +4458,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4213,7 +4483,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4238,7 +4508,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4263,7 +4533,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4288,7 +4558,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4313,7 +4583,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -4326,137 +4596,144 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X115"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="33.7266" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.3516" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.22656" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.4922" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5469" style="1" customWidth="1"/>
-    <col min="7" max="8" width="5.22656" style="1" customWidth="1"/>
-    <col min="9" max="13" width="16.3516" style="1" customWidth="1"/>
-    <col min="14" max="14" width="23.9453" style="1" customWidth="1"/>
-    <col min="15" max="16" width="16.3516" style="1" customWidth="1"/>
-    <col min="17" max="17" width="11.4922" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.6875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="22.7344" style="1" customWidth="1"/>
-    <col min="20" max="20" width="40.2734" style="1" customWidth="1"/>
-    <col min="21" max="21" width="38.2188" style="1" customWidth="1"/>
-    <col min="22" max="24" width="16.3516" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="1" width="40.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
+    <col min="7" max="8" width="5.1640625" style="1" customWidth="1"/>
+    <col min="9" max="13" width="16.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24" style="1" customWidth="1"/>
+    <col min="15" max="16" width="16.33203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="22.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="40.33203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="38.1640625" style="1" customWidth="1"/>
+    <col min="22" max="25" width="16.33203125" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="44.55" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:24" ht="44.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="2">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="2">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="2">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="3">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="3">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s" s="2">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="2">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s" s="2">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s" s="4">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s" s="5">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s" s="5">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s" s="3">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s" s="3">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s" s="3">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s" s="4">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s" s="4">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s" s="4">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s" s="4">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s" s="4">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" ht="32.55" customHeight="1">
-      <c r="A2" t="s" s="6">
+    <row r="2" spans="1:24" ht="32.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="7">
+      <c r="B2" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="8">
         <v>2023</v>
       </c>
-      <c r="D2" t="s" s="9">
+      <c r="D2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s" s="9">
+      <c r="E2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s" s="9">
+      <c r="F2" s="9" t="s">
         <v>28</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
-      <c r="J2" t="s" s="9">
+      <c r="J2" s="9" t="s">
         <v>29</v>
       </c>
       <c r="K2" s="10"/>
@@ -4474,11 +4751,11 @@
       <c r="W2" s="11"/>
       <c r="X2" s="11"/>
     </row>
-    <row r="3" ht="32.35" customHeight="1">
-      <c r="A3" t="s" s="13">
+    <row r="3" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s" s="14">
+      <c r="B3" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="15">
@@ -4489,15 +4766,15 @@
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
-      <c r="I3" t="s" s="17">
+      <c r="I3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="J3" t="s" s="17">
+      <c r="J3" s="17" t="s">
         <v>29</v>
       </c>
       <c r="K3" s="16"/>
       <c r="L3" s="16"/>
-      <c r="M3" t="s" s="17">
+      <c r="M3" s="17" t="s">
         <v>32</v>
       </c>
       <c r="N3" s="18"/>
@@ -4506,7 +4783,7 @@
       <c r="Q3" s="16"/>
       <c r="R3" s="19"/>
       <c r="S3" s="16"/>
-      <c r="T3" t="s" s="20">
+      <c r="T3" s="20" t="s">
         <v>33</v>
       </c>
       <c r="U3" s="18"/>
@@ -4514,8 +4791,8 @@
       <c r="W3" s="18"/>
       <c r="X3" s="18"/>
     </row>
-    <row r="4" ht="32.05" customHeight="1">
-      <c r="A4" t="s" s="21">
+    <row r="4" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="21" t="s">
         <v>34</v>
       </c>
       <c r="B4" s="22">
@@ -4524,13 +4801,13 @@
       <c r="C4" s="23">
         <v>2021</v>
       </c>
-      <c r="D4" t="s" s="24">
+      <c r="D4" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E4" t="s" s="24">
+      <c r="E4" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s" s="24">
+      <c r="F4" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G4" s="23">
@@ -4539,39 +4816,39 @@
       <c r="H4" s="23">
         <v>2021</v>
       </c>
-      <c r="I4" t="s" s="24">
+      <c r="I4" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="J4" t="s" s="24">
+      <c r="J4" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K4" s="19"/>
-      <c r="L4" t="s" s="24">
+      <c r="L4" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M4" s="19"/>
       <c r="N4" s="25"/>
-      <c r="O4" t="s" s="26">
+      <c r="O4" s="26" t="s">
         <v>39</v>
       </c>
       <c r="P4" s="25"/>
       <c r="Q4" s="19"/>
       <c r="R4" s="19"/>
       <c r="S4" s="19"/>
-      <c r="T4" t="s" s="26">
+      <c r="T4" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="U4" t="s" s="26">
+      <c r="U4" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="V4" t="s" s="26">
+      <c r="V4" s="26" t="s">
         <v>42</v>
       </c>
       <c r="W4" s="25"/>
       <c r="X4" s="25"/>
     </row>
-    <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" t="s" s="21">
+    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="21" t="s">
         <v>43</v>
       </c>
       <c r="B5" s="22">
@@ -4580,52 +4857,52 @@
       <c r="C5" s="23">
         <v>2024</v>
       </c>
-      <c r="D5" t="s" s="24">
+      <c r="D5" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="E5" t="s" s="24">
+      <c r="E5" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F5" t="s" s="24">
+      <c r="F5" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
-      <c r="I5" t="s" s="24">
+      <c r="I5" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="J5" t="s" s="24">
+      <c r="J5" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K5" s="19"/>
-      <c r="L5" t="s" s="24">
+      <c r="L5" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M5" s="19"/>
       <c r="N5" s="25"/>
-      <c r="O5" t="s" s="26">
+      <c r="O5" s="26" t="s">
         <v>46</v>
       </c>
       <c r="P5" s="25"/>
       <c r="Q5" s="19"/>
       <c r="R5" s="19"/>
-      <c r="S5" t="s" s="24">
+      <c r="S5" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="T5" t="s" s="26">
+      <c r="T5" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="U5" t="s" s="26">
+      <c r="U5" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="V5" t="s" s="26">
+      <c r="V5" s="26" t="s">
         <v>50</v>
       </c>
       <c r="W5" s="25"/>
       <c r="X5" s="25"/>
     </row>
-    <row r="6" ht="44.05" customHeight="1">
-      <c r="A6" t="s" s="21">
+    <row r="6" spans="1:24" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="21" t="s">
         <v>51</v>
       </c>
       <c r="B6" s="22">
@@ -4634,10 +4911,10 @@
       <c r="C6" s="23">
         <v>2016</v>
       </c>
-      <c r="D6" t="s" s="24">
+      <c r="D6" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="E6" t="s" s="24">
+      <c r="E6" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F6" s="19"/>
@@ -4648,21 +4925,21 @@
         <v>2017</v>
       </c>
       <c r="I6" s="27"/>
-      <c r="J6" t="s" s="24">
+      <c r="J6" s="24" t="s">
         <v>54</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
       <c r="N6" s="25"/>
-      <c r="O6" t="s" s="26">
+      <c r="O6" s="26" t="s">
         <v>55</v>
       </c>
       <c r="P6" s="25"/>
       <c r="Q6" s="19"/>
       <c r="R6" s="19"/>
       <c r="S6" s="19"/>
-      <c r="T6" t="s" s="26">
+      <c r="T6" s="26" t="s">
         <v>56</v>
       </c>
       <c r="U6" s="25"/>
@@ -4670,8 +4947,8 @@
       <c r="W6" s="25"/>
       <c r="X6" s="25"/>
     </row>
-    <row r="7" ht="32.05" customHeight="1">
-      <c r="A7" t="s" s="21">
+    <row r="7" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B7" s="22">
@@ -4680,13 +4957,13 @@
       <c r="C7" s="23">
         <v>2014</v>
       </c>
-      <c r="D7" t="s" s="24">
+      <c r="D7" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="E7" t="s" s="24">
+      <c r="E7" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F7" t="s" s="24">
+      <c r="F7" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G7" s="23">
@@ -4694,18 +4971,18 @@
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="27"/>
-      <c r="J7" t="s" s="24">
+      <c r="J7" s="24" t="s">
         <v>59</v>
       </c>
       <c r="K7" s="19"/>
-      <c r="L7" t="s" s="24">
+      <c r="L7" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="M7" t="s" s="24">
+      <c r="M7" s="24" t="s">
         <v>60</v>
       </c>
       <c r="N7" s="25"/>
-      <c r="O7" t="s" s="26">
+      <c r="O7" s="26" t="s">
         <v>61</v>
       </c>
       <c r="P7" s="25"/>
@@ -4718,8 +4995,8 @@
       <c r="W7" s="25"/>
       <c r="X7" s="25"/>
     </row>
-    <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" t="s" s="21">
+    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="21" t="s">
         <v>62</v>
       </c>
       <c r="B8" s="22">
@@ -4728,35 +5005,35 @@
       <c r="C8" s="23">
         <v>2006</v>
       </c>
-      <c r="D8" t="s" s="24">
+      <c r="D8" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="E8" t="s" s="24">
+      <c r="E8" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F8" t="s" s="24">
+      <c r="F8" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
-      <c r="J8" t="s" s="24">
+      <c r="J8" s="24" t="s">
         <v>64</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" s="25"/>
-      <c r="O8" t="s" s="26">
+      <c r="O8" s="26" t="s">
         <v>65</v>
       </c>
       <c r="P8" s="25"/>
       <c r="Q8" s="19"/>
       <c r="R8" s="19"/>
-      <c r="S8" t="s" s="24">
+      <c r="S8" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="T8" t="s" s="26">
+      <c r="T8" s="26" t="s">
         <v>67</v>
       </c>
       <c r="U8" s="25"/>
@@ -4764,8 +5041,8 @@
       <c r="W8" s="25"/>
       <c r="X8" s="25"/>
     </row>
-    <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" t="s" s="21">
+    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="21" t="s">
         <v>68</v>
       </c>
       <c r="B9" s="22">
@@ -4774,10 +5051,10 @@
       <c r="C9" s="23">
         <v>1989</v>
       </c>
-      <c r="D9" t="s" s="24">
+      <c r="D9" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="E9" t="s" s="24">
+      <c r="E9" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="19"/>
@@ -4789,16 +5066,16 @@
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="25"/>
-      <c r="O9" t="s" s="26">
+      <c r="O9" s="26" t="s">
         <v>70</v>
       </c>
       <c r="P9" s="25"/>
       <c r="Q9" s="19"/>
       <c r="R9" s="19"/>
-      <c r="S9" t="s" s="24">
+      <c r="S9" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="T9" t="s" s="26">
+      <c r="T9" s="26" t="s">
         <v>72</v>
       </c>
       <c r="U9" s="25"/>
@@ -4806,8 +5083,8 @@
       <c r="W9" s="25"/>
       <c r="X9" s="25"/>
     </row>
-    <row r="10" ht="44.05" customHeight="1">
-      <c r="A10" t="s" s="21">
+    <row r="10" spans="1:24" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="21" t="s">
         <v>73</v>
       </c>
       <c r="B10" s="22">
@@ -4816,10 +5093,10 @@
       <c r="C10" s="23">
         <v>2019</v>
       </c>
-      <c r="D10" t="s" s="24">
+      <c r="D10" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="E10" t="s" s="24">
+      <c r="E10" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F10" s="19"/>
@@ -4832,30 +5109,30 @@
       <c r="I10" s="27"/>
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
-      <c r="L10" t="s" s="24">
+      <c r="L10" s="24" t="s">
         <v>75</v>
       </c>
       <c r="M10" s="19"/>
       <c r="N10" s="25"/>
-      <c r="O10" t="s" s="26">
+      <c r="O10" s="26" t="s">
         <v>76</v>
       </c>
       <c r="P10" s="25"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
       <c r="S10" s="19"/>
-      <c r="T10" t="s" s="26">
+      <c r="T10" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="U10" t="s" s="26">
+      <c r="U10" s="26" t="s">
         <v>78</v>
       </c>
       <c r="V10" s="25"/>
       <c r="W10" s="25"/>
       <c r="X10" s="25"/>
     </row>
-    <row r="11" ht="32.05" customHeight="1">
-      <c r="A11" t="s" s="21">
+    <row r="11" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="21" t="s">
         <v>79</v>
       </c>
       <c r="B11" s="22">
@@ -4865,7 +5142,7 @@
         <v>2015</v>
       </c>
       <c r="D11" s="19"/>
-      <c r="E11" t="s" s="24">
+      <c r="E11" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F11" s="19"/>
@@ -4876,23 +5153,23 @@
         <v>2018</v>
       </c>
       <c r="I11" s="27"/>
-      <c r="J11" t="s" s="24">
+      <c r="J11" s="24" t="s">
         <v>59</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
-      <c r="M11" t="s" s="24">
+      <c r="M11" s="24" t="s">
         <v>60</v>
       </c>
       <c r="N11" s="25"/>
-      <c r="O11" t="s" s="26">
+      <c r="O11" s="26" t="s">
         <v>80</v>
       </c>
       <c r="P11" s="25"/>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
       <c r="S11" s="19"/>
-      <c r="T11" t="s" s="26">
+      <c r="T11" s="26" t="s">
         <v>81</v>
       </c>
       <c r="U11" s="25"/>
@@ -4900,8 +5177,8 @@
       <c r="W11" s="25"/>
       <c r="X11" s="25"/>
     </row>
-    <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" t="s" s="21">
+    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="21" t="s">
         <v>82</v>
       </c>
       <c r="B12" s="22">
@@ -4910,35 +5187,35 @@
       <c r="C12" s="23">
         <v>2018</v>
       </c>
-      <c r="D12" t="s" s="24">
+      <c r="D12" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E12" t="s" s="24">
+      <c r="E12" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F12" t="s" s="24">
+      <c r="F12" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
-      <c r="I12" t="s" s="24">
+      <c r="I12" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="J12" t="s" s="24">
+      <c r="J12" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K12" s="19"/>
       <c r="L12" s="19"/>
       <c r="M12" s="19"/>
       <c r="N12" s="25"/>
-      <c r="O12" t="s" s="26">
+      <c r="O12" s="26" t="s">
         <v>85</v>
       </c>
       <c r="P12" s="25"/>
       <c r="Q12" s="19"/>
       <c r="R12" s="19"/>
       <c r="S12" s="19"/>
-      <c r="T12" t="s" s="26">
+      <c r="T12" s="26" t="s">
         <v>86</v>
       </c>
       <c r="U12" s="25"/>
@@ -4946,8 +5223,8 @@
       <c r="W12" s="25"/>
       <c r="X12" s="25"/>
     </row>
-    <row r="13" ht="32.05" customHeight="1">
-      <c r="A13" t="s" s="21">
+    <row r="13" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="21" t="s">
         <v>87</v>
       </c>
       <c r="B13" s="22">
@@ -4956,13 +5233,13 @@
       <c r="C13" s="23">
         <v>2021</v>
       </c>
-      <c r="D13" t="s" s="24">
+      <c r="D13" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="E13" t="s" s="24">
+      <c r="E13" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F13" t="s" s="24">
+      <c r="F13" s="24" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="23">
@@ -4971,28 +5248,28 @@
       <c r="H13" s="23">
         <v>2020</v>
       </c>
-      <c r="I13" t="s" s="24">
+      <c r="I13" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="J13" t="s" s="24">
+      <c r="J13" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K13" s="19"/>
-      <c r="L13" t="s" s="24">
+      <c r="L13" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M13" s="19"/>
       <c r="N13" s="25"/>
-      <c r="O13" t="s" s="26">
+      <c r="O13" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="P13" t="s" s="26">
+      <c r="P13" s="26" t="s">
         <v>93</v>
       </c>
       <c r="Q13" s="19"/>
       <c r="R13" s="19"/>
       <c r="S13" s="19"/>
-      <c r="T13" t="s" s="26">
+      <c r="T13" s="26" t="s">
         <v>94</v>
       </c>
       <c r="U13" s="25"/>
@@ -5000,8 +5277,8 @@
       <c r="W13" s="25"/>
       <c r="X13" s="25"/>
     </row>
-    <row r="14" ht="32.05" customHeight="1">
-      <c r="A14" t="s" s="21">
+    <row r="14" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="21" t="s">
         <v>95</v>
       </c>
       <c r="B14" s="22">
@@ -5010,37 +5287,37 @@
       <c r="C14" s="23">
         <v>2017</v>
       </c>
-      <c r="D14" t="s" s="24">
+      <c r="D14" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E14" t="s" s="24">
+      <c r="E14" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F14" t="s" s="24">
+      <c r="F14" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
-      <c r="I14" t="s" s="24">
+      <c r="I14" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="J14" t="s" s="24">
+      <c r="J14" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K14" s="19"/>
-      <c r="L14" t="s" s="24">
+      <c r="L14" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M14" s="19"/>
       <c r="N14" s="25"/>
-      <c r="O14" t="s" s="26">
+      <c r="O14" s="26" t="s">
         <v>97</v>
       </c>
       <c r="P14" s="25"/>
       <c r="Q14" s="19"/>
       <c r="R14" s="19"/>
       <c r="S14" s="19"/>
-      <c r="T14" t="s" s="26">
+      <c r="T14" s="26" t="s">
         <v>98</v>
       </c>
       <c r="U14" s="25"/>
@@ -5048,8 +5325,8 @@
       <c r="W14" s="25"/>
       <c r="X14" s="25"/>
     </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" t="s" s="21">
+    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="21" t="s">
         <v>99</v>
       </c>
       <c r="B15" s="22">
@@ -5059,7 +5336,7 @@
         <v>2023</v>
       </c>
       <c r="D15" s="19"/>
-      <c r="E15" t="s" s="24">
+      <c r="E15" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F15" s="19"/>
@@ -5068,19 +5345,19 @@
       <c r="I15" s="19"/>
       <c r="J15" s="19"/>
       <c r="K15" s="19"/>
-      <c r="L15" t="s" s="24">
+      <c r="L15" s="24" t="s">
         <v>75</v>
       </c>
       <c r="M15" s="19"/>
       <c r="N15" s="25"/>
-      <c r="O15" t="s" s="26">
+      <c r="O15" s="26" t="s">
         <v>100</v>
       </c>
       <c r="P15" s="25"/>
       <c r="Q15" s="19"/>
       <c r="R15" s="19"/>
       <c r="S15" s="19"/>
-      <c r="T15" t="s" s="26">
+      <c r="T15" s="26" t="s">
         <v>101</v>
       </c>
       <c r="U15" s="25"/>
@@ -5088,8 +5365,8 @@
       <c r="W15" s="25"/>
       <c r="X15" s="25"/>
     </row>
-    <row r="16" ht="32.05" customHeight="1">
-      <c r="A16" t="s" s="21">
+    <row r="16" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="21" t="s">
         <v>102</v>
       </c>
       <c r="B16" s="22">
@@ -5098,46 +5375,46 @@
       <c r="C16" s="23">
         <v>2024</v>
       </c>
-      <c r="D16" t="s" s="24">
+      <c r="D16" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="E16" t="s" s="24">
+      <c r="E16" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F16" t="s" s="24">
+      <c r="F16" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
-      <c r="I16" t="s" s="24">
+      <c r="I16" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J16" t="s" s="24">
+      <c r="J16" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
       <c r="M16" s="19"/>
       <c r="N16" s="25"/>
-      <c r="O16" t="s" s="26">
+      <c r="O16" s="26" t="s">
         <v>105</v>
       </c>
       <c r="P16" s="25"/>
       <c r="Q16" s="19"/>
       <c r="R16" s="19"/>
       <c r="S16" s="25"/>
-      <c r="T16" t="s" s="26">
+      <c r="T16" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="U16" t="s" s="26">
+      <c r="U16" s="26" t="s">
         <v>107</v>
       </c>
       <c r="V16" s="25"/>
       <c r="W16" s="25"/>
       <c r="X16" s="25"/>
     </row>
-    <row r="17" ht="32.05" customHeight="1">
-      <c r="A17" t="s" s="21">
+    <row r="17" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="21" t="s">
         <v>108</v>
       </c>
       <c r="B17" s="22">
@@ -5146,13 +5423,13 @@
       <c r="C17" s="23">
         <v>2018</v>
       </c>
-      <c r="D17" t="s" s="24">
+      <c r="D17" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="E17" t="s" s="24">
+      <c r="E17" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F17" t="s" s="24">
+      <c r="F17" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="23">
@@ -5161,26 +5438,26 @@
       <c r="H17" s="23">
         <v>2021</v>
       </c>
-      <c r="I17" t="s" s="24">
+      <c r="I17" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="J17" t="s" s="24">
+      <c r="J17" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K17" s="19"/>
-      <c r="L17" t="s" s="24">
+      <c r="L17" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M17" s="19"/>
       <c r="N17" s="25"/>
-      <c r="O17" t="s" s="26">
+      <c r="O17" s="26" t="s">
         <v>111</v>
       </c>
       <c r="P17" s="25"/>
       <c r="Q17" s="19"/>
       <c r="R17" s="19"/>
       <c r="S17" s="19"/>
-      <c r="T17" t="s" s="26">
+      <c r="T17" s="26" t="s">
         <v>112</v>
       </c>
       <c r="U17" s="19"/>
@@ -5188,8 +5465,8 @@
       <c r="W17" s="25"/>
       <c r="X17" s="25"/>
     </row>
-    <row r="18" ht="44.05" customHeight="1">
-      <c r="A18" t="s" s="21">
+    <row r="18" spans="1:24" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="21" t="s">
         <v>113</v>
       </c>
       <c r="B18" s="22">
@@ -5198,13 +5475,13 @@
       <c r="C18" s="23">
         <v>2012</v>
       </c>
-      <c r="D18" t="s" s="24">
+      <c r="D18" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="E18" t="s" s="24">
+      <c r="E18" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F18" t="s" s="24">
+      <c r="F18" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="23">
@@ -5214,36 +5491,36 @@
         <v>2015</v>
       </c>
       <c r="I18" s="19"/>
-      <c r="J18" t="s" s="24">
+      <c r="J18" s="24" t="s">
         <v>115</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
       <c r="M18" s="19"/>
       <c r="N18" s="25"/>
-      <c r="O18" t="s" s="26">
+      <c r="O18" s="26" t="s">
         <v>116</v>
       </c>
       <c r="P18" s="25"/>
       <c r="Q18" s="19"/>
       <c r="R18" s="19"/>
-      <c r="S18" t="s" s="24">
+      <c r="S18" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="T18" t="s" s="26">
+      <c r="T18" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="U18" t="s" s="26">
+      <c r="U18" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="V18" t="s" s="26">
+      <c r="V18" s="26" t="s">
         <v>120</v>
       </c>
       <c r="W18" s="25"/>
       <c r="X18" s="25"/>
     </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" t="s" s="21">
+    <row r="19" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="21" t="s">
         <v>121</v>
       </c>
       <c r="B19" s="22">
@@ -5252,54 +5529,54 @@
       <c r="C19" s="23">
         <v>2023</v>
       </c>
-      <c r="D19" t="s" s="24">
+      <c r="D19" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="E19" t="s" s="24">
+      <c r="E19" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F19" t="s" s="24">
+      <c r="F19" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
-      <c r="I19" t="s" s="24">
+      <c r="I19" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="J19" t="s" s="24">
+      <c r="J19" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K19" s="19"/>
-      <c r="L19" t="s" s="24">
+      <c r="L19" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M19" s="19"/>
       <c r="N19" s="25"/>
-      <c r="O19" t="s" s="26">
+      <c r="O19" s="26" t="s">
         <v>124</v>
       </c>
       <c r="P19" s="25"/>
       <c r="Q19" s="19"/>
       <c r="R19" s="19"/>
-      <c r="S19" t="s" s="24">
+      <c r="S19" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="T19" t="s" s="26">
+      <c r="T19" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="U19" t="s" s="26">
+      <c r="U19" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="V19" t="s" s="26">
+      <c r="V19" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="W19" t="s" s="26">
+      <c r="W19" s="26" t="s">
         <v>128</v>
       </c>
       <c r="X19" s="25"/>
     </row>
-    <row r="20" ht="32.05" customHeight="1">
-      <c r="A20" t="s" s="21">
+    <row r="20" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="21" t="s">
         <v>129</v>
       </c>
       <c r="B20" s="22">
@@ -5308,13 +5585,13 @@
       <c r="C20" s="23">
         <v>2020</v>
       </c>
-      <c r="D20" t="s" s="24">
+      <c r="D20" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="E20" t="s" s="24">
+      <c r="E20" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F20" t="s" s="24">
+      <c r="F20" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G20" s="23">
@@ -5323,24 +5600,24 @@
       <c r="H20" s="23">
         <v>2020</v>
       </c>
-      <c r="I20" t="s" s="24">
+      <c r="I20" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="J20" t="s" s="24">
+      <c r="J20" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="25"/>
-      <c r="O20" t="s" s="26">
+      <c r="O20" s="26" t="s">
         <v>132</v>
       </c>
       <c r="P20" s="25"/>
       <c r="Q20" s="19"/>
       <c r="R20" s="19"/>
       <c r="S20" s="19"/>
-      <c r="T20" t="s" s="26">
+      <c r="T20" s="26" t="s">
         <v>133</v>
       </c>
       <c r="U20" s="25"/>
@@ -5348,8 +5625,8 @@
       <c r="W20" s="25"/>
       <c r="X20" s="25"/>
     </row>
-    <row r="21" ht="20.05" customHeight="1">
-      <c r="A21" t="s" s="21">
+    <row r="21" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="21" t="s">
         <v>134</v>
       </c>
       <c r="B21" s="22">
@@ -5358,13 +5635,13 @@
       <c r="C21" s="23">
         <v>2024</v>
       </c>
-      <c r="D21" t="s" s="24">
+      <c r="D21" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="E21" t="s" s="24">
+      <c r="E21" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="F21" t="s" s="24">
+      <c r="F21" s="24" t="s">
         <v>136</v>
       </c>
       <c r="G21" s="23">
@@ -5373,24 +5650,24 @@
       <c r="H21" s="23">
         <v>2021</v>
       </c>
-      <c r="I21" t="s" s="24">
+      <c r="I21" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="J21" t="s" s="24">
+      <c r="J21" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K21" s="19"/>
       <c r="L21" s="19"/>
       <c r="M21" s="19"/>
       <c r="N21" s="25"/>
-      <c r="O21" t="s" s="26">
+      <c r="O21" s="26" t="s">
         <v>138</v>
       </c>
       <c r="P21" s="25"/>
       <c r="Q21" s="19"/>
       <c r="R21" s="19"/>
       <c r="S21" s="19"/>
-      <c r="T21" t="s" s="26">
+      <c r="T21" s="26" t="s">
         <v>139</v>
       </c>
       <c r="U21" s="25"/>
@@ -5398,8 +5675,8 @@
       <c r="W21" s="25"/>
       <c r="X21" s="25"/>
     </row>
-    <row r="22" ht="32.35" customHeight="1">
-      <c r="A22" t="s" s="13">
+    <row r="22" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="13" t="s">
         <v>140</v>
       </c>
       <c r="B22" s="28">
@@ -5408,13 +5685,13 @@
       <c r="C22" s="15">
         <v>2020</v>
       </c>
-      <c r="D22" t="s" s="29">
+      <c r="D22" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="E22" t="s" s="17">
+      <c r="E22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F22" t="s" s="17">
+      <c r="F22" s="17" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="15">
@@ -5423,41 +5700,41 @@
       <c r="H22" s="15">
         <v>2022</v>
       </c>
-      <c r="I22" t="s" s="17">
+      <c r="I22" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="J22" t="s" s="17">
+      <c r="J22" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="K22" t="s" s="17">
+      <c r="K22" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="L22" t="s" s="17">
+      <c r="L22" s="17" t="s">
         <v>29</v>
       </c>
       <c r="M22" s="16"/>
       <c r="N22" s="18"/>
-      <c r="O22" t="s" s="20">
+      <c r="O22" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="P22" t="s" s="20">
+      <c r="P22" s="20" t="s">
         <v>93</v>
       </c>
       <c r="Q22" s="16"/>
       <c r="R22" s="19"/>
       <c r="S22" s="16"/>
-      <c r="T22" t="s" s="20">
+      <c r="T22" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="U22" t="s" s="20">
+      <c r="U22" s="20" t="s">
         <v>147</v>
       </c>
       <c r="V22" s="18"/>
       <c r="W22" s="18"/>
       <c r="X22" s="18"/>
     </row>
-    <row r="23" ht="20.05" customHeight="1">
-      <c r="A23" t="s" s="21">
+    <row r="23" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="21" t="s">
         <v>148</v>
       </c>
       <c r="B23" s="22">
@@ -5467,41 +5744,41 @@
         <v>2003</v>
       </c>
       <c r="D23" s="19"/>
-      <c r="E23" t="s" s="24">
+      <c r="E23" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
       <c r="I23" s="27"/>
-      <c r="J23" t="s" s="24">
+      <c r="J23" s="24" t="s">
         <v>59</v>
       </c>
       <c r="K23" s="19"/>
-      <c r="L23" t="s" s="24">
+      <c r="L23" s="24" t="s">
         <v>75</v>
       </c>
       <c r="M23" s="19"/>
       <c r="N23" s="25"/>
-      <c r="O23" t="s" s="26">
+      <c r="O23" s="26" t="s">
         <v>149</v>
       </c>
       <c r="P23" s="25"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
       <c r="S23" s="19"/>
-      <c r="T23" t="s" s="26">
+      <c r="T23" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="U23" t="s" s="26">
+      <c r="U23" s="26" t="s">
         <v>151</v>
       </c>
       <c r="V23" s="25"/>
       <c r="W23" s="25"/>
       <c r="X23" s="25"/>
     </row>
-    <row r="24" ht="20.35" customHeight="1">
-      <c r="A24" t="s" s="30">
+    <row r="24" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="30" t="s">
         <v>152</v>
       </c>
       <c r="B24" s="31">
@@ -5511,22 +5788,22 @@
         <v>2023</v>
       </c>
       <c r="D24" s="16"/>
-      <c r="E24" t="s" s="17">
+      <c r="E24" s="17" t="s">
         <v>53</v>
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
-      <c r="I24" t="s" s="17">
+      <c r="I24" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="J24" t="s" s="17">
+      <c r="J24" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="16"/>
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
-      <c r="N24" t="s" s="20">
+      <c r="N24" s="20" t="s">
         <v>154</v>
       </c>
       <c r="O24" s="18"/>
@@ -5534,18 +5811,18 @@
       <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
-      <c r="T24" t="s" s="20">
+      <c r="T24" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="U24" t="s" s="20">
+      <c r="U24" s="20" t="s">
         <v>156</v>
       </c>
       <c r="V24" s="18"/>
       <c r="W24" s="18"/>
       <c r="X24" s="18"/>
     </row>
-    <row r="25" ht="20.05" customHeight="1">
-      <c r="A25" t="s" s="21">
+    <row r="25" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="21" t="s">
         <v>157</v>
       </c>
       <c r="B25" s="22">
@@ -5554,13 +5831,13 @@
       <c r="C25" s="23">
         <v>2017</v>
       </c>
-      <c r="D25" t="s" s="24">
+      <c r="D25" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="E25" t="s" s="24">
+      <c r="E25" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F25" t="s" s="24">
+      <c r="F25" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G25" s="23">
@@ -5569,41 +5846,41 @@
       <c r="H25" s="23">
         <v>2024</v>
       </c>
-      <c r="I25" t="s" s="24">
+      <c r="I25" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="J25" t="s" s="24">
+      <c r="J25" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K25" s="19"/>
-      <c r="L25" t="s" s="24">
+      <c r="L25" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M25" s="19"/>
       <c r="N25" s="25"/>
-      <c r="O25" t="s" s="26">
+      <c r="O25" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="P25" t="s" s="26">
+      <c r="P25" s="26" t="s">
         <v>93</v>
       </c>
       <c r="Q25" s="19"/>
       <c r="R25" s="19"/>
       <c r="S25" s="19"/>
-      <c r="T25" t="s" s="26">
+      <c r="T25" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="U25" t="s" s="26">
+      <c r="U25" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="V25" t="s" s="26">
+      <c r="V25" s="26" t="s">
         <v>163</v>
       </c>
       <c r="W25" s="25"/>
       <c r="X25" s="25"/>
     </row>
-    <row r="26" ht="32.05" customHeight="1">
-      <c r="A26" t="s" s="21">
+    <row r="26" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="21" t="s">
         <v>164</v>
       </c>
       <c r="B26" s="22">
@@ -5612,13 +5889,13 @@
       <c r="C26" s="23">
         <v>2022</v>
       </c>
-      <c r="D26" t="s" s="24">
+      <c r="D26" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="E26" t="s" s="24">
+      <c r="E26" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F26" t="s" s="24">
+      <c r="F26" s="24" t="s">
         <v>167</v>
       </c>
       <c r="G26" s="23">
@@ -5627,39 +5904,39 @@
       <c r="H26" s="23">
         <v>2021</v>
       </c>
-      <c r="I26" t="s" s="24">
+      <c r="I26" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="J26" t="s" s="24">
+      <c r="J26" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="19"/>
       <c r="M26" s="19"/>
       <c r="N26" s="25"/>
-      <c r="O26" t="s" s="26">
+      <c r="O26" s="26" t="s">
         <v>169</v>
       </c>
       <c r="P26" s="25"/>
       <c r="Q26" s="19"/>
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
-      <c r="T26" t="s" s="26">
+      <c r="T26" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="U26" t="s" s="26">
+      <c r="U26" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="V26" t="s" s="26">
+      <c r="V26" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="W26" t="s" s="26">
+      <c r="W26" s="26" t="s">
         <v>173</v>
       </c>
       <c r="X26" s="25"/>
     </row>
-    <row r="27" ht="32.35" customHeight="1">
-      <c r="A27" t="s" s="30">
+    <row r="27" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="30" t="s">
         <v>174</v>
       </c>
       <c r="B27" s="31">
@@ -5668,50 +5945,50 @@
       <c r="C27" s="15">
         <v>2023</v>
       </c>
-      <c r="D27" t="s" s="17">
+      <c r="D27" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="E27" t="s" s="17">
+      <c r="E27" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F27" t="s" s="17">
+      <c r="F27" s="17" t="s">
         <v>176</v>
       </c>
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
-      <c r="I27" t="s" s="17">
+      <c r="I27" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="J27" t="s" s="17">
+      <c r="J27" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
       <c r="M27" s="16"/>
-      <c r="N27" t="s" s="20">
+      <c r="N27" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="O27" t="s" s="20">
+      <c r="O27" s="20" t="s">
         <v>179</v>
       </c>
       <c r="P27" s="18"/>
       <c r="Q27" s="16"/>
       <c r="R27" s="16"/>
       <c r="S27" s="16"/>
-      <c r="T27" t="s" s="20">
+      <c r="T27" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="U27" t="s" s="20">
+      <c r="U27" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="V27" t="s" s="20">
+      <c r="V27" s="20" t="s">
         <v>182</v>
       </c>
       <c r="W27" s="18"/>
       <c r="X27" s="18"/>
     </row>
-    <row r="28" ht="20.05" customHeight="1">
-      <c r="A28" t="s" s="21">
+    <row r="28" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="21" t="s">
         <v>183</v>
       </c>
       <c r="B28" s="22">
@@ -5720,13 +5997,13 @@
       <c r="C28" s="23">
         <v>2023</v>
       </c>
-      <c r="D28" t="s" s="24">
+      <c r="D28" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="E28" t="s" s="24">
+      <c r="E28" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F28" t="s" s="24">
+      <c r="F28" s="24" t="s">
         <v>136</v>
       </c>
       <c r="G28" s="23">
@@ -5735,35 +6012,35 @@
       <c r="H28" s="23">
         <v>2019</v>
       </c>
-      <c r="I28" t="s" s="24">
+      <c r="I28" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="J28" t="s" s="24">
+      <c r="J28" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="19"/>
       <c r="M28" s="19"/>
       <c r="N28" s="25"/>
-      <c r="O28" t="s" s="26">
+      <c r="O28" s="26" t="s">
         <v>186</v>
       </c>
       <c r="P28" s="25"/>
       <c r="Q28" s="19"/>
       <c r="R28" s="19"/>
       <c r="S28" s="19"/>
-      <c r="T28" t="s" s="26">
+      <c r="T28" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="U28" t="s" s="26">
+      <c r="U28" s="26" t="s">
         <v>188</v>
       </c>
       <c r="V28" s="25"/>
       <c r="W28" s="25"/>
       <c r="X28" s="25"/>
     </row>
-    <row r="29" ht="20.05" customHeight="1">
-      <c r="A29" t="s" s="21">
+    <row r="29" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="21" t="s">
         <v>189</v>
       </c>
       <c r="B29" s="22">
@@ -5773,7 +6050,7 @@
         <v>2013</v>
       </c>
       <c r="D29" s="19"/>
-      <c r="E29" t="s" s="24">
+      <c r="E29" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F29" s="19"/>
@@ -5782,25 +6059,25 @@
       </c>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
-      <c r="J29" t="s" s="24">
+      <c r="J29" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="K29" t="s" s="24">
+      <c r="K29" s="24" t="s">
         <v>190</v>
       </c>
       <c r="L29" s="19"/>
-      <c r="M29" t="s" s="24">
+      <c r="M29" s="24" t="s">
         <v>191</v>
       </c>
       <c r="N29" s="25"/>
-      <c r="O29" t="s" s="26">
+      <c r="O29" s="26" t="s">
         <v>192</v>
       </c>
       <c r="P29" s="25"/>
       <c r="Q29" s="19"/>
       <c r="R29" s="19"/>
       <c r="S29" s="19"/>
-      <c r="T29" t="s" s="26">
+      <c r="T29" s="26" t="s">
         <v>193</v>
       </c>
       <c r="U29" s="25"/>
@@ -5808,8 +6085,8 @@
       <c r="W29" s="25"/>
       <c r="X29" s="25"/>
     </row>
-    <row r="30" ht="32.35" customHeight="1">
-      <c r="A30" t="s" s="13">
+    <row r="30" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="13" t="s">
         <v>194</v>
       </c>
       <c r="B30" s="28">
@@ -5818,13 +6095,13 @@
       <c r="C30" s="15">
         <v>2024</v>
       </c>
-      <c r="D30" t="s" s="17">
+      <c r="D30" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="E30" t="s" s="17">
+      <c r="E30" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F30" t="s" s="17">
+      <c r="F30" s="17" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="15">
@@ -5833,35 +6110,35 @@
       <c r="H30" s="15">
         <v>2024</v>
       </c>
-      <c r="I30" t="s" s="17">
+      <c r="I30" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="J30" t="s" s="17">
+      <c r="J30" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
       <c r="N30" s="18"/>
-      <c r="O30" t="s" s="20">
+      <c r="O30" s="20" t="s">
         <v>192</v>
       </c>
       <c r="P30" s="18"/>
       <c r="Q30" s="16"/>
       <c r="R30" s="19"/>
       <c r="S30" s="16"/>
-      <c r="T30" t="s" s="20">
+      <c r="T30" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="U30" t="s" s="20">
+      <c r="U30" s="20" t="s">
         <v>198</v>
       </c>
       <c r="V30" s="18"/>
       <c r="W30" s="18"/>
       <c r="X30" s="18"/>
     </row>
-    <row r="31" ht="32.05" customHeight="1">
-      <c r="A31" t="s" s="21">
+    <row r="31" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="21" t="s">
         <v>199</v>
       </c>
       <c r="B31" s="22">
@@ -5870,13 +6147,13 @@
       <c r="C31" s="23">
         <v>2019</v>
       </c>
-      <c r="D31" t="s" s="24">
+      <c r="D31" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="E31" t="s" s="24">
+      <c r="E31" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F31" t="s" s="24">
+      <c r="F31" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G31" s="23">
@@ -5885,37 +6162,37 @@
       <c r="H31" s="23">
         <v>2023</v>
       </c>
-      <c r="I31" t="s" s="24">
+      <c r="I31" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="J31" t="s" s="24">
+      <c r="J31" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K31" s="19"/>
       <c r="L31" s="19"/>
       <c r="M31" s="19"/>
       <c r="N31" s="25"/>
-      <c r="O31" t="s" s="26">
+      <c r="O31" s="26" t="s">
         <v>202</v>
       </c>
       <c r="P31" s="25"/>
       <c r="Q31" s="19"/>
       <c r="R31" s="19"/>
       <c r="S31" s="19"/>
-      <c r="T31" t="s" s="26">
+      <c r="T31" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="U31" t="s" s="26">
+      <c r="U31" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="V31" t="s" s="26">
+      <c r="V31" s="26" t="s">
         <v>204</v>
       </c>
       <c r="W31" s="25"/>
       <c r="X31" s="25"/>
     </row>
-    <row r="32" ht="20.05" customHeight="1">
-      <c r="A32" t="s" s="21">
+    <row r="32" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="21" t="s">
         <v>205</v>
       </c>
       <c r="B32" s="22">
@@ -5924,10 +6201,10 @@
       <c r="C32" s="23">
         <v>2017</v>
       </c>
-      <c r="D32" t="s" s="24">
+      <c r="D32" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="E32" t="s" s="24">
+      <c r="E32" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F32" s="19"/>
@@ -5936,27 +6213,27 @@
       </c>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
-      <c r="J32" t="s" s="24">
+      <c r="J32" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="K32" t="s" s="24">
+      <c r="K32" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="L32" t="s" s="24">
+      <c r="L32" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="M32" t="s" s="24">
+      <c r="M32" s="24" t="s">
         <v>191</v>
       </c>
       <c r="N32" s="25"/>
-      <c r="O32" t="s" s="26">
+      <c r="O32" s="26" t="s">
         <v>207</v>
       </c>
       <c r="P32" s="25"/>
       <c r="Q32" s="19"/>
       <c r="R32" s="19"/>
       <c r="S32" s="19"/>
-      <c r="T32" t="s" s="26">
+      <c r="T32" s="26" t="s">
         <v>208</v>
       </c>
       <c r="U32" s="25"/>
@@ -5964,8 +6241,8 @@
       <c r="W32" s="25"/>
       <c r="X32" s="25"/>
     </row>
-    <row r="33" ht="32.35" customHeight="1">
-      <c r="A33" t="s" s="13">
+    <row r="33" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="13" t="s">
         <v>209</v>
       </c>
       <c r="B33" s="28">
@@ -5975,22 +6252,22 @@
         <v>2023</v>
       </c>
       <c r="D33" s="16"/>
-      <c r="E33" t="s" s="17">
+      <c r="E33" s="17" t="s">
         <v>53</v>
       </c>
       <c r="F33" s="16"/>
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
-      <c r="I33" t="s" s="17">
+      <c r="I33" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="J33" t="s" s="17">
+      <c r="J33" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K33" s="16"/>
       <c r="L33" s="16"/>
       <c r="M33" s="16"/>
-      <c r="N33" t="s" s="32">
+      <c r="N33" s="32" t="s">
         <v>211</v>
       </c>
       <c r="O33" s="18"/>
@@ -5998,7 +6275,7 @@
       <c r="Q33" s="16"/>
       <c r="R33" s="16"/>
       <c r="S33" s="16"/>
-      <c r="T33" t="s" s="20">
+      <c r="T33" s="20" t="s">
         <v>212</v>
       </c>
       <c r="U33" s="18"/>
@@ -6006,8 +6283,8 @@
       <c r="W33" s="18"/>
       <c r="X33" s="18"/>
     </row>
-    <row r="34" ht="44.05" customHeight="1">
-      <c r="A34" t="s" s="21">
+    <row r="34" spans="1:24" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="21" t="s">
         <v>213</v>
       </c>
       <c r="B34" s="22">
@@ -6016,13 +6293,13 @@
       <c r="C34" s="23">
         <v>2020</v>
       </c>
-      <c r="D34" t="s" s="24">
+      <c r="D34" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="E34" t="s" s="24">
+      <c r="E34" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F34" t="s" s="24">
+      <c r="F34" s="24" t="s">
         <v>215</v>
       </c>
       <c r="G34" s="23">
@@ -6031,30 +6308,30 @@
       <c r="H34" s="23">
         <v>2022</v>
       </c>
-      <c r="I34" t="s" s="24">
+      <c r="I34" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="J34" t="s" s="24">
+      <c r="J34" s="24" t="s">
         <v>217</v>
       </c>
       <c r="K34" s="19"/>
-      <c r="L34" t="s" s="24">
+      <c r="L34" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M34" s="19"/>
       <c r="N34" s="25"/>
-      <c r="O34" t="s" s="26">
+      <c r="O34" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="P34" t="s" s="26">
+      <c r="P34" s="26" t="s">
         <v>219</v>
       </c>
       <c r="Q34" s="19"/>
       <c r="R34" s="19"/>
-      <c r="S34" t="s" s="24">
+      <c r="S34" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="T34" t="s" s="26">
+      <c r="T34" s="26" t="s">
         <v>221</v>
       </c>
       <c r="U34" s="25"/>
@@ -6062,8 +6339,8 @@
       <c r="W34" s="25"/>
       <c r="X34" s="25"/>
     </row>
-    <row r="35" ht="20.05" customHeight="1">
-      <c r="A35" t="s" s="21">
+    <row r="35" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="21" t="s">
         <v>222</v>
       </c>
       <c r="B35" s="22">
@@ -6072,10 +6349,10 @@
       <c r="C35" s="23">
         <v>2004</v>
       </c>
-      <c r="D35" t="s" s="24">
+      <c r="D35" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="E35" t="s" s="24">
+      <c r="E35" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F35" s="19"/>
@@ -6086,7 +6363,7 @@
         <v>2004</v>
       </c>
       <c r="I35" s="27"/>
-      <c r="J35" t="s" s="24">
+      <c r="J35" s="24" t="s">
         <v>64</v>
       </c>
       <c r="K35" s="19"/>
@@ -6098,18 +6375,18 @@
       <c r="Q35" s="19"/>
       <c r="R35" s="19"/>
       <c r="S35" s="19"/>
-      <c r="T35" t="s" s="26">
+      <c r="T35" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="U35" t="s" s="26">
+      <c r="U35" s="26" t="s">
         <v>224</v>
       </c>
       <c r="V35" s="25"/>
       <c r="W35" s="25"/>
       <c r="X35" s="25"/>
     </row>
-    <row r="36" ht="32.35" customHeight="1">
-      <c r="A36" t="s" s="13">
+    <row r="36" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="13" t="s">
         <v>225</v>
       </c>
       <c r="B36" s="28">
@@ -6118,13 +6395,13 @@
       <c r="C36" s="15">
         <v>2022</v>
       </c>
-      <c r="D36" t="s" s="17">
+      <c r="D36" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="E36" t="s" s="17">
+      <c r="E36" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F36" t="s" s="17">
+      <c r="F36" s="17" t="s">
         <v>227</v>
       </c>
       <c r="G36" s="15">
@@ -6133,10 +6410,10 @@
       <c r="H36" s="15">
         <v>2023</v>
       </c>
-      <c r="I36" t="s" s="17">
+      <c r="I36" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="J36" t="s" s="17">
+      <c r="J36" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K36" s="16"/>
@@ -6148,20 +6425,20 @@
       <c r="Q36" s="16"/>
       <c r="R36" s="19"/>
       <c r="S36" s="16"/>
-      <c r="T36" t="s" s="20">
+      <c r="T36" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="U36" t="s" s="20">
+      <c r="U36" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="V36" t="s" s="20">
+      <c r="V36" s="20" t="s">
         <v>231</v>
       </c>
       <c r="W36" s="18"/>
       <c r="X36" s="18"/>
     </row>
-    <row r="37" ht="20.05" customHeight="1">
-      <c r="A37" t="s" s="21">
+    <row r="37" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="21" t="s">
         <v>232</v>
       </c>
       <c r="B37" s="22">
@@ -6171,10 +6448,10 @@
         <v>2000</v>
       </c>
       <c r="D37" s="19"/>
-      <c r="E37" t="s" s="24">
+      <c r="E37" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F37" t="s" s="24">
+      <c r="F37" s="24" t="s">
         <v>233</v>
       </c>
       <c r="G37" s="23">
@@ -6194,18 +6471,18 @@
       <c r="Q37" s="19"/>
       <c r="R37" s="19"/>
       <c r="S37" s="19"/>
-      <c r="T37" t="s" s="26">
+      <c r="T37" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="U37" t="s" s="26">
+      <c r="U37" s="26" t="s">
         <v>234</v>
       </c>
       <c r="V37" s="25"/>
       <c r="W37" s="25"/>
       <c r="X37" s="25"/>
     </row>
-    <row r="38" ht="32.35" customHeight="1">
-      <c r="A38" t="s" s="13">
+    <row r="38" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="13" t="s">
         <v>235</v>
       </c>
       <c r="B38" s="28">
@@ -6219,16 +6496,16 @@
       <c r="F38" s="16"/>
       <c r="G38" s="16"/>
       <c r="H38" s="16"/>
-      <c r="I38" t="s" s="17">
+      <c r="I38" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="J38" t="s" s="17">
+      <c r="J38" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K38" s="16"/>
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
-      <c r="N38" t="s" s="32">
+      <c r="N38" s="32" t="s">
         <v>236</v>
       </c>
       <c r="O38" s="18"/>
@@ -6236,7 +6513,7 @@
       <c r="Q38" s="16"/>
       <c r="R38" s="16"/>
       <c r="S38" s="16"/>
-      <c r="T38" t="s" s="20">
+      <c r="T38" s="20" t="s">
         <v>212</v>
       </c>
       <c r="U38" s="18"/>
@@ -6244,8 +6521,8 @@
       <c r="W38" s="18"/>
       <c r="X38" s="18"/>
     </row>
-    <row r="39" ht="20.35" customHeight="1">
-      <c r="A39" t="s" s="13">
+    <row r="39" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="13" t="s">
         <v>237</v>
       </c>
       <c r="B39" s="28">
@@ -6255,22 +6532,22 @@
         <v>2023</v>
       </c>
       <c r="D39" s="16"/>
-      <c r="E39" t="s" s="17">
+      <c r="E39" s="17" t="s">
         <v>53</v>
       </c>
       <c r="F39" s="16"/>
       <c r="G39" s="16"/>
       <c r="H39" s="16"/>
-      <c r="I39" t="s" s="17">
+      <c r="I39" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="J39" t="s" s="17">
+      <c r="J39" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K39" s="16"/>
       <c r="L39" s="16"/>
       <c r="M39" s="16"/>
-      <c r="N39" t="s" s="20">
+      <c r="N39" s="20" t="s">
         <v>238</v>
       </c>
       <c r="O39" s="18"/>
@@ -6278,18 +6555,18 @@
       <c r="Q39" s="16"/>
       <c r="R39" s="16"/>
       <c r="S39" s="16"/>
-      <c r="T39" t="s" s="20">
+      <c r="T39" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="U39" t="s" s="20">
+      <c r="U39" s="20" t="s">
         <v>212</v>
       </c>
       <c r="V39" s="18"/>
       <c r="W39" s="18"/>
       <c r="X39" s="18"/>
     </row>
-    <row r="40" ht="20.35" customHeight="1">
-      <c r="A40" t="s" s="30">
+    <row r="40" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="30" t="s">
         <v>240</v>
       </c>
       <c r="B40" s="31">
@@ -6298,13 +6575,13 @@
       <c r="C40" s="15">
         <v>2023</v>
       </c>
-      <c r="D40" t="s" s="17">
+      <c r="D40" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="E40" t="s" s="17">
+      <c r="E40" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="F40" t="s" s="17">
+      <c r="F40" s="17" t="s">
         <v>242</v>
       </c>
       <c r="G40" s="15">
@@ -6313,37 +6590,37 @@
       <c r="H40" s="15">
         <v>2024</v>
       </c>
-      <c r="I40" t="s" s="17">
+      <c r="I40" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="J40" t="s" s="17">
+      <c r="J40" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K40" s="16"/>
       <c r="L40" s="16"/>
       <c r="M40" s="16"/>
       <c r="N40" s="18"/>
-      <c r="O40" t="s" s="20">
+      <c r="O40" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="P40" t="s" s="20">
+      <c r="P40" s="20" t="s">
         <v>93</v>
       </c>
       <c r="Q40" s="16"/>
       <c r="R40" s="16"/>
       <c r="S40" s="16"/>
-      <c r="T40" t="s" s="20">
+      <c r="T40" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="U40" t="s" s="20">
+      <c r="U40" s="20" t="s">
         <v>245</v>
       </c>
       <c r="V40" s="18"/>
       <c r="W40" s="18"/>
       <c r="X40" s="18"/>
     </row>
-    <row r="41" ht="32.05" customHeight="1">
-      <c r="A41" t="s" s="21">
+    <row r="41" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="21" t="s">
         <v>246</v>
       </c>
       <c r="B41" s="22">
@@ -6352,13 +6629,13 @@
       <c r="C41" s="23">
         <v>2022</v>
       </c>
-      <c r="D41" t="s" s="24">
+      <c r="D41" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="E41" t="s" s="24">
+      <c r="E41" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F41" t="s" s="24">
+      <c r="F41" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G41" s="23">
@@ -6367,26 +6644,26 @@
       <c r="H41" s="23">
         <v>2023</v>
       </c>
-      <c r="I41" t="s" s="24">
+      <c r="I41" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="J41" t="s" s="24">
+      <c r="J41" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K41" s="19"/>
-      <c r="L41" t="s" s="24">
+      <c r="L41" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M41" s="19"/>
       <c r="N41" s="25"/>
-      <c r="O41" t="s" s="26">
+      <c r="O41" s="26" t="s">
         <v>249</v>
       </c>
       <c r="P41" s="25"/>
       <c r="Q41" s="19"/>
       <c r="R41" s="19"/>
       <c r="S41" s="19"/>
-      <c r="T41" t="s" s="26">
+      <c r="T41" s="26" t="s">
         <v>250</v>
       </c>
       <c r="U41" s="25"/>
@@ -6394,8 +6671,8 @@
       <c r="W41" s="25"/>
       <c r="X41" s="25"/>
     </row>
-    <row r="42" ht="20.05" customHeight="1">
-      <c r="A42" t="s" s="21">
+    <row r="42" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="21" t="s">
         <v>251</v>
       </c>
       <c r="B42" s="22">
@@ -6404,50 +6681,50 @@
       <c r="C42" s="23">
         <v>2023</v>
       </c>
-      <c r="D42" t="s" s="24">
+      <c r="D42" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="E42" t="s" s="24">
+      <c r="E42" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F42" t="s" s="24">
+      <c r="F42" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G42" s="19"/>
       <c r="H42" s="19"/>
-      <c r="I42" t="s" s="24">
+      <c r="I42" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="J42" t="s" s="24">
+      <c r="J42" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K42" s="19"/>
-      <c r="L42" t="s" s="24">
+      <c r="L42" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M42" s="19"/>
       <c r="N42" s="25"/>
-      <c r="O42" t="s" s="26">
+      <c r="O42" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="P42" t="s" s="26">
+      <c r="P42" s="26" t="s">
         <v>255</v>
       </c>
       <c r="Q42" s="19"/>
       <c r="R42" s="19"/>
       <c r="S42" s="19"/>
-      <c r="T42" t="s" s="26">
+      <c r="T42" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="U42" t="s" s="26">
+      <c r="U42" s="26" t="s">
         <v>257</v>
       </c>
       <c r="V42" s="25"/>
       <c r="W42" s="25"/>
       <c r="X42" s="25"/>
     </row>
-    <row r="43" ht="20.05" customHeight="1">
-      <c r="A43" t="s" s="21">
+    <row r="43" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="21" t="s">
         <v>258</v>
       </c>
       <c r="B43" s="22">
@@ -6457,10 +6734,10 @@
         <v>2006</v>
       </c>
       <c r="D43" s="19"/>
-      <c r="E43" t="s" s="24">
+      <c r="E43" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F43" t="s" s="24">
+      <c r="F43" s="24" t="s">
         <v>90</v>
       </c>
       <c r="G43" s="19"/>
@@ -6476,7 +6753,7 @@
       <c r="Q43" s="19"/>
       <c r="R43" s="19"/>
       <c r="S43" s="19"/>
-      <c r="T43" t="s" s="26">
+      <c r="T43" s="26" t="s">
         <v>150</v>
       </c>
       <c r="U43" s="25"/>
@@ -6484,8 +6761,8 @@
       <c r="W43" s="25"/>
       <c r="X43" s="25"/>
     </row>
-    <row r="44" ht="44.05" customHeight="1">
-      <c r="A44" t="s" s="21">
+    <row r="44" spans="1:24" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="21" t="s">
         <v>259</v>
       </c>
       <c r="B44" s="22">
@@ -6494,7 +6771,7 @@
       <c r="C44" s="23">
         <v>2024</v>
       </c>
-      <c r="D44" t="s" s="24">
+      <c r="D44" s="24" t="s">
         <v>260</v>
       </c>
       <c r="E44" s="19"/>
@@ -6512,7 +6789,7 @@
       <c r="Q44" s="19"/>
       <c r="R44" s="19"/>
       <c r="S44" s="19"/>
-      <c r="T44" t="s" s="26">
+      <c r="T44" s="26" t="s">
         <v>261</v>
       </c>
       <c r="U44" s="25"/>
@@ -6520,8 +6797,8 @@
       <c r="W44" s="25"/>
       <c r="X44" s="25"/>
     </row>
-    <row r="45" ht="32.05" customHeight="1">
-      <c r="A45" t="s" s="21">
+    <row r="45" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="21" t="s">
         <v>262</v>
       </c>
       <c r="B45" s="22">
@@ -6530,13 +6807,13 @@
       <c r="C45" s="23">
         <v>2023</v>
       </c>
-      <c r="D45" t="s" s="24">
+      <c r="D45" s="24" t="s">
         <v>263</v>
       </c>
-      <c r="E45" t="s" s="24">
+      <c r="E45" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F45" t="s" s="24">
+      <c r="F45" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G45" s="23">
@@ -6545,28 +6822,28 @@
       <c r="H45" s="23">
         <v>2015</v>
       </c>
-      <c r="I45" t="s" s="24">
+      <c r="I45" s="24" t="s">
         <v>264</v>
       </c>
-      <c r="J45" t="s" s="24">
+      <c r="J45" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K45" s="19"/>
       <c r="L45" s="19"/>
       <c r="M45" s="19"/>
       <c r="N45" s="25"/>
-      <c r="O45" t="s" s="26">
+      <c r="O45" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="P45" t="s" s="26">
+      <c r="P45" s="26" t="s">
         <v>266</v>
       </c>
       <c r="Q45" s="19"/>
       <c r="R45" s="19"/>
-      <c r="S45" t="s" s="26">
+      <c r="S45" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="T45" t="s" s="26">
+      <c r="T45" s="26" t="s">
         <v>268</v>
       </c>
       <c r="U45" s="25"/>
@@ -6574,8 +6851,8 @@
       <c r="W45" s="25"/>
       <c r="X45" s="25"/>
     </row>
-    <row r="46" ht="32.35" customHeight="1">
-      <c r="A46" t="s" s="30">
+    <row r="46" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="30" t="s">
         <v>269</v>
       </c>
       <c r="B46" s="31">
@@ -6584,13 +6861,13 @@
       <c r="C46" s="15">
         <v>2023</v>
       </c>
-      <c r="D46" t="s" s="17">
+      <c r="D46" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="E46" t="s" s="17">
+      <c r="E46" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F46" t="s" s="17">
+      <c r="F46" s="17" t="s">
         <v>271</v>
       </c>
       <c r="G46" s="15">
@@ -6599,41 +6876,41 @@
       <c r="H46" s="15">
         <v>2024</v>
       </c>
-      <c r="I46" t="s" s="17">
+      <c r="I46" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="J46" t="s" s="17">
+      <c r="J46" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K46" s="16"/>
       <c r="L46" s="16"/>
       <c r="M46" s="16"/>
-      <c r="N46" t="s" s="20">
+      <c r="N46" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="O46" t="s" s="20">
+      <c r="O46" s="20" t="s">
         <v>273</v>
       </c>
       <c r="P46" s="18"/>
       <c r="Q46" s="16"/>
       <c r="R46" s="16"/>
       <c r="S46" s="16"/>
-      <c r="T46" t="s" s="20">
+      <c r="T46" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="U46" t="s" s="20">
+      <c r="U46" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="V46" t="s" s="20">
+      <c r="V46" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="W46" t="s" s="20">
+      <c r="W46" s="20" t="s">
         <v>276</v>
       </c>
       <c r="X46" s="18"/>
     </row>
-    <row r="47" ht="32.05" customHeight="1">
-      <c r="A47" t="s" s="21">
+    <row r="47" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="21" t="s">
         <v>277</v>
       </c>
       <c r="B47" s="22">
@@ -6642,50 +6919,50 @@
       <c r="C47" s="23">
         <v>2018</v>
       </c>
-      <c r="D47" t="s" s="24">
+      <c r="D47" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="E47" t="s" s="24">
+      <c r="E47" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F47" t="s" s="24">
+      <c r="F47" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G47" s="19"/>
       <c r="H47" s="19"/>
-      <c r="I47" t="s" s="24">
+      <c r="I47" s="24" t="s">
         <v>279</v>
       </c>
-      <c r="J47" t="s" s="24">
+      <c r="J47" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K47" s="19"/>
-      <c r="L47" t="s" s="24">
+      <c r="L47" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M47" s="19"/>
       <c r="N47" s="25"/>
-      <c r="O47" t="s" s="26">
+      <c r="O47" s="26" t="s">
         <v>124</v>
       </c>
       <c r="P47" s="25"/>
       <c r="Q47" s="19"/>
       <c r="R47" s="19"/>
       <c r="S47" s="19"/>
-      <c r="T47" t="s" s="26">
+      <c r="T47" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="U47" t="s" s="26">
+      <c r="U47" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="V47" t="s" s="26">
+      <c r="V47" s="26" t="s">
         <v>282</v>
       </c>
       <c r="W47" s="25"/>
       <c r="X47" s="25"/>
     </row>
-    <row r="48" ht="20.35" customHeight="1">
-      <c r="A48" t="s" s="13">
+    <row r="48" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="13" t="s">
         <v>283</v>
       </c>
       <c r="B48" s="31">
@@ -6695,45 +6972,45 @@
         <v>2023</v>
       </c>
       <c r="D48" s="16"/>
-      <c r="E48" t="s" s="17">
+      <c r="E48" s="17" t="s">
         <v>53</v>
       </c>
       <c r="F48" s="16"/>
       <c r="G48" s="16"/>
       <c r="H48" s="16"/>
-      <c r="I48" t="s" s="17">
+      <c r="I48" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="J48" t="s" s="17">
+      <c r="J48" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K48" s="16"/>
       <c r="L48" s="16"/>
       <c r="M48" s="16"/>
-      <c r="N48" t="s" s="20">
+      <c r="N48" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="O48" t="s" s="20">
+      <c r="O48" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="P48" t="s" s="20">
+      <c r="P48" s="20" t="s">
         <v>93</v>
       </c>
       <c r="Q48" s="16"/>
       <c r="R48" s="16"/>
       <c r="S48" s="16"/>
-      <c r="T48" t="s" s="20">
+      <c r="T48" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="U48" t="s" s="20">
+      <c r="U48" s="20" t="s">
         <v>287</v>
       </c>
       <c r="V48" s="18"/>
       <c r="W48" s="18"/>
       <c r="X48" s="18"/>
     </row>
-    <row r="49" ht="56.35" customHeight="1">
-      <c r="A49" t="s" s="13">
+    <row r="49" spans="1:24" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="13" t="s">
         <v>288</v>
       </c>
       <c r="B49" s="28">
@@ -6742,13 +7019,13 @@
       <c r="C49" s="15">
         <v>2024</v>
       </c>
-      <c r="D49" t="s" s="17">
+      <c r="D49" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="E49" t="s" s="17">
+      <c r="E49" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F49" t="s" s="17">
+      <c r="F49" s="17" t="s">
         <v>36</v>
       </c>
       <c r="G49" s="15">
@@ -6757,49 +7034,49 @@
       <c r="H49" s="15">
         <v>2018</v>
       </c>
-      <c r="I49" t="s" s="17">
+      <c r="I49" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="J49" t="s" s="17">
+      <c r="J49" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="K49" t="s" s="17">
+      <c r="K49" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="L49" t="s" s="17">
+      <c r="L49" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="M49" t="s" s="17">
+      <c r="M49" s="17" t="s">
         <v>191</v>
       </c>
       <c r="N49" s="18"/>
-      <c r="O49" t="s" s="20">
+      <c r="O49" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="P49" t="s" s="20">
+      <c r="P49" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="Q49" t="s" s="17">
+      <c r="Q49" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="R49" t="s" s="24">
+      <c r="R49" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="S49" t="s" s="17">
+      <c r="S49" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="T49" t="s" s="20">
+      <c r="T49" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="U49" t="s" s="20">
+      <c r="U49" s="20" t="s">
         <v>298</v>
       </c>
       <c r="V49" s="18"/>
       <c r="W49" s="18"/>
       <c r="X49" s="18"/>
     </row>
-    <row r="50" ht="20.35" customHeight="1">
-      <c r="A50" t="s" s="13">
+    <row r="50" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="13" t="s">
         <v>299</v>
       </c>
       <c r="B50" s="28">
@@ -6808,44 +7085,44 @@
       <c r="C50" s="15">
         <v>2023</v>
       </c>
-      <c r="D50" t="s" s="17">
+      <c r="D50" s="17" t="s">
         <v>300</v>
       </c>
-      <c r="E50" t="s" s="17">
+      <c r="E50" s="17" t="s">
         <v>166</v>
       </c>
       <c r="F50" s="16"/>
       <c r="G50" s="16"/>
       <c r="H50" s="16"/>
       <c r="I50" s="16"/>
-      <c r="J50" t="s" s="17">
+      <c r="J50" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K50" s="16"/>
       <c r="L50" s="16"/>
       <c r="M50" s="16"/>
-      <c r="N50" t="s" s="20">
+      <c r="N50" s="20" t="s">
         <v>301</v>
       </c>
       <c r="O50" s="18"/>
-      <c r="P50" t="s" s="20">
+      <c r="P50" s="20" t="s">
         <v>93</v>
       </c>
       <c r="Q50" s="16"/>
       <c r="R50" s="19"/>
       <c r="S50" s="16"/>
-      <c r="T50" t="s" s="20">
+      <c r="T50" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="U50" t="s" s="20">
+      <c r="U50" s="20" t="s">
         <v>303</v>
       </c>
       <c r="V50" s="18"/>
       <c r="W50" s="18"/>
       <c r="X50" s="18"/>
     </row>
-    <row r="51" ht="20.05" customHeight="1">
-      <c r="A51" t="s" s="21">
+    <row r="51" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="21" t="s">
         <v>304</v>
       </c>
       <c r="B51" s="22">
@@ -6854,46 +7131,46 @@
       <c r="C51" s="23">
         <v>2020</v>
       </c>
-      <c r="D51" t="s" s="24">
+      <c r="D51" s="24" t="s">
         <v>305</v>
       </c>
-      <c r="E51" t="s" s="24">
+      <c r="E51" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F51" t="s" s="24">
+      <c r="F51" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G51" s="19"/>
       <c r="H51" s="19"/>
-      <c r="I51" t="s" s="24">
+      <c r="I51" s="24" t="s">
         <v>306</v>
       </c>
-      <c r="J51" t="s" s="24">
+      <c r="J51" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K51" s="19"/>
       <c r="L51" s="19"/>
       <c r="M51" s="19"/>
       <c r="N51" s="25"/>
-      <c r="O51" t="s" s="26">
+      <c r="O51" s="26" t="s">
         <v>265</v>
       </c>
       <c r="P51" s="25"/>
       <c r="Q51" s="19"/>
       <c r="R51" s="19"/>
       <c r="S51" s="19"/>
-      <c r="T51" t="s" s="26">
+      <c r="T51" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="U51" t="s" s="26">
+      <c r="U51" s="26" t="s">
         <v>308</v>
       </c>
       <c r="V51" s="25"/>
       <c r="W51" s="25"/>
       <c r="X51" s="25"/>
     </row>
-    <row r="52" ht="20.05" customHeight="1">
-      <c r="A52" t="s" s="21">
+    <row r="52" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="21" t="s">
         <v>309</v>
       </c>
       <c r="B52" s="22">
@@ -6902,13 +7179,13 @@
       <c r="C52" s="23">
         <v>2019</v>
       </c>
-      <c r="D52" t="s" s="24">
+      <c r="D52" s="24" t="s">
         <v>310</v>
       </c>
-      <c r="E52" t="s" s="24">
+      <c r="E52" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F52" t="s" s="24">
+      <c r="F52" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G52" s="19"/>
@@ -6919,14 +7196,14 @@
       <c r="L52" s="19"/>
       <c r="M52" s="19"/>
       <c r="N52" s="25"/>
-      <c r="O52" t="s" s="26">
+      <c r="O52" s="26" t="s">
         <v>311</v>
       </c>
       <c r="P52" s="25"/>
       <c r="Q52" s="19"/>
       <c r="R52" s="19"/>
       <c r="S52" s="19"/>
-      <c r="T52" t="s" s="26">
+      <c r="T52" s="26" t="s">
         <v>312</v>
       </c>
       <c r="U52" s="25"/>
@@ -6934,8 +7211,8 @@
       <c r="W52" s="25"/>
       <c r="X52" s="25"/>
     </row>
-    <row r="53" ht="32.35" customHeight="1">
-      <c r="A53" t="s" s="30">
+    <row r="53" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="30" t="s">
         <v>313</v>
       </c>
       <c r="B53" s="31">
@@ -6944,13 +7221,13 @@
       <c r="C53" s="15">
         <v>2023</v>
       </c>
-      <c r="D53" t="s" s="17">
+      <c r="D53" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="E53" t="s" s="17">
+      <c r="E53" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F53" t="s" s="17">
+      <c r="F53" s="17" t="s">
         <v>215</v>
       </c>
       <c r="G53" s="15">
@@ -6959,37 +7236,37 @@
       <c r="H53" s="15">
         <v>2024</v>
       </c>
-      <c r="I53" t="s" s="17">
+      <c r="I53" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="J53" t="s" s="17">
+      <c r="J53" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K53" s="16"/>
       <c r="L53" s="16"/>
       <c r="M53" s="16"/>
-      <c r="N53" t="s" s="20">
+      <c r="N53" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="O53" t="s" s="20">
+      <c r="O53" s="20" t="s">
         <v>265</v>
       </c>
       <c r="P53" s="18"/>
       <c r="Q53" s="16"/>
       <c r="R53" s="16"/>
       <c r="S53" s="16"/>
-      <c r="T53" t="s" s="20">
+      <c r="T53" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="U53" t="s" s="20">
+      <c r="U53" s="20" t="s">
         <v>316</v>
       </c>
       <c r="V53" s="18"/>
       <c r="W53" s="18"/>
       <c r="X53" s="18"/>
     </row>
-    <row r="54" ht="44.35" customHeight="1">
-      <c r="A54" t="s" s="13">
+    <row r="54" spans="1:24" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="13" t="s">
         <v>317</v>
       </c>
       <c r="B54" s="28">
@@ -6998,50 +7275,50 @@
       <c r="C54" s="15">
         <v>2023</v>
       </c>
-      <c r="D54" t="s" s="17">
+      <c r="D54" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="E54" t="s" s="17">
+      <c r="E54" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F54" t="s" s="17">
+      <c r="F54" s="17" t="s">
         <v>319</v>
       </c>
       <c r="G54" s="16"/>
       <c r="H54" s="16"/>
-      <c r="I54" t="s" s="17">
+      <c r="I54" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="J54" t="s" s="17">
+      <c r="J54" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K54" s="16"/>
       <c r="L54" s="16"/>
       <c r="M54" s="16"/>
-      <c r="N54" t="s" s="20">
+      <c r="N54" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="O54" t="s" s="20">
+      <c r="O54" s="20" t="s">
         <v>321</v>
       </c>
       <c r="P54" s="18"/>
       <c r="Q54" s="16"/>
       <c r="R54" s="16"/>
       <c r="S54" s="16"/>
-      <c r="T54" t="s" s="20">
+      <c r="T54" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="U54" t="s" s="20">
+      <c r="U54" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="V54" t="s" s="20">
+      <c r="V54" s="20" t="s">
         <v>324</v>
       </c>
       <c r="W54" s="18"/>
       <c r="X54" s="18"/>
     </row>
-    <row r="55" ht="44.05" customHeight="1">
-      <c r="A55" t="s" s="21">
+    <row r="55" spans="1:24" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="21" t="s">
         <v>325</v>
       </c>
       <c r="B55" s="22">
@@ -7050,33 +7327,33 @@
       <c r="C55" s="23">
         <v>2023</v>
       </c>
-      <c r="D55" t="s" s="24">
+      <c r="D55" s="24" t="s">
         <v>326</v>
       </c>
-      <c r="E55" t="s" s="24">
+      <c r="E55" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F55" t="s" s="24">
+      <c r="F55" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G55" s="19"/>
       <c r="H55" s="19"/>
       <c r="I55" s="16"/>
-      <c r="J55" t="s" s="24">
+      <c r="J55" s="24" t="s">
         <v>327</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" s="25"/>
-      <c r="O55" t="s" s="26">
+      <c r="O55" s="26" t="s">
         <v>265</v>
       </c>
       <c r="P55" s="25"/>
       <c r="Q55" s="19"/>
       <c r="R55" s="19"/>
       <c r="S55" s="19"/>
-      <c r="T55" t="s" s="24">
+      <c r="T55" s="24" t="s">
         <v>328</v>
       </c>
       <c r="U55" s="25"/>
@@ -7084,8 +7361,8 @@
       <c r="W55" s="25"/>
       <c r="X55" s="25"/>
     </row>
-    <row r="56" ht="32.05" customHeight="1">
-      <c r="A56" t="s" s="21">
+    <row r="56" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="21" t="s">
         <v>329</v>
       </c>
       <c r="B56" s="22">
@@ -7094,13 +7371,13 @@
       <c r="C56" s="23">
         <v>2019</v>
       </c>
-      <c r="D56" t="s" s="24">
+      <c r="D56" s="24" t="s">
         <v>330</v>
       </c>
-      <c r="E56" t="s" s="24">
+      <c r="E56" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F56" t="s" s="24">
+      <c r="F56" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G56" s="23">
@@ -7111,35 +7388,35 @@
       </c>
       <c r="I56" s="27"/>
       <c r="J56" s="19"/>
-      <c r="K56" t="s" s="24">
+      <c r="K56" s="24" t="s">
         <v>331</v>
       </c>
       <c r="L56" s="19"/>
-      <c r="M56" t="s" s="24">
+      <c r="M56" s="24" t="s">
         <v>60</v>
       </c>
       <c r="N56" s="25"/>
-      <c r="O56" t="s" s="26">
+      <c r="O56" s="26" t="s">
         <v>332</v>
       </c>
       <c r="P56" s="25"/>
       <c r="Q56" s="19"/>
       <c r="R56" s="19"/>
-      <c r="S56" t="s" s="24">
+      <c r="S56" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="T56" t="s" s="26">
+      <c r="T56" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="U56" t="s" s="26">
+      <c r="U56" s="26" t="s">
         <v>334</v>
       </c>
       <c r="V56" s="25"/>
       <c r="W56" s="25"/>
       <c r="X56" s="25"/>
     </row>
-    <row r="57" ht="20.35" customHeight="1">
-      <c r="A57" t="s" s="13">
+    <row r="57" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="13" t="s">
         <v>335</v>
       </c>
       <c r="B57" s="28">
@@ -7149,47 +7426,47 @@
         <v>2023</v>
       </c>
       <c r="D57" s="16"/>
-      <c r="E57" t="s" s="17">
+      <c r="E57" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F57" t="s" s="17">
+      <c r="F57" s="17" t="s">
         <v>271</v>
       </c>
       <c r="G57" s="16"/>
       <c r="H57" s="16"/>
-      <c r="I57" t="s" s="17">
+      <c r="I57" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="J57" t="s" s="17">
+      <c r="J57" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K57" s="16"/>
       <c r="L57" s="16"/>
       <c r="M57" s="16"/>
-      <c r="N57" t="s" s="20">
+      <c r="N57" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="O57" t="s" s="20">
+      <c r="O57" s="20" t="s">
         <v>338</v>
       </c>
       <c r="P57" s="18"/>
       <c r="Q57" s="16"/>
       <c r="R57" s="16"/>
       <c r="S57" s="16"/>
-      <c r="T57" t="s" s="20">
+      <c r="T57" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="U57" t="s" s="20">
+      <c r="U57" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="V57" t="s" s="20">
+      <c r="V57" s="20" t="s">
         <v>341</v>
       </c>
       <c r="W57" s="18"/>
       <c r="X57" s="18"/>
     </row>
-    <row r="58" ht="32.05" customHeight="1">
-      <c r="A58" t="s" s="21">
+    <row r="58" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="21" t="s">
         <v>342</v>
       </c>
       <c r="B58" s="22">
@@ -7198,13 +7475,13 @@
       <c r="C58" s="23">
         <v>2021</v>
       </c>
-      <c r="D58" t="s" s="24">
+      <c r="D58" s="24" t="s">
         <v>343</v>
       </c>
-      <c r="E58" t="s" s="24">
+      <c r="E58" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F58" t="s" s="24">
+      <c r="F58" s="24" t="s">
         <v>136</v>
       </c>
       <c r="G58" s="23">
@@ -7213,39 +7490,39 @@
       <c r="H58" s="23">
         <v>2016</v>
       </c>
-      <c r="I58" t="s" s="24">
+      <c r="I58" s="24" t="s">
         <v>344</v>
       </c>
-      <c r="J58" t="s" s="24">
+      <c r="J58" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K58" s="19"/>
       <c r="L58" s="19"/>
       <c r="M58" s="19"/>
       <c r="N58" s="25"/>
-      <c r="O58" t="s" s="26">
+      <c r="O58" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="P58" t="s" s="26">
+      <c r="P58" s="26" t="s">
         <v>16</v>
       </c>
       <c r="Q58" s="19"/>
       <c r="R58" s="19"/>
-      <c r="S58" t="s" s="24">
+      <c r="S58" s="24" t="s">
         <v>346</v>
       </c>
-      <c r="T58" t="s" s="24">
+      <c r="T58" s="24" t="s">
         <v>347</v>
       </c>
-      <c r="U58" t="s" s="26">
+      <c r="U58" s="26" t="s">
         <v>348</v>
       </c>
       <c r="V58" s="25"/>
       <c r="W58" s="25"/>
       <c r="X58" s="25"/>
     </row>
-    <row r="59" ht="32.05" customHeight="1">
-      <c r="A59" t="s" s="21">
+    <row r="59" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="21" t="s">
         <v>349</v>
       </c>
       <c r="B59" s="22">
@@ -7254,13 +7531,13 @@
       <c r="C59" s="23">
         <v>2023</v>
       </c>
-      <c r="D59" t="s" s="24">
+      <c r="D59" s="24" t="s">
         <v>350</v>
       </c>
-      <c r="E59" t="s" s="24">
+      <c r="E59" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F59" t="s" s="24">
+      <c r="F59" s="24" t="s">
         <v>351</v>
       </c>
       <c r="G59" s="19"/>
@@ -7271,14 +7548,14 @@
       <c r="L59" s="19"/>
       <c r="M59" s="19"/>
       <c r="N59" s="25"/>
-      <c r="O59" t="s" s="26">
+      <c r="O59" s="26" t="s">
         <v>352</v>
       </c>
       <c r="P59" s="25"/>
       <c r="Q59" s="19"/>
       <c r="R59" s="19"/>
       <c r="S59" s="25"/>
-      <c r="T59" t="s" s="26">
+      <c r="T59" s="26" t="s">
         <v>353</v>
       </c>
       <c r="U59" s="25"/>
@@ -7286,8 +7563,8 @@
       <c r="W59" s="25"/>
       <c r="X59" s="25"/>
     </row>
-    <row r="60" ht="20.05" customHeight="1">
-      <c r="A60" t="s" s="21">
+    <row r="60" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="21" t="s">
         <v>354</v>
       </c>
       <c r="B60" s="22">
@@ -7296,31 +7573,31 @@
       <c r="C60" s="23">
         <v>2006</v>
       </c>
-      <c r="D60" t="s" s="24">
+      <c r="D60" s="24" t="s">
         <v>355</v>
       </c>
-      <c r="E60" t="s" s="24">
+      <c r="E60" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
       <c r="H60" s="19"/>
       <c r="I60" s="19"/>
-      <c r="J60" t="s" s="24">
+      <c r="J60" s="24" t="s">
         <v>356</v>
       </c>
       <c r="K60" s="19"/>
       <c r="L60" s="19"/>
       <c r="M60" s="19"/>
       <c r="N60" s="25"/>
-      <c r="O60" t="s" s="26">
+      <c r="O60" s="26" t="s">
         <v>345</v>
       </c>
       <c r="P60" s="25"/>
       <c r="Q60" s="19"/>
       <c r="R60" s="19"/>
       <c r="S60" s="19"/>
-      <c r="T60" t="s" s="26">
+      <c r="T60" s="26" t="s">
         <v>357</v>
       </c>
       <c r="U60" s="25"/>
@@ -7328,8 +7605,8 @@
       <c r="W60" s="25"/>
       <c r="X60" s="25"/>
     </row>
-    <row r="61" ht="20.05" customHeight="1">
-      <c r="A61" t="s" s="21">
+    <row r="61" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="21" t="s">
         <v>358</v>
       </c>
       <c r="B61" s="22">
@@ -7338,35 +7615,35 @@
       <c r="C61" s="23">
         <v>2018</v>
       </c>
-      <c r="D61" t="s" s="24">
+      <c r="D61" s="24" t="s">
         <v>359</v>
       </c>
-      <c r="E61" t="s" s="24">
+      <c r="E61" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F61" t="s" s="24">
+      <c r="F61" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G61" s="19"/>
       <c r="H61" s="19"/>
-      <c r="I61" t="s" s="24">
+      <c r="I61" s="24" t="s">
         <v>360</v>
       </c>
-      <c r="J61" t="s" s="24">
+      <c r="J61" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K61" s="19"/>
       <c r="L61" s="19"/>
       <c r="M61" s="19"/>
       <c r="N61" s="25"/>
-      <c r="O61" t="s" s="26">
+      <c r="O61" s="26" t="s">
         <v>361</v>
       </c>
       <c r="P61" s="25"/>
       <c r="Q61" s="19"/>
       <c r="R61" s="19"/>
       <c r="S61" s="19"/>
-      <c r="T61" t="s" s="26">
+      <c r="T61" s="26" t="s">
         <v>98</v>
       </c>
       <c r="U61" s="25"/>
@@ -7374,8 +7651,8 @@
       <c r="W61" s="25"/>
       <c r="X61" s="25"/>
     </row>
-    <row r="62" ht="20.05" customHeight="1">
-      <c r="A62" t="s" s="21">
+    <row r="62" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="21" t="s">
         <v>362</v>
       </c>
       <c r="B62" s="22">
@@ -7384,13 +7661,13 @@
       <c r="C62" s="23">
         <v>2017</v>
       </c>
-      <c r="D62" t="s" s="24">
+      <c r="D62" s="24" t="s">
         <v>363</v>
       </c>
-      <c r="E62" t="s" s="24">
+      <c r="E62" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F62" t="s" s="24">
+      <c r="F62" s="24" t="s">
         <v>167</v>
       </c>
       <c r="G62" s="23">
@@ -7399,30 +7676,30 @@
       <c r="H62" s="23">
         <v>2017</v>
       </c>
-      <c r="I62" t="s" s="24">
+      <c r="I62" s="24" t="s">
         <v>364</v>
       </c>
-      <c r="J62" t="s" s="24">
+      <c r="J62" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="K62" t="s" s="24">
+      <c r="K62" s="24" t="s">
         <v>331</v>
       </c>
-      <c r="L62" t="s" s="24">
+      <c r="L62" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="M62" t="s" s="24">
+      <c r="M62" s="24" t="s">
         <v>191</v>
       </c>
       <c r="N62" s="25"/>
-      <c r="O62" t="s" s="26">
+      <c r="O62" s="26" t="s">
         <v>365</v>
       </c>
       <c r="P62" s="25"/>
       <c r="Q62" s="19"/>
       <c r="R62" s="19"/>
       <c r="S62" s="19"/>
-      <c r="T62" t="s" s="26">
+      <c r="T62" s="26" t="s">
         <v>366</v>
       </c>
       <c r="U62" s="25"/>
@@ -7430,8 +7707,8 @@
       <c r="W62" s="25"/>
       <c r="X62" s="25"/>
     </row>
-    <row r="63" ht="20.35" customHeight="1">
-      <c r="A63" t="s" s="30">
+    <row r="63" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="30" t="s">
         <v>367</v>
       </c>
       <c r="B63" s="31">
@@ -7441,22 +7718,22 @@
         <v>2023</v>
       </c>
       <c r="D63" s="16"/>
-      <c r="E63" t="s" s="17">
+      <c r="E63" s="17" t="s">
         <v>53</v>
       </c>
       <c r="F63" s="16"/>
       <c r="G63" s="16"/>
       <c r="H63" s="16"/>
-      <c r="I63" t="s" s="17">
+      <c r="I63" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="J63" t="s" s="17">
+      <c r="J63" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K63" s="16"/>
       <c r="L63" s="16"/>
       <c r="M63" s="16"/>
-      <c r="N63" t="s" s="20">
+      <c r="N63" s="20" t="s">
         <v>368</v>
       </c>
       <c r="O63" s="18"/>
@@ -7464,7 +7741,7 @@
       <c r="Q63" s="16"/>
       <c r="R63" s="16"/>
       <c r="S63" s="16"/>
-      <c r="T63" t="s" s="20">
+      <c r="T63" s="20" t="s">
         <v>155</v>
       </c>
       <c r="U63" s="18"/>
@@ -7472,8 +7749,8 @@
       <c r="W63" s="18"/>
       <c r="X63" s="18"/>
     </row>
-    <row r="64" ht="20.05" customHeight="1">
-      <c r="A64" t="s" s="21">
+    <row r="64" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="21" t="s">
         <v>369</v>
       </c>
       <c r="B64" s="22">
@@ -7482,13 +7759,13 @@
       <c r="C64" s="23">
         <v>2021</v>
       </c>
-      <c r="D64" t="s" s="24">
+      <c r="D64" s="24" t="s">
         <v>370</v>
       </c>
-      <c r="E64" t="s" s="24">
+      <c r="E64" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F64" t="s" s="24">
+      <c r="F64" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G64" s="19"/>
@@ -7499,14 +7776,14 @@
       <c r="L64" s="19"/>
       <c r="M64" s="19"/>
       <c r="N64" s="25"/>
-      <c r="O64" t="s" s="26">
+      <c r="O64" s="26" t="s">
         <v>116</v>
       </c>
       <c r="P64" s="25"/>
       <c r="Q64" s="19"/>
       <c r="R64" s="19"/>
       <c r="S64" s="19"/>
-      <c r="T64" t="s" s="26">
+      <c r="T64" s="26" t="s">
         <v>371</v>
       </c>
       <c r="U64" s="25"/>
@@ -7514,8 +7791,8 @@
       <c r="W64" s="25"/>
       <c r="X64" s="25"/>
     </row>
-    <row r="65" ht="32.35" customHeight="1">
-      <c r="A65" t="s" s="30">
+    <row r="65" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="30" t="s">
         <v>372</v>
       </c>
       <c r="B65" s="31">
@@ -7524,50 +7801,50 @@
       <c r="C65" s="15">
         <v>2023</v>
       </c>
-      <c r="D65" t="s" s="17">
+      <c r="D65" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="E65" t="s" s="17">
+      <c r="E65" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F65" t="s" s="17">
+      <c r="F65" s="17" t="s">
         <v>136</v>
       </c>
       <c r="G65" s="16"/>
       <c r="H65" s="16"/>
-      <c r="I65" t="s" s="17">
+      <c r="I65" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="J65" t="s" s="17">
+      <c r="J65" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K65" s="16"/>
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
-      <c r="N65" t="s" s="20">
+      <c r="N65" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="O65" t="s" s="20">
+      <c r="O65" s="20" t="s">
         <v>375</v>
       </c>
       <c r="P65" s="18"/>
       <c r="Q65" s="16"/>
       <c r="R65" s="16"/>
       <c r="S65" s="16"/>
-      <c r="T65" t="s" s="20">
+      <c r="T65" s="20" t="s">
         <v>376</v>
       </c>
-      <c r="U65" t="s" s="20">
+      <c r="U65" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="V65" t="s" s="20">
+      <c r="V65" s="20" t="s">
         <v>239</v>
       </c>
       <c r="W65" s="18"/>
       <c r="X65" s="18"/>
     </row>
-    <row r="66" ht="44.35" customHeight="1">
-      <c r="A66" t="s" s="13">
+    <row r="66" spans="1:24" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="13" t="s">
         <v>378</v>
       </c>
       <c r="B66" s="28">
@@ -7576,13 +7853,13 @@
       <c r="C66" s="15">
         <v>2024</v>
       </c>
-      <c r="D66" t="s" s="17">
+      <c r="D66" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="E66" t="s" s="17">
+      <c r="E66" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F66" t="s" s="17">
+      <c r="F66" s="17" t="s">
         <v>28</v>
       </c>
       <c r="G66" s="15">
@@ -7597,16 +7874,16 @@
       <c r="L66" s="16"/>
       <c r="M66" s="16"/>
       <c r="N66" s="18"/>
-      <c r="O66" t="s" s="20">
+      <c r="O66" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="P66" t="s" s="20">
+      <c r="P66" s="20" t="s">
         <v>93</v>
       </c>
       <c r="Q66" s="16"/>
       <c r="R66" s="16"/>
       <c r="S66" s="16"/>
-      <c r="T66" t="s" s="20">
+      <c r="T66" s="20" t="s">
         <v>381</v>
       </c>
       <c r="U66" s="18"/>
@@ -7614,8 +7891,8 @@
       <c r="W66" s="18"/>
       <c r="X66" s="18"/>
     </row>
-    <row r="67" ht="20.05" customHeight="1">
-      <c r="A67" t="s" s="21">
+    <row r="67" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="21" t="s">
         <v>382</v>
       </c>
       <c r="B67" s="22">
@@ -7624,25 +7901,25 @@
       <c r="C67" s="23">
         <v>2018</v>
       </c>
-      <c r="D67" t="s" s="24">
+      <c r="D67" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="E67" t="s" s="24">
+      <c r="E67" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F67" t="s" s="24">
+      <c r="F67" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G67" s="19"/>
       <c r="H67" s="19"/>
-      <c r="I67" t="s" s="24">
+      <c r="I67" s="24" t="s">
         <v>384</v>
       </c>
-      <c r="J67" t="s" s="24">
+      <c r="J67" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K67" s="19"/>
-      <c r="L67" t="s" s="24">
+      <c r="L67" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M67" s="19"/>
@@ -7652,18 +7929,18 @@
       <c r="Q67" s="19"/>
       <c r="R67" s="19"/>
       <c r="S67" s="19"/>
-      <c r="T67" t="s" s="26">
+      <c r="T67" s="26" t="s">
         <v>385</v>
       </c>
-      <c r="U67" t="s" s="26">
+      <c r="U67" s="26" t="s">
         <v>98</v>
       </c>
       <c r="V67" s="25"/>
       <c r="W67" s="25"/>
       <c r="X67" s="25"/>
     </row>
-    <row r="68" ht="20.05" customHeight="1">
-      <c r="A68" t="s" s="21">
+    <row r="68" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="21" t="s">
         <v>386</v>
       </c>
       <c r="B68" s="22">
@@ -7672,13 +7949,13 @@
       <c r="C68" s="23">
         <v>2022</v>
       </c>
-      <c r="D68" t="s" s="24">
+      <c r="D68" s="24" t="s">
         <v>387</v>
       </c>
-      <c r="E68" t="s" s="24">
+      <c r="E68" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F68" t="s" s="24">
+      <c r="F68" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G68" s="23">
@@ -7687,14 +7964,14 @@
       <c r="H68" s="23">
         <v>2021</v>
       </c>
-      <c r="I68" t="s" s="24">
+      <c r="I68" s="24" t="s">
         <v>388</v>
       </c>
-      <c r="J68" t="s" s="24">
+      <c r="J68" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K68" s="19"/>
-      <c r="L68" t="s" s="24">
+      <c r="L68" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M68" s="19"/>
@@ -7704,20 +7981,20 @@
       <c r="Q68" s="19"/>
       <c r="R68" s="19"/>
       <c r="S68" s="19"/>
-      <c r="T68" t="s" s="26">
+      <c r="T68" s="26" t="s">
         <v>389</v>
       </c>
-      <c r="U68" t="s" s="26">
+      <c r="U68" s="26" t="s">
         <v>390</v>
       </c>
-      <c r="V68" t="s" s="26">
+      <c r="V68" s="26" t="s">
         <v>391</v>
       </c>
       <c r="W68" s="25"/>
       <c r="X68" s="25"/>
     </row>
-    <row r="69" ht="32.35" customHeight="1">
-      <c r="A69" t="s" s="13">
+    <row r="69" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="13" t="s">
         <v>392</v>
       </c>
       <c r="B69" s="28">
@@ -7726,13 +8003,13 @@
       <c r="C69" s="15">
         <v>2024</v>
       </c>
-      <c r="D69" t="s" s="17">
+      <c r="D69" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="E69" t="s" s="17">
+      <c r="E69" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F69" t="s" s="17">
+      <c r="F69" s="17" t="s">
         <v>227</v>
       </c>
       <c r="G69" s="15">
@@ -7741,26 +8018,26 @@
       <c r="H69" s="15">
         <v>2024</v>
       </c>
-      <c r="I69" t="s" s="17">
+      <c r="I69" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="J69" t="s" s="24">
+      <c r="J69" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K69" s="16"/>
       <c r="L69" s="16"/>
       <c r="M69" s="16"/>
       <c r="N69" s="18"/>
-      <c r="O69" t="s" s="20">
+      <c r="O69" s="20" t="s">
         <v>393</v>
       </c>
       <c r="P69" s="18"/>
       <c r="Q69" s="16"/>
       <c r="R69" s="19"/>
-      <c r="S69" t="s" s="17">
+      <c r="S69" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="T69" t="s" s="20">
+      <c r="T69" s="20" t="s">
         <v>395</v>
       </c>
       <c r="U69" s="18"/>
@@ -7768,8 +8045,8 @@
       <c r="W69" s="18"/>
       <c r="X69" s="18"/>
     </row>
-    <row r="70" ht="32.05" customHeight="1">
-      <c r="A70" t="s" s="21">
+    <row r="70" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="21" t="s">
         <v>396</v>
       </c>
       <c r="B70" s="22">
@@ -7778,46 +8055,46 @@
       <c r="C70" s="23">
         <v>2024</v>
       </c>
-      <c r="D70" t="s" s="24">
+      <c r="D70" s="24" t="s">
         <v>397</v>
       </c>
-      <c r="E70" t="s" s="24">
+      <c r="E70" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F70" t="s" s="24">
+      <c r="F70" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G70" s="19"/>
       <c r="H70" s="19"/>
-      <c r="I70" t="s" s="24">
+      <c r="I70" s="24" t="s">
         <v>398</v>
       </c>
-      <c r="J70" t="s" s="24">
+      <c r="J70" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K70" s="19"/>
       <c r="L70" s="19"/>
       <c r="M70" s="19"/>
       <c r="N70" s="25"/>
-      <c r="O70" t="s" s="26">
+      <c r="O70" s="26" t="s">
         <v>265</v>
       </c>
       <c r="P70" s="25"/>
       <c r="Q70" s="19"/>
       <c r="R70" s="19"/>
       <c r="S70" s="25"/>
-      <c r="T70" t="s" s="26">
+      <c r="T70" s="26" t="s">
         <v>399</v>
       </c>
-      <c r="U70" t="s" s="26">
+      <c r="U70" s="26" t="s">
         <v>400</v>
       </c>
       <c r="V70" s="25"/>
       <c r="W70" s="25"/>
       <c r="X70" s="25"/>
     </row>
-    <row r="71" ht="20.05" customHeight="1">
-      <c r="A71" t="s" s="21">
+    <row r="71" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="21" t="s">
         <v>401</v>
       </c>
       <c r="B71" s="22">
@@ -7826,35 +8103,35 @@
       <c r="C71" s="23">
         <v>2021</v>
       </c>
-      <c r="D71" t="s" s="24">
+      <c r="D71" s="24" t="s">
         <v>402</v>
       </c>
-      <c r="E71" t="s" s="24">
+      <c r="E71" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F71" t="s" s="24">
+      <c r="F71" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G71" s="19"/>
       <c r="H71" s="19"/>
-      <c r="I71" t="s" s="24">
+      <c r="I71" s="24" t="s">
         <v>403</v>
       </c>
-      <c r="J71" t="s" s="24">
+      <c r="J71" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K71" s="19"/>
       <c r="L71" s="19"/>
       <c r="M71" s="19"/>
       <c r="N71" s="25"/>
-      <c r="O71" t="s" s="26">
+      <c r="O71" s="26" t="s">
         <v>404</v>
       </c>
       <c r="P71" s="25"/>
       <c r="Q71" s="19"/>
       <c r="R71" s="19"/>
       <c r="S71" s="19"/>
-      <c r="T71" t="s" s="26">
+      <c r="T71" s="26" t="s">
         <v>98</v>
       </c>
       <c r="U71" s="25"/>
@@ -7862,8 +8139,8 @@
       <c r="W71" s="25"/>
       <c r="X71" s="25"/>
     </row>
-    <row r="72" ht="32.05" customHeight="1">
-      <c r="A72" t="s" s="21">
+    <row r="72" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="21" t="s">
         <v>405</v>
       </c>
       <c r="B72" s="22">
@@ -7872,13 +8149,13 @@
       <c r="C72" s="23">
         <v>2024</v>
       </c>
-      <c r="D72" t="s" s="24">
+      <c r="D72" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="E72" t="s" s="24">
+      <c r="E72" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F72" t="s" s="24">
+      <c r="F72" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G72" s="23">
@@ -7887,41 +8164,41 @@
       <c r="H72" s="23">
         <v>2021</v>
       </c>
-      <c r="I72" t="s" s="24">
+      <c r="I72" s="24" t="s">
         <v>407</v>
       </c>
-      <c r="J72" t="s" s="24">
+      <c r="J72" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K72" s="19"/>
-      <c r="L72" t="s" s="24">
+      <c r="L72" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M72" s="19"/>
       <c r="N72" s="25"/>
-      <c r="O72" t="s" s="26">
+      <c r="O72" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="P72" t="s" s="26">
+      <c r="P72" s="26" t="s">
         <v>408</v>
       </c>
       <c r="Q72" s="19"/>
       <c r="R72" s="19"/>
-      <c r="S72" t="s" s="24">
+      <c r="S72" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="T72" t="s" s="26">
+      <c r="T72" s="26" t="s">
         <v>410</v>
       </c>
-      <c r="U72" t="s" s="26">
+      <c r="U72" s="26" t="s">
         <v>411</v>
       </c>
       <c r="V72" s="25"/>
       <c r="W72" s="25"/>
       <c r="X72" s="25"/>
     </row>
-    <row r="73" ht="32.35" customHeight="1">
-      <c r="A73" t="s" s="13">
+    <row r="73" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="13" t="s">
         <v>412</v>
       </c>
       <c r="B73" s="28">
@@ -7930,10 +8207,10 @@
       <c r="C73" s="15">
         <v>2021</v>
       </c>
-      <c r="D73" t="s" s="17">
+      <c r="D73" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="E73" t="s" s="17">
+      <c r="E73" s="17" t="s">
         <v>53</v>
       </c>
       <c r="F73" s="16"/>
@@ -7944,32 +8221,32 @@
         <v>2017</v>
       </c>
       <c r="I73" s="16"/>
-      <c r="J73" t="s" s="17">
+      <c r="J73" s="17" t="s">
         <v>414</v>
       </c>
       <c r="K73" s="16"/>
       <c r="L73" s="16"/>
       <c r="M73" s="16"/>
       <c r="N73" s="18"/>
-      <c r="O73" t="s" s="20">
+      <c r="O73" s="20" t="s">
         <v>415</v>
       </c>
       <c r="P73" s="18"/>
       <c r="Q73" s="16"/>
       <c r="R73" s="16"/>
       <c r="S73" s="16"/>
-      <c r="T73" t="s" s="20">
+      <c r="T73" s="20" t="s">
         <v>416</v>
       </c>
-      <c r="U73" t="s" s="20">
+      <c r="U73" s="20" t="s">
         <v>417</v>
       </c>
       <c r="V73" s="18"/>
       <c r="W73" s="18"/>
       <c r="X73" s="18"/>
     </row>
-    <row r="74" ht="20.05" customHeight="1">
-      <c r="A74" t="s" s="21">
+    <row r="74" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="21" t="s">
         <v>418</v>
       </c>
       <c r="B74" s="22">
@@ -7978,13 +8255,13 @@
       <c r="C74" s="23">
         <v>2020</v>
       </c>
-      <c r="D74" t="s" s="24">
+      <c r="D74" s="24" t="s">
         <v>419</v>
       </c>
-      <c r="E74" t="s" s="24">
+      <c r="E74" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F74" t="s" s="24">
+      <c r="F74" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G74" s="23">
@@ -7993,10 +8270,10 @@
       <c r="H74" s="23">
         <v>2020</v>
       </c>
-      <c r="I74" t="s" s="24">
+      <c r="I74" s="24" t="s">
         <v>420</v>
       </c>
-      <c r="J74" t="s" s="24">
+      <c r="J74" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K74" s="19"/>
@@ -8004,26 +8281,26 @@
       <c r="M74" s="19"/>
       <c r="N74" s="25"/>
       <c r="O74" s="25"/>
-      <c r="P74" t="s" s="26">
+      <c r="P74" s="26" t="s">
         <v>408</v>
       </c>
-      <c r="Q74" t="s" s="24">
+      <c r="Q74" s="24" t="s">
         <v>295</v>
       </c>
       <c r="R74" s="19"/>
       <c r="S74" s="19"/>
-      <c r="T74" t="s" s="26">
+      <c r="T74" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="U74" t="s" s="26">
+      <c r="U74" s="26" t="s">
         <v>422</v>
       </c>
       <c r="V74" s="25"/>
       <c r="W74" s="25"/>
       <c r="X74" s="25"/>
     </row>
-    <row r="75" ht="20.35" customHeight="1">
-      <c r="A75" t="s" s="30">
+    <row r="75" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="30" t="s">
         <v>423</v>
       </c>
       <c r="B75" s="31">
@@ -8033,24 +8310,24 @@
         <v>2023</v>
       </c>
       <c r="D75" s="16"/>
-      <c r="E75" t="s" s="17">
+      <c r="E75" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F75" t="s" s="17">
+      <c r="F75" s="17" t="s">
         <v>424</v>
       </c>
       <c r="G75" s="16"/>
       <c r="H75" s="16"/>
-      <c r="I75" t="s" s="17">
+      <c r="I75" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="J75" t="s" s="17">
+      <c r="J75" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K75" s="16"/>
       <c r="L75" s="16"/>
       <c r="M75" s="16"/>
-      <c r="N75" t="s" s="20">
+      <c r="N75" s="20" t="s">
         <v>426</v>
       </c>
       <c r="O75" s="18"/>
@@ -8058,18 +8335,18 @@
       <c r="Q75" s="16"/>
       <c r="R75" s="16"/>
       <c r="S75" s="16"/>
-      <c r="T75" t="s" s="20">
+      <c r="T75" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="U75" t="s" s="20">
+      <c r="U75" s="20" t="s">
         <v>427</v>
       </c>
       <c r="V75" s="18"/>
       <c r="W75" s="18"/>
       <c r="X75" s="18"/>
     </row>
-    <row r="76" ht="32.35" customHeight="1">
-      <c r="A76" t="s" s="13">
+    <row r="76" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="13" t="s">
         <v>428</v>
       </c>
       <c r="B76" s="28">
@@ -8078,21 +8355,21 @@
       <c r="C76" s="15">
         <v>2024</v>
       </c>
-      <c r="D76" t="s" s="17">
+      <c r="D76" s="17" t="s">
         <v>429</v>
       </c>
-      <c r="E76" t="s" s="17">
+      <c r="E76" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="F76" t="s" s="17">
+      <c r="F76" s="17" t="s">
         <v>430</v>
       </c>
       <c r="G76" s="16"/>
       <c r="H76" s="16"/>
-      <c r="I76" t="s" s="17">
+      <c r="I76" s="17" t="s">
         <v>431</v>
       </c>
-      <c r="J76" t="s" s="17">
+      <c r="J76" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K76" s="16"/>
@@ -8104,7 +8381,7 @@
       <c r="Q76" s="16"/>
       <c r="R76" s="19"/>
       <c r="S76" s="16"/>
-      <c r="T76" t="s" s="20">
+      <c r="T76" s="20" t="s">
         <v>432</v>
       </c>
       <c r="U76" s="18"/>
@@ -8112,8 +8389,8 @@
       <c r="W76" s="18"/>
       <c r="X76" s="18"/>
     </row>
-    <row r="77" ht="32.05" customHeight="1">
-      <c r="A77" t="s" s="21">
+    <row r="77" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="21" t="s">
         <v>433</v>
       </c>
       <c r="B77" s="22">
@@ -8122,13 +8399,13 @@
       <c r="C77" s="23">
         <v>2024</v>
       </c>
-      <c r="D77" t="s" s="24">
+      <c r="D77" s="24" t="s">
         <v>434</v>
       </c>
-      <c r="E77" t="s" s="24">
+      <c r="E77" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F77" t="s" s="24">
+      <c r="F77" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G77" s="23">
@@ -8137,35 +8414,35 @@
       <c r="H77" s="23">
         <v>2018</v>
       </c>
-      <c r="I77" t="s" s="24">
+      <c r="I77" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="J77" t="s" s="24">
+      <c r="J77" s="24" t="s">
         <v>217</v>
       </c>
       <c r="K77" s="19"/>
       <c r="L77" s="19"/>
       <c r="M77" s="19"/>
       <c r="N77" s="25"/>
-      <c r="O77" t="s" s="26">
+      <c r="O77" s="26" t="s">
         <v>265</v>
       </c>
       <c r="P77" s="25"/>
       <c r="Q77" s="19"/>
       <c r="R77" s="19"/>
       <c r="S77" s="19"/>
-      <c r="T77" t="s" s="26">
+      <c r="T77" s="26" t="s">
         <v>435</v>
       </c>
-      <c r="U77" t="s" s="26">
+      <c r="U77" s="26" t="s">
         <v>436</v>
       </c>
       <c r="V77" s="25"/>
       <c r="W77" s="25"/>
       <c r="X77" s="25"/>
     </row>
-    <row r="78" ht="32.35" customHeight="1">
-      <c r="A78" t="s" s="13">
+    <row r="78" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="13" t="s">
         <v>437</v>
       </c>
       <c r="B78" s="28">
@@ -8174,21 +8451,21 @@
       <c r="C78" s="15">
         <v>2024</v>
       </c>
-      <c r="D78" t="s" s="17">
+      <c r="D78" s="17" t="s">
         <v>438</v>
       </c>
-      <c r="E78" t="s" s="17">
+      <c r="E78" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F78" t="s" s="17">
+      <c r="F78" s="17" t="s">
         <v>167</v>
       </c>
       <c r="G78" s="16"/>
       <c r="H78" s="16"/>
-      <c r="I78" t="s" s="17">
+      <c r="I78" s="17" t="s">
         <v>439</v>
       </c>
-      <c r="J78" t="s" s="17">
+      <c r="J78" s="17" t="s">
         <v>29</v>
       </c>
       <c r="K78" s="16"/>
@@ -8200,18 +8477,18 @@
       <c r="Q78" s="16"/>
       <c r="R78" s="19"/>
       <c r="S78" s="16"/>
-      <c r="T78" t="s" s="20">
+      <c r="T78" s="20" t="s">
         <v>440</v>
       </c>
-      <c r="U78" t="s" s="20">
+      <c r="U78" s="20" t="s">
         <v>441</v>
       </c>
       <c r="V78" s="18"/>
       <c r="W78" s="18"/>
       <c r="X78" s="18"/>
     </row>
-    <row r="79" ht="32.05" customHeight="1">
-      <c r="A79" t="s" s="21">
+    <row r="79" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A79" s="21" t="s">
         <v>442</v>
       </c>
       <c r="B79" s="22">
@@ -8220,13 +8497,13 @@
       <c r="C79" s="23">
         <v>2020</v>
       </c>
-      <c r="D79" t="s" s="24">
+      <c r="D79" s="24" t="s">
         <v>443</v>
       </c>
-      <c r="E79" t="s" s="24">
+      <c r="E79" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F79" t="s" s="24">
+      <c r="F79" s="24" t="s">
         <v>167</v>
       </c>
       <c r="G79" s="23">
@@ -8235,28 +8512,28 @@
       <c r="H79" s="23">
         <v>2020</v>
       </c>
-      <c r="I79" t="s" s="24">
+      <c r="I79" s="24" t="s">
         <v>444</v>
       </c>
-      <c r="J79" t="s" s="24">
+      <c r="J79" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K79" s="19"/>
-      <c r="L79" t="s" s="24">
+      <c r="L79" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M79" s="19"/>
       <c r="N79" s="25"/>
-      <c r="O79" t="s" s="26">
+      <c r="O79" s="26" t="s">
         <v>445</v>
       </c>
-      <c r="P79" t="s" s="26">
+      <c r="P79" s="26" t="s">
         <v>255</v>
       </c>
       <c r="Q79" s="19"/>
       <c r="R79" s="19"/>
       <c r="S79" s="19"/>
-      <c r="T79" t="s" s="26">
+      <c r="T79" s="26" t="s">
         <v>446</v>
       </c>
       <c r="U79" s="25"/>
@@ -8264,8 +8541,8 @@
       <c r="W79" s="25"/>
       <c r="X79" s="25"/>
     </row>
-    <row r="80" ht="32.05" customHeight="1">
-      <c r="A80" t="s" s="21">
+    <row r="80" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="21" t="s">
         <v>447</v>
       </c>
       <c r="B80" s="22">
@@ -8274,13 +8551,13 @@
       <c r="C80" s="23">
         <v>2023</v>
       </c>
-      <c r="D80" t="s" s="24">
+      <c r="D80" s="24" t="s">
         <v>448</v>
       </c>
-      <c r="E80" t="s" s="24">
+      <c r="E80" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F80" t="s" s="24">
+      <c r="F80" s="24" t="s">
         <v>430</v>
       </c>
       <c r="G80" s="23">
@@ -8289,47 +8566,47 @@
       <c r="H80" s="23">
         <v>2023</v>
       </c>
-      <c r="I80" t="s" s="24">
+      <c r="I80" s="24" t="s">
         <v>444</v>
       </c>
-      <c r="J80" t="s" s="24">
+      <c r="J80" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="K80" t="s" s="24">
+      <c r="K80" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="L80" t="s" s="24">
+      <c r="L80" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M80" s="19"/>
       <c r="N80" s="25"/>
-      <c r="O80" t="s" s="26">
+      <c r="O80" s="26" t="s">
         <v>449</v>
       </c>
-      <c r="P80" t="s" s="26">
+      <c r="P80" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="Q80" t="s" s="24">
+      <c r="Q80" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="R80" t="s" s="24">
+      <c r="R80" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="S80" t="s" s="24">
+      <c r="S80" s="24" t="s">
         <v>450</v>
       </c>
-      <c r="T80" t="s" s="26">
+      <c r="T80" s="26" t="s">
         <v>451</v>
       </c>
-      <c r="U80" t="s" s="26">
+      <c r="U80" s="26" t="s">
         <v>452</v>
       </c>
       <c r="V80" s="25"/>
       <c r="W80" s="25"/>
       <c r="X80" s="25"/>
     </row>
-    <row r="81" ht="32.35" customHeight="1">
-      <c r="A81" t="s" s="13">
+    <row r="81" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" s="13" t="s">
         <v>453</v>
       </c>
       <c r="B81" s="28">
@@ -8338,13 +8615,13 @@
       <c r="C81" s="15">
         <v>2024</v>
       </c>
-      <c r="D81" t="s" s="17">
+      <c r="D81" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="E81" t="s" s="17">
+      <c r="E81" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F81" t="s" s="17">
+      <c r="F81" s="17" t="s">
         <v>36</v>
       </c>
       <c r="G81" s="15">
@@ -8353,13 +8630,13 @@
       <c r="H81" s="15">
         <v>2022</v>
       </c>
-      <c r="I81" t="s" s="17">
+      <c r="I81" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J81" t="s" s="17">
+      <c r="J81" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="K81" t="s" s="17">
+      <c r="K81" s="17" t="s">
         <v>455</v>
       </c>
       <c r="L81" s="16"/>
@@ -8369,21 +8646,21 @@
       <c r="P81" s="18"/>
       <c r="Q81" s="16"/>
       <c r="R81" s="19"/>
-      <c r="S81" t="s" s="17">
+      <c r="S81" s="17" t="s">
         <v>456</v>
       </c>
-      <c r="T81" t="s" s="20">
+      <c r="T81" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="U81" t="s" s="20">
+      <c r="U81" s="20" t="s">
         <v>458</v>
       </c>
       <c r="V81" s="18"/>
       <c r="W81" s="18"/>
       <c r="X81" s="18"/>
     </row>
-    <row r="82" ht="32.35" customHeight="1">
-      <c r="A82" t="s" s="13">
+    <row r="82" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" s="13" t="s">
         <v>459</v>
       </c>
       <c r="B82" s="28">
@@ -8392,13 +8669,13 @@
       <c r="C82" s="15">
         <v>2024</v>
       </c>
-      <c r="D82" t="s" s="17">
+      <c r="D82" s="17" t="s">
         <v>460</v>
       </c>
-      <c r="E82" t="s" s="17">
+      <c r="E82" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F82" t="s" s="17">
+      <c r="F82" s="17" t="s">
         <v>167</v>
       </c>
       <c r="G82" s="15">
@@ -8407,39 +8684,39 @@
       <c r="H82" s="15">
         <v>2024</v>
       </c>
-      <c r="I82" t="s" s="24">
+      <c r="I82" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="J82" t="s" s="17">
+      <c r="J82" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K82" s="16"/>
       <c r="L82" s="16"/>
       <c r="M82" s="16"/>
       <c r="N82" s="18"/>
-      <c r="O82" t="s" s="20">
+      <c r="O82" s="20" t="s">
         <v>462</v>
       </c>
       <c r="P82" s="18"/>
       <c r="Q82" s="16"/>
       <c r="R82" s="19"/>
       <c r="S82" s="16"/>
-      <c r="T82" t="s" s="20">
+      <c r="T82" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="U82" t="s" s="20">
+      <c r="U82" s="20" t="s">
         <v>464</v>
       </c>
-      <c r="V82" t="s" s="20">
+      <c r="V82" s="20" t="s">
         <v>465</v>
       </c>
-      <c r="W82" t="s" s="20">
+      <c r="W82" s="20" t="s">
         <v>466</v>
       </c>
       <c r="X82" s="18"/>
     </row>
-    <row r="83" ht="20.05" customHeight="1">
-      <c r="A83" t="s" s="21">
+    <row r="83" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="21" t="s">
         <v>467</v>
       </c>
       <c r="B83" s="22">
@@ -8448,33 +8725,33 @@
       <c r="C83" s="23">
         <v>2018</v>
       </c>
-      <c r="D83" t="s" s="24">
+      <c r="D83" s="24" t="s">
         <v>468</v>
       </c>
-      <c r="E83" t="s" s="24">
+      <c r="E83" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F83" t="s" s="24">
+      <c r="F83" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G83" s="19"/>
       <c r="H83" s="19"/>
       <c r="I83" s="19"/>
-      <c r="J83" t="s" s="24">
+      <c r="J83" s="24" t="s">
         <v>327</v>
       </c>
       <c r="K83" s="19"/>
       <c r="L83" s="19"/>
       <c r="M83" s="19"/>
       <c r="N83" s="25"/>
-      <c r="O83" t="s" s="26">
+      <c r="O83" s="26" t="s">
         <v>469</v>
       </c>
       <c r="P83" s="25"/>
       <c r="Q83" s="19"/>
       <c r="R83" s="19"/>
       <c r="S83" s="19"/>
-      <c r="T83" t="s" s="26">
+      <c r="T83" s="26" t="s">
         <v>470</v>
       </c>
       <c r="U83" s="25"/>
@@ -8482,8 +8759,8 @@
       <c r="W83" s="25"/>
       <c r="X83" s="25"/>
     </row>
-    <row r="84" ht="20.05" customHeight="1">
-      <c r="A84" t="s" s="21">
+    <row r="84" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="21" t="s">
         <v>471</v>
       </c>
       <c r="B84" s="22">
@@ -8492,21 +8769,21 @@
       <c r="C84" s="23">
         <v>2020</v>
       </c>
-      <c r="D84" t="s" s="24">
+      <c r="D84" s="24" t="s">
         <v>472</v>
       </c>
-      <c r="E84" t="s" s="24">
+      <c r="E84" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F84" t="s" s="24">
+      <c r="F84" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="19"/>
       <c r="H84" s="19"/>
-      <c r="I84" t="s" s="24">
+      <c r="I84" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="J84" t="s" s="24">
+      <c r="J84" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K84" s="19"/>
@@ -8518,7 +8795,7 @@
       <c r="Q84" s="19"/>
       <c r="R84" s="19"/>
       <c r="S84" s="19"/>
-      <c r="T84" t="s" s="26">
+      <c r="T84" s="26" t="s">
         <v>98</v>
       </c>
       <c r="U84" s="25"/>
@@ -8526,8 +8803,8 @@
       <c r="W84" s="25"/>
       <c r="X84" s="25"/>
     </row>
-    <row r="85" ht="32.35" customHeight="1">
-      <c r="A85" t="s" s="13">
+    <row r="85" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="13" t="s">
         <v>473</v>
       </c>
       <c r="B85" s="28">
@@ -8536,13 +8813,13 @@
       <c r="C85" s="15">
         <v>2024</v>
       </c>
-      <c r="D85" t="s" s="17">
+      <c r="D85" s="17" t="s">
         <v>474</v>
       </c>
-      <c r="E85" t="s" s="17">
+      <c r="E85" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="F85" t="s" s="17">
+      <c r="F85" s="17" t="s">
         <v>475</v>
       </c>
       <c r="G85" s="15">
@@ -8551,10 +8828,10 @@
       <c r="H85" s="15">
         <v>2023</v>
       </c>
-      <c r="I85" t="s" s="17">
+      <c r="I85" s="17" t="s">
         <v>476</v>
       </c>
-      <c r="J85" t="s" s="17">
+      <c r="J85" s="17" t="s">
         <v>29</v>
       </c>
       <c r="K85" s="16"/>
@@ -8566,7 +8843,7 @@
       <c r="Q85" s="16"/>
       <c r="R85" s="19"/>
       <c r="S85" s="16"/>
-      <c r="T85" t="s" s="20">
+      <c r="T85" s="20" t="s">
         <v>440</v>
       </c>
       <c r="U85" s="18"/>
@@ -8574,8 +8851,8 @@
       <c r="W85" s="18"/>
       <c r="X85" s="18"/>
     </row>
-    <row r="86" ht="20.05" customHeight="1">
-      <c r="A86" t="s" s="21">
+    <row r="86" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="21" t="s">
         <v>477</v>
       </c>
       <c r="B86" s="22">
@@ -8585,7 +8862,7 @@
         <v>1993</v>
       </c>
       <c r="D86" s="19"/>
-      <c r="E86" t="s" s="24">
+      <c r="E86" s="24" t="s">
         <v>53</v>
       </c>
       <c r="F86" s="19"/>
@@ -8595,10 +8872,10 @@
       <c r="H86" s="23">
         <v>2013</v>
       </c>
-      <c r="I86" t="s" s="24">
+      <c r="I86" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="J86" t="s" s="24">
+      <c r="J86" s="24" t="s">
         <v>59</v>
       </c>
       <c r="K86" s="19"/>
@@ -8610,7 +8887,7 @@
       <c r="Q86" s="19"/>
       <c r="R86" s="19"/>
       <c r="S86" s="19"/>
-      <c r="T86" t="s" s="26">
+      <c r="T86" s="26" t="s">
         <v>478</v>
       </c>
       <c r="U86" s="25"/>
@@ -8618,8 +8895,8 @@
       <c r="W86" s="25"/>
       <c r="X86" s="25"/>
     </row>
-    <row r="87" ht="32.05" customHeight="1">
-      <c r="A87" t="s" s="21">
+    <row r="87" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="21" t="s">
         <v>479</v>
       </c>
       <c r="B87" s="22">
@@ -8628,13 +8905,13 @@
       <c r="C87" s="23">
         <v>2023</v>
       </c>
-      <c r="D87" t="s" s="24">
+      <c r="D87" s="24" t="s">
         <v>480</v>
       </c>
-      <c r="E87" t="s" s="24">
+      <c r="E87" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F87" t="s" s="24">
+      <c r="F87" s="24" t="s">
         <v>430</v>
       </c>
       <c r="G87" s="23">
@@ -8643,24 +8920,24 @@
       <c r="H87" s="23">
         <v>2021</v>
       </c>
-      <c r="I87" t="s" s="24">
+      <c r="I87" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="J87" t="s" s="24">
+      <c r="J87" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K87" s="19"/>
       <c r="L87" s="19"/>
       <c r="M87" s="19"/>
       <c r="N87" s="25"/>
-      <c r="O87" t="s" s="26">
+      <c r="O87" s="26" t="s">
         <v>481</v>
       </c>
       <c r="P87" s="25"/>
       <c r="Q87" s="19"/>
       <c r="R87" s="19"/>
       <c r="S87" s="19"/>
-      <c r="T87" t="s" s="26">
+      <c r="T87" s="26" t="s">
         <v>482</v>
       </c>
       <c r="U87" s="25"/>
@@ -8668,8 +8945,8 @@
       <c r="W87" s="25"/>
       <c r="X87" s="25"/>
     </row>
-    <row r="88" ht="20.05" customHeight="1">
-      <c r="A88" t="s" s="21">
+    <row r="88" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A88" s="21" t="s">
         <v>483</v>
       </c>
       <c r="B88" s="22">
@@ -8678,13 +8955,13 @@
       <c r="C88" s="23">
         <v>2002</v>
       </c>
-      <c r="D88" t="s" s="24">
+      <c r="D88" s="24" t="s">
         <v>484</v>
       </c>
-      <c r="E88" t="s" s="24">
+      <c r="E88" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F88" t="s" s="24">
+      <c r="F88" s="24" t="s">
         <v>485</v>
       </c>
       <c r="G88" s="19"/>
@@ -8695,27 +8972,27 @@
       <c r="L88" s="19"/>
       <c r="M88" s="19"/>
       <c r="N88" s="25"/>
-      <c r="O88" t="s" s="26">
+      <c r="O88" s="26" t="s">
         <v>486</v>
       </c>
       <c r="P88" s="25"/>
       <c r="Q88" s="19"/>
       <c r="R88" s="19"/>
-      <c r="S88" t="s" s="24">
+      <c r="S88" s="24" t="s">
         <v>487</v>
       </c>
-      <c r="T88" t="s" s="26">
+      <c r="T88" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="U88" t="s" s="26">
+      <c r="U88" s="26" t="s">
         <v>488</v>
       </c>
       <c r="V88" s="25"/>
       <c r="W88" s="25"/>
       <c r="X88" s="25"/>
     </row>
-    <row r="89" ht="32.05" customHeight="1">
-      <c r="A89" t="s" s="21">
+    <row r="89" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A89" s="21" t="s">
         <v>489</v>
       </c>
       <c r="B89" s="22">
@@ -8724,13 +9001,13 @@
       <c r="C89" s="23">
         <v>2019</v>
       </c>
-      <c r="D89" t="s" s="24">
+      <c r="D89" s="24" t="s">
         <v>490</v>
       </c>
-      <c r="E89" t="s" s="24">
+      <c r="E89" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F89" t="s" s="24">
+      <c r="F89" s="24" t="s">
         <v>90</v>
       </c>
       <c r="G89" s="23">
@@ -8739,34 +9016,34 @@
       <c r="H89" s="23">
         <v>2019</v>
       </c>
-      <c r="I89" t="s" s="24">
+      <c r="I89" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="J89" t="s" s="24">
+      <c r="J89" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K89" s="19"/>
-      <c r="L89" t="s" s="24">
+      <c r="L89" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M89" s="19"/>
       <c r="N89" s="25"/>
-      <c r="O89" t="s" s="26">
+      <c r="O89" s="26" t="s">
         <v>491</v>
       </c>
-      <c r="P89" t="s" s="26">
+      <c r="P89" s="26" t="s">
         <v>492</v>
       </c>
-      <c r="Q89" t="s" s="24">
+      <c r="Q89" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="R89" t="s" s="24">
+      <c r="R89" s="24" t="s">
         <v>493</v>
       </c>
-      <c r="S89" t="s" s="24">
+      <c r="S89" s="24" t="s">
         <v>494</v>
       </c>
-      <c r="T89" t="s" s="26">
+      <c r="T89" s="26" t="s">
         <v>495</v>
       </c>
       <c r="U89" s="25"/>
@@ -8774,8 +9051,8 @@
       <c r="W89" s="25"/>
       <c r="X89" s="25"/>
     </row>
-    <row r="90" ht="20.05" customHeight="1">
-      <c r="A90" t="s" s="21">
+    <row r="90" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A90" s="21" t="s">
         <v>496</v>
       </c>
       <c r="B90" s="22">
@@ -8784,13 +9061,13 @@
       <c r="C90" s="23">
         <v>2009</v>
       </c>
-      <c r="D90" t="s" s="24">
+      <c r="D90" s="24" t="s">
         <v>496</v>
       </c>
-      <c r="E90" t="s" s="24">
+      <c r="E90" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F90" t="s" s="24">
+      <c r="F90" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G90" s="23">
@@ -8798,7 +9075,7 @@
       </c>
       <c r="H90" s="19"/>
       <c r="I90" s="19"/>
-      <c r="J90" t="s" s="24">
+      <c r="J90" s="24" t="s">
         <v>497</v>
       </c>
       <c r="K90" s="19"/>
@@ -8810,7 +9087,7 @@
       <c r="Q90" s="19"/>
       <c r="R90" s="19"/>
       <c r="S90" s="19"/>
-      <c r="T90" t="s" s="26">
+      <c r="T90" s="26" t="s">
         <v>498</v>
       </c>
       <c r="U90" s="25"/>
@@ -8818,8 +9095,8 @@
       <c r="W90" s="25"/>
       <c r="X90" s="25"/>
     </row>
-    <row r="91" ht="44.05" customHeight="1">
-      <c r="A91" t="s" s="21">
+    <row r="91" spans="1:24" ht="44" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="21" t="s">
         <v>499</v>
       </c>
       <c r="B91" s="22">
@@ -8828,13 +9105,13 @@
       <c r="C91" s="23">
         <v>2022</v>
       </c>
-      <c r="D91" t="s" s="24">
+      <c r="D91" s="24" t="s">
         <v>500</v>
       </c>
-      <c r="E91" t="s" s="24">
+      <c r="E91" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F91" t="s" s="24">
+      <c r="F91" s="24" t="s">
         <v>136</v>
       </c>
       <c r="G91" s="23">
@@ -8843,41 +9120,41 @@
       <c r="H91" s="23">
         <v>2016</v>
       </c>
-      <c r="I91" t="s" s="24">
+      <c r="I91" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="J91" t="s" s="24">
+      <c r="J91" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K91" s="19"/>
       <c r="L91" s="19"/>
       <c r="M91" s="19"/>
       <c r="N91" s="25"/>
-      <c r="O91" t="s" s="26">
+      <c r="O91" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="P91" t="s" s="26">
+      <c r="P91" s="26" t="s">
         <v>501</v>
       </c>
       <c r="Q91" s="19"/>
       <c r="R91" s="19"/>
-      <c r="S91" t="s" s="24">
+      <c r="S91" s="24" t="s">
         <v>502</v>
       </c>
-      <c r="T91" t="s" s="26">
+      <c r="T91" s="26" t="s">
         <v>503</v>
       </c>
-      <c r="U91" t="s" s="26">
+      <c r="U91" s="26" t="s">
         <v>504</v>
       </c>
-      <c r="V91" t="s" s="26">
+      <c r="V91" s="26" t="s">
         <v>505</v>
       </c>
       <c r="W91" s="25"/>
       <c r="X91" s="25"/>
     </row>
-    <row r="92" ht="20.05" customHeight="1">
-      <c r="A92" t="s" s="21">
+    <row r="92" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="21" t="s">
         <v>506</v>
       </c>
       <c r="B92" s="22">
@@ -8886,13 +9163,13 @@
       <c r="C92" s="23">
         <v>2008</v>
       </c>
-      <c r="D92" t="s" s="24">
+      <c r="D92" s="24" t="s">
         <v>507</v>
       </c>
-      <c r="E92" t="s" s="24">
+      <c r="E92" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="F92" t="s" s="24">
+      <c r="F92" s="24" t="s">
         <v>430</v>
       </c>
       <c r="G92" s="23">
@@ -8907,25 +9184,25 @@
       <c r="L92" s="19"/>
       <c r="M92" s="19"/>
       <c r="N92" s="25"/>
-      <c r="O92" t="s" s="26">
+      <c r="O92" s="26" t="s">
         <v>265</v>
       </c>
       <c r="P92" s="25"/>
       <c r="Q92" s="19"/>
       <c r="R92" s="19"/>
       <c r="S92" s="19"/>
-      <c r="T92" t="s" s="26">
+      <c r="T92" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="U92" t="s" s="26">
+      <c r="U92" s="26" t="s">
         <v>508</v>
       </c>
       <c r="V92" s="25"/>
       <c r="W92" s="25"/>
       <c r="X92" s="25"/>
     </row>
-    <row r="93" ht="20.05" customHeight="1">
-      <c r="A93" t="s" s="21">
+    <row r="93" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="21" t="s">
         <v>509</v>
       </c>
       <c r="B93" s="22">
@@ -8934,13 +9211,13 @@
       <c r="C93" s="23">
         <v>2013</v>
       </c>
-      <c r="D93" t="s" s="24">
+      <c r="D93" s="24" t="s">
         <v>510</v>
       </c>
-      <c r="E93" t="s" s="24">
+      <c r="E93" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F93" t="s" s="24">
+      <c r="F93" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G93" s="23">
@@ -8949,30 +9226,30 @@
       <c r="H93" s="23">
         <v>2012</v>
       </c>
-      <c r="I93" t="s" s="24">
+      <c r="I93" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="J93" t="s" s="24">
+      <c r="J93" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="K93" t="s" s="24">
+      <c r="K93" s="24" t="s">
         <v>511</v>
       </c>
-      <c r="L93" t="s" s="24">
+      <c r="L93" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="M93" t="s" s="24">
+      <c r="M93" s="24" t="s">
         <v>511</v>
       </c>
       <c r="N93" s="25"/>
-      <c r="O93" t="s" s="26">
+      <c r="O93" s="26" t="s">
         <v>512</v>
       </c>
       <c r="P93" s="25"/>
       <c r="Q93" s="19"/>
       <c r="R93" s="19"/>
       <c r="S93" s="19"/>
-      <c r="T93" t="s" s="26">
+      <c r="T93" s="26" t="s">
         <v>513</v>
       </c>
       <c r="U93" s="25"/>
@@ -8980,8 +9257,8 @@
       <c r="W93" s="25"/>
       <c r="X93" s="25"/>
     </row>
-    <row r="94" ht="32.35" customHeight="1">
-      <c r="A94" t="s" s="13">
+    <row r="94" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="13" t="s">
         <v>514</v>
       </c>
       <c r="B94" s="28">
@@ -8990,13 +9267,13 @@
       <c r="C94" s="15">
         <v>2024</v>
       </c>
-      <c r="D94" t="s" s="17">
+      <c r="D94" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="E94" t="s" s="17">
+      <c r="E94" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="F94" t="s" s="17">
+      <c r="F94" s="17" t="s">
         <v>167</v>
       </c>
       <c r="G94" s="15">
@@ -9005,39 +9282,39 @@
       <c r="H94" s="15">
         <v>2024</v>
       </c>
-      <c r="I94" t="s" s="24">
+      <c r="I94" s="24" t="s">
         <v>516</v>
       </c>
-      <c r="J94" t="s" s="17">
+      <c r="J94" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K94" s="16"/>
       <c r="L94" s="16"/>
       <c r="M94" s="16"/>
       <c r="N94" s="18"/>
-      <c r="O94" t="s" s="20">
+      <c r="O94" s="20" t="s">
         <v>517</v>
       </c>
       <c r="P94" s="18"/>
       <c r="Q94" s="16"/>
       <c r="R94" s="19"/>
       <c r="S94" s="16"/>
-      <c r="T94" t="s" s="20">
+      <c r="T94" s="20" t="s">
         <v>518</v>
       </c>
-      <c r="U94" t="s" s="20">
+      <c r="U94" s="20" t="s">
         <v>519</v>
       </c>
-      <c r="V94" t="s" s="20">
+      <c r="V94" s="20" t="s">
         <v>520</v>
       </c>
-      <c r="W94" t="s" s="20">
+      <c r="W94" s="20" t="s">
         <v>521</v>
       </c>
       <c r="X94" s="18"/>
     </row>
-    <row r="95" ht="20.05" customHeight="1">
-      <c r="A95" t="s" s="21">
+    <row r="95" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="21" t="s">
         <v>522</v>
       </c>
       <c r="B95" s="22">
@@ -9046,13 +9323,13 @@
       <c r="C95" s="23">
         <v>2023</v>
       </c>
-      <c r="D95" t="s" s="24">
+      <c r="D95" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="E95" t="s" s="24">
+      <c r="E95" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F95" t="s" s="24">
+      <c r="F95" s="24" t="s">
         <v>227</v>
       </c>
       <c r="G95" s="23">
@@ -9061,41 +9338,41 @@
       <c r="H95" s="23">
         <v>2024</v>
       </c>
-      <c r="I95" t="s" s="24">
+      <c r="I95" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="J95" t="s" s="24">
+      <c r="J95" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="K95" t="s" s="24">
+      <c r="K95" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="L95" t="s" s="24">
+      <c r="L95" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M95" s="19"/>
       <c r="N95" s="25"/>
-      <c r="O95" t="s" s="26">
+      <c r="O95" s="26" t="s">
         <v>523</v>
       </c>
-      <c r="P95" t="s" s="26">
+      <c r="P95" s="26" t="s">
         <v>93</v>
       </c>
       <c r="Q95" s="19"/>
       <c r="R95" s="19"/>
       <c r="S95" s="19"/>
-      <c r="T95" t="s" s="26">
+      <c r="T95" s="26" t="s">
         <v>524</v>
       </c>
-      <c r="U95" t="s" s="26">
+      <c r="U95" s="26" t="s">
         <v>525</v>
       </c>
       <c r="V95" s="19"/>
       <c r="W95" s="25"/>
       <c r="X95" s="25"/>
     </row>
-    <row r="96" ht="20.05" customHeight="1">
-      <c r="A96" t="s" s="21">
+    <row r="96" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="21" t="s">
         <v>526</v>
       </c>
       <c r="B96" s="22">
@@ -9104,25 +9381,25 @@
       <c r="C96" s="23">
         <v>2015</v>
       </c>
-      <c r="D96" t="s" s="24">
+      <c r="D96" s="24" t="s">
         <v>527</v>
       </c>
-      <c r="E96" t="s" s="24">
+      <c r="E96" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F96" t="s" s="24">
+      <c r="F96" s="24" t="s">
         <v>28</v>
       </c>
       <c r="G96" s="19"/>
       <c r="H96" s="19"/>
-      <c r="I96" t="s" s="24">
+      <c r="I96" s="24" t="s">
         <v>407</v>
       </c>
-      <c r="J96" t="s" s="24">
+      <c r="J96" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K96" s="19"/>
-      <c r="L96" t="s" s="24">
+      <c r="L96" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M96" s="19"/>
@@ -9131,10 +9408,10 @@
       <c r="P96" s="25"/>
       <c r="Q96" s="19"/>
       <c r="R96" s="19"/>
-      <c r="S96" t="s" s="24">
+      <c r="S96" s="24" t="s">
         <v>528</v>
       </c>
-      <c r="T96" t="s" s="26">
+      <c r="T96" s="26" t="s">
         <v>98</v>
       </c>
       <c r="U96" s="25"/>
@@ -9142,8 +9419,8 @@
       <c r="W96" s="25"/>
       <c r="X96" s="25"/>
     </row>
-    <row r="97" ht="20.05" customHeight="1">
-      <c r="A97" t="s" s="21">
+    <row r="97" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A97" s="21" t="s">
         <v>529</v>
       </c>
       <c r="B97" s="22">
@@ -9152,13 +9429,13 @@
       <c r="C97" s="23">
         <v>2024</v>
       </c>
-      <c r="D97" t="s" s="24">
+      <c r="D97" s="24" t="s">
         <v>530</v>
       </c>
-      <c r="E97" t="s" s="24">
+      <c r="E97" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F97" t="s" s="24">
+      <c r="F97" s="24" t="s">
         <v>36</v>
       </c>
       <c r="G97" s="23">
@@ -9167,39 +9444,39 @@
       <c r="H97" s="23">
         <v>2024</v>
       </c>
-      <c r="I97" t="s" s="24">
+      <c r="I97" s="24" t="s">
         <v>531</v>
       </c>
-      <c r="J97" t="s" s="24">
+      <c r="J97" s="24" t="s">
         <v>38</v>
       </c>
       <c r="K97" s="19"/>
-      <c r="L97" t="s" s="24">
+      <c r="L97" s="24" t="s">
         <v>29</v>
       </c>
       <c r="M97" s="19"/>
       <c r="N97" s="25"/>
-      <c r="O97" t="s" s="26">
+      <c r="O97" s="26" t="s">
         <v>532</v>
       </c>
-      <c r="P97" t="s" s="26">
+      <c r="P97" s="26" t="s">
         <v>93</v>
       </c>
       <c r="Q97" s="19"/>
       <c r="R97" s="19"/>
       <c r="S97" s="19"/>
-      <c r="T97" t="s" s="26">
+      <c r="T97" s="26" t="s">
         <v>533</v>
       </c>
-      <c r="U97" t="s" s="26">
+      <c r="U97" s="26" t="s">
         <v>534</v>
       </c>
       <c r="V97" s="25"/>
       <c r="W97" s="25"/>
       <c r="X97" s="25"/>
     </row>
-    <row r="98" ht="32.35" customHeight="1">
-      <c r="A98" t="s" s="13">
+    <row r="98" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A98" s="13" t="s">
         <v>535</v>
       </c>
       <c r="B98" s="31">
@@ -9208,50 +9485,50 @@
       <c r="C98" s="15">
         <v>2023</v>
       </c>
-      <c r="D98" t="s" s="29">
+      <c r="D98" s="29" t="s">
         <v>536</v>
       </c>
-      <c r="E98" t="s" s="17">
+      <c r="E98" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F98" t="s" s="17">
+      <c r="F98" s="17" t="s">
         <v>28</v>
       </c>
       <c r="G98" s="16"/>
       <c r="H98" s="16"/>
-      <c r="I98" t="s" s="17">
+      <c r="I98" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="J98" t="s" s="17">
+      <c r="J98" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K98" s="16"/>
       <c r="L98" s="16"/>
       <c r="M98" s="16"/>
-      <c r="N98" t="s" s="20">
+      <c r="N98" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="O98" t="s" s="20">
+      <c r="O98" s="20" t="s">
         <v>537</v>
       </c>
       <c r="P98" s="18"/>
       <c r="Q98" s="16"/>
       <c r="R98" s="16"/>
       <c r="S98" s="16"/>
-      <c r="T98" t="s" s="20">
+      <c r="T98" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="U98" t="s" s="20">
+      <c r="U98" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="V98" t="s" s="20">
+      <c r="V98" s="20" t="s">
         <v>538</v>
       </c>
       <c r="W98" s="18"/>
       <c r="X98" s="18"/>
     </row>
-    <row r="99" ht="20.35" customHeight="1">
-      <c r="A99" t="s" s="13">
+    <row r="99" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A99" s="13" t="s">
         <v>539</v>
       </c>
       <c r="B99" s="22">
@@ -9260,7 +9537,7 @@
       <c r="C99" s="15">
         <v>2022</v>
       </c>
-      <c r="D99" t="s" s="17">
+      <c r="D99" s="17" t="s">
         <v>540</v>
       </c>
       <c r="E99" s="16"/>
@@ -9271,35 +9548,35 @@
       <c r="H99" s="15">
         <v>2022</v>
       </c>
-      <c r="I99" t="s" s="24">
+      <c r="I99" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="J99" t="s" s="17">
+      <c r="J99" s="17" t="s">
         <v>541</v>
       </c>
       <c r="K99" s="16"/>
       <c r="L99" s="16"/>
       <c r="M99" s="16"/>
       <c r="N99" s="18"/>
-      <c r="O99" t="s" s="20">
+      <c r="O99" s="20" t="s">
         <v>542</v>
       </c>
       <c r="P99" s="18"/>
       <c r="Q99" s="16"/>
       <c r="R99" s="19"/>
       <c r="S99" s="16"/>
-      <c r="T99" t="s" s="20">
+      <c r="T99" s="20" t="s">
         <v>543</v>
       </c>
-      <c r="U99" t="s" s="20">
+      <c r="U99" s="20" t="s">
         <v>544</v>
       </c>
       <c r="V99" s="18"/>
       <c r="W99" s="18"/>
       <c r="X99" s="18"/>
     </row>
-    <row r="100" ht="20.35" customHeight="1">
-      <c r="A100" t="s" s="13">
+    <row r="100" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A100" s="13" t="s">
         <v>545</v>
       </c>
       <c r="B100" s="28">
@@ -9309,22 +9586,22 @@
         <v>2023</v>
       </c>
       <c r="D100" s="16"/>
-      <c r="E100" t="s" s="17">
+      <c r="E100" s="17" t="s">
         <v>53</v>
       </c>
       <c r="F100" s="16"/>
       <c r="G100" s="16"/>
       <c r="H100" s="16"/>
-      <c r="I100" t="s" s="17">
+      <c r="I100" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="J100" t="s" s="17">
+      <c r="J100" s="17" t="s">
         <v>13</v>
       </c>
       <c r="K100" s="16"/>
       <c r="L100" s="16"/>
       <c r="M100" s="16"/>
-      <c r="N100" t="s" s="20">
+      <c r="N100" s="20" t="s">
         <v>546</v>
       </c>
       <c r="O100" s="18"/>
@@ -9332,31 +9609,31 @@
       <c r="Q100" s="16"/>
       <c r="R100" s="16"/>
       <c r="S100" s="16"/>
-      <c r="T100" t="s" s="20">
+      <c r="T100" s="20" t="s">
         <v>547</v>
       </c>
-      <c r="U100" t="s" s="20">
+      <c r="U100" s="20" t="s">
         <v>548</v>
       </c>
       <c r="V100" s="18"/>
       <c r="W100" s="18"/>
       <c r="X100" s="18"/>
     </row>
-    <row r="101" ht="44.35" customHeight="1">
-      <c r="A101" t="s" s="13">
+    <row r="101" spans="1:24" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A101" s="13" t="s">
         <v>549</v>
       </c>
       <c r="B101" s="28"/>
       <c r="C101" s="15">
         <v>2023</v>
       </c>
-      <c r="D101" t="s" s="17">
+      <c r="D101" s="17" t="s">
         <v>550</v>
       </c>
-      <c r="E101" t="s" s="17">
+      <c r="E101" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F101" t="s" s="17">
+      <c r="F101" s="17" t="s">
         <v>36</v>
       </c>
       <c r="G101" s="15">
@@ -9365,162 +9642,162 @@
       <c r="H101" s="15">
         <v>2023</v>
       </c>
-      <c r="I101" t="s" s="17">
+      <c r="I101" s="17" t="s">
         <v>551</v>
       </c>
-      <c r="J101" t="s" s="17">
+      <c r="J101" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K101" s="16"/>
       <c r="L101" s="16"/>
       <c r="M101" s="16"/>
       <c r="N101" s="18"/>
-      <c r="O101" t="s" s="20">
+      <c r="O101" s="20" t="s">
         <v>552</v>
       </c>
       <c r="P101" s="18"/>
       <c r="Q101" s="16"/>
       <c r="R101" s="19"/>
-      <c r="S101" t="s" s="17">
+      <c r="S101" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="T101" t="s" s="20">
+      <c r="T101" s="20" t="s">
         <v>553</v>
       </c>
-      <c r="U101" t="s" s="20">
+      <c r="U101" s="20" t="s">
         <v>554</v>
       </c>
-      <c r="V101" t="s" s="20">
+      <c r="V101" s="20" t="s">
         <v>555</v>
       </c>
-      <c r="W101" t="s" s="20">
+      <c r="W101" s="20" t="s">
         <v>556</v>
       </c>
       <c r="X101" s="18"/>
     </row>
-    <row r="102" ht="32.35" customHeight="1">
-      <c r="A102" t="s" s="13">
+    <row r="102" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A102" s="13" t="s">
         <v>557</v>
       </c>
       <c r="B102" s="28"/>
       <c r="C102" s="15">
         <v>2023</v>
       </c>
-      <c r="D102" t="s" s="17">
+      <c r="D102" s="17" t="s">
         <v>558</v>
       </c>
-      <c r="E102" t="s" s="17">
+      <c r="E102" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F102" t="s" s="17">
+      <c r="F102" s="17" t="s">
         <v>36</v>
       </c>
       <c r="G102" s="16"/>
       <c r="H102" s="15">
         <v>2023</v>
       </c>
-      <c r="I102" t="s" s="17">
+      <c r="I102" s="17" t="s">
         <v>559</v>
       </c>
-      <c r="J102" t="s" s="17">
+      <c r="J102" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K102" s="16"/>
       <c r="L102" s="16"/>
       <c r="M102" s="16"/>
       <c r="N102" s="18"/>
-      <c r="O102" t="s" s="20">
+      <c r="O102" s="20" t="s">
         <v>560</v>
       </c>
       <c r="P102" s="18"/>
       <c r="Q102" s="16"/>
       <c r="R102" s="19"/>
-      <c r="S102" t="s" s="17">
+      <c r="S102" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="T102" t="s" s="20">
+      <c r="T102" s="20" t="s">
         <v>561</v>
       </c>
-      <c r="U102" t="s" s="20">
+      <c r="U102" s="20" t="s">
         <v>562</v>
       </c>
       <c r="V102" s="18"/>
       <c r="W102" s="18"/>
       <c r="X102" s="18"/>
     </row>
-    <row r="103" ht="32.35" customHeight="1">
-      <c r="A103" t="s" s="13">
+    <row r="103" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="13" t="s">
         <v>563</v>
       </c>
       <c r="B103" s="28"/>
       <c r="C103" s="15">
         <v>2023</v>
       </c>
-      <c r="D103" t="s" s="17">
+      <c r="D103" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="E103" t="s" s="17">
+      <c r="E103" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="F103" t="s" s="17">
+      <c r="F103" s="17" t="s">
         <v>430</v>
       </c>
       <c r="G103" s="16"/>
       <c r="H103" s="15">
         <v>2023</v>
       </c>
-      <c r="I103" t="s" s="17">
+      <c r="I103" s="17" t="s">
         <v>565</v>
       </c>
-      <c r="J103" t="s" s="17">
+      <c r="J103" s="17" t="s">
         <v>38</v>
       </c>
       <c r="K103" s="16"/>
       <c r="L103" s="16"/>
       <c r="M103" s="16"/>
       <c r="N103" s="18"/>
-      <c r="O103" t="s" s="20">
+      <c r="O103" s="20" t="s">
         <v>566</v>
       </c>
       <c r="P103" s="18"/>
       <c r="Q103" s="16"/>
       <c r="R103" s="19"/>
-      <c r="S103" t="s" s="17">
+      <c r="S103" s="17" t="s">
         <v>567</v>
       </c>
-      <c r="T103" t="s" s="20">
+      <c r="T103" s="20" t="s">
         <v>562</v>
       </c>
-      <c r="U103" t="s" s="20">
+      <c r="U103" s="20" t="s">
         <v>568</v>
       </c>
       <c r="V103" s="18"/>
       <c r="W103" s="18"/>
       <c r="X103" s="18"/>
     </row>
-    <row r="104" ht="32.35" customHeight="1">
-      <c r="A104" t="s" s="13">
+    <row r="104" spans="1:24" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="13" t="s">
         <v>569</v>
       </c>
       <c r="B104" s="28"/>
       <c r="C104" s="15">
         <v>2023</v>
       </c>
-      <c r="D104" t="s" s="17">
+      <c r="D104" s="17" t="s">
         <v>570</v>
       </c>
-      <c r="E104" t="s" s="17">
+      <c r="E104" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F104" t="s" s="17">
+      <c r="F104" s="17" t="s">
         <v>36</v>
       </c>
       <c r="G104" s="16"/>
       <c r="H104" s="16"/>
-      <c r="I104" t="s" s="17">
+      <c r="I104" s="17" t="s">
         <v>571</v>
       </c>
-      <c r="J104" t="s" s="17">
+      <c r="J104" s="17" t="s">
         <v>29</v>
       </c>
       <c r="K104" s="16"/>
@@ -9532,43 +9809,76 @@
       <c r="Q104" s="16"/>
       <c r="R104" s="19"/>
       <c r="S104" s="16"/>
-      <c r="T104" t="s" s="20">
+      <c r="T104" s="20" t="s">
         <v>572</v>
       </c>
-      <c r="U104" t="s" s="20">
+      <c r="U104" s="20" t="s">
         <v>556</v>
       </c>
       <c r="V104" s="18"/>
       <c r="W104" s="18"/>
       <c r="X104" s="18"/>
     </row>
-    <row r="105" ht="20.35" customHeight="1">
-      <c r="A105" s="33"/>
-      <c r="B105" s="22"/>
-      <c r="C105" s="16"/>
-      <c r="D105" s="16"/>
-      <c r="E105" s="16"/>
-      <c r="F105" s="16"/>
-      <c r="G105" s="16"/>
-      <c r="H105" s="16"/>
-      <c r="I105" s="19"/>
-      <c r="J105" s="16"/>
-      <c r="K105" s="16"/>
-      <c r="L105" s="16"/>
+    <row r="105" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="33" t="s">
+        <v>578</v>
+      </c>
+      <c r="B105" s="34">
+        <f>17000000*12*4</f>
+        <v>816000000</v>
+      </c>
+      <c r="C105" s="16">
+        <v>2018</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="E105" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G105" s="16">
+        <v>2018</v>
+      </c>
+      <c r="H105" s="16">
+        <v>2022</v>
+      </c>
+      <c r="I105" s="35" t="s">
+        <v>403</v>
+      </c>
+      <c r="J105" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="K105" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="L105" s="16" t="s">
+        <v>75</v>
+      </c>
       <c r="M105" s="16"/>
       <c r="N105" s="18"/>
-      <c r="O105" s="18"/>
-      <c r="P105" s="18"/>
+      <c r="O105" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="P105" s="20" t="s">
+        <v>93</v>
+      </c>
       <c r="Q105" s="16"/>
       <c r="R105" s="19"/>
       <c r="S105" s="16"/>
-      <c r="T105" s="18"/>
-      <c r="U105" s="18"/>
+      <c r="T105" s="18" t="s">
+        <v>576</v>
+      </c>
+      <c r="U105" s="18" t="s">
+        <v>577</v>
+      </c>
       <c r="V105" s="18"/>
       <c r="W105" s="18"/>
       <c r="X105" s="18"/>
     </row>
-    <row r="106" ht="20.35" customHeight="1">
+    <row r="106" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="33"/>
       <c r="B106" s="22"/>
       <c r="C106" s="16"/>
@@ -9594,7 +9904,7 @@
       <c r="W106" s="18"/>
       <c r="X106" s="18"/>
     </row>
-    <row r="107" ht="20.35" customHeight="1">
+    <row r="107" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="33"/>
       <c r="B107" s="22"/>
       <c r="C107" s="16"/>
@@ -9620,7 +9930,7 @@
       <c r="W107" s="18"/>
       <c r="X107" s="18"/>
     </row>
-    <row r="108" ht="20.35" customHeight="1">
+    <row r="108" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="33"/>
       <c r="B108" s="22"/>
       <c r="C108" s="16"/>
@@ -9646,7 +9956,7 @@
       <c r="W108" s="18"/>
       <c r="X108" s="18"/>
     </row>
-    <row r="109" ht="20.35" customHeight="1">
+    <row r="109" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="33"/>
       <c r="B109" s="22"/>
       <c r="C109" s="16"/>
@@ -9672,7 +9982,7 @@
       <c r="W109" s="18"/>
       <c r="X109" s="18"/>
     </row>
-    <row r="110" ht="20.35" customHeight="1">
+    <row r="110" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="33"/>
       <c r="B110" s="22"/>
       <c r="C110" s="16"/>
@@ -9698,7 +10008,7 @@
       <c r="W110" s="18"/>
       <c r="X110" s="18"/>
     </row>
-    <row r="111" ht="20.35" customHeight="1">
+    <row r="111" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="33"/>
       <c r="B111" s="22"/>
       <c r="C111" s="16"/>
@@ -9724,7 +10034,7 @@
       <c r="W111" s="18"/>
       <c r="X111" s="18"/>
     </row>
-    <row r="112" ht="20.35" customHeight="1">
+    <row r="112" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="33"/>
       <c r="B112" s="22"/>
       <c r="C112" s="16"/>
@@ -9750,7 +10060,7 @@
       <c r="W112" s="18"/>
       <c r="X112" s="18"/>
     </row>
-    <row r="113" ht="20.35" customHeight="1">
+    <row r="113" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="33"/>
       <c r="B113" s="22"/>
       <c r="C113" s="16"/>
@@ -9776,7 +10086,7 @@
       <c r="W113" s="18"/>
       <c r="X113" s="18"/>
     </row>
-    <row r="114" ht="20.35" customHeight="1">
+    <row r="114" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="33"/>
       <c r="B114" s="22"/>
       <c r="C114" s="16"/>
@@ -9802,7 +10112,7 @@
       <c r="W114" s="18"/>
       <c r="X114" s="18"/>
     </row>
-    <row r="115" ht="20.35" customHeight="1">
+    <row r="115" spans="1:24" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="33"/>
       <c r="B115" s="22"/>
       <c r="C115" s="16"/>
@@ -9829,193 +10139,193 @@
       <c r="X115" s="18"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C13 E1:E13 G1:H12 H13 C14:C16 E14:E16 G14:H15 H16 C17:C34 E17:E34 G17:H33 H34 C35:C45 E35:E45 G35:H44 H45 C46:C59 E46:E59 G46:H58 H59 C60:C62 E60:E62 G60:H61 H62 C63:C70 E63:E70 G63:H69 H70 C71:C72 E71:E72 G71:H71 H72 C73:C79 E73:E79 G73:H78 H79:H80 C80:C86 E80:E86 G81:H85 H86 C87:C89 E87:E89 G87:H88 H89:H90 C90:C97 E90:E97 G91:H96 H97 C98:C115 E98:E115 G98:H115">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal" stopIfTrue="1">
+  <conditionalFormatting sqref="G1:H12 C1:C115 H13 G14:H15 H16 G17:H33 H34 G35:H44 H45 G46:H58 H59 G60:H61 H62 G63:H69 H70 G71:H71 H72 G73:H78 H79:H80 G81:H85 H86 G87:H88 H89:H90 G91:H96 H97 G98:H115 E1:E115">
+    <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="equal">
       <formula>"Izquierda"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal" stopIfTrue="1">
+    <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="equal">
       <formula>"Derecha"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="T3" r:id="rId1" location="" tooltip="" display="https://www.ciperchile.cl/2023/05/26/escandalo-de-cuentas-corrientes-municipales-de-nuble-golpea-en-la-region-metropolitana-contraloria-obliga-a-san-bernardo-a-terminar-contrato/"/>
-    <hyperlink ref="T4" r:id="rId2" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-valparaiso/2022/09/23/auditoria-revela-caos-municipal-en-administracion-reginato-100-mil-millones-en-perdidas.shtml"/>
-    <hyperlink ref="U4" r:id="rId3" location="" tooltip="" display="https://www.publimetro.cl/noticias/2022/09/23/100-mil-millones-las-perdidas-de-virginia-reginato-en-municipalidad-de-vina-del-mar/"/>
-    <hyperlink ref="V4" r:id="rId4" location="" tooltip="" display="https://www.fastcheck.cl/2023/05/16/misterio-sin-resolver-ocho-escandalos-de-corrupcion-municipal-pendientes-de-justicia/"/>
-    <hyperlink ref="T5" r:id="rId5" location="" tooltip="" display="https://radio.uchile.cl/2024/01/17/en-suspenso-prision-preventiva-para-cathy-barriga-tribunal-dictara-cautelar-este-jueves/"/>
-    <hyperlink ref="U5" r:id="rId6" location="" tooltip="" display="https://lavozdemaipu.cl/cathy-barriga-ultimo-informe-con-peras-y-manzanas/"/>
-    <hyperlink ref="V5" r:id="rId7" location="" tooltip="" display="https://www.tvn.cl/programas/buenos-dias-a-todos/actualidad/caso-cathy-barriga-los-41-mil-millones-de-pesos-que-no-se-saben-donde"/>
-    <hyperlink ref="T6" r:id="rId8" location="" tooltip="" display="https://es.wikipedia.org/wiki/Pacogate#Investigación_y_sentencias"/>
-    <hyperlink ref="T8" r:id="rId9" location="" tooltip="" display="https://interferencia.cl/articulos/tres-graves-casos-de-corrupcion-en-que-latam-se-ha-visto-envuelta-en-su-historia-reciente"/>
-    <hyperlink ref="T9" r:id="rId10" location="" tooltip="" display="https://es.wikipedia.org/wiki/Pinocheques"/>
-    <hyperlink ref="T10" r:id="rId11" location="" tooltip="" display="https://es.wikipedia.org/wiki/Milicogate"/>
-    <hyperlink ref="U10" r:id="rId12" location="" tooltip="" display="https://www.latercera.com/la-tercera-domingo/noticia/el-metodo-rutherford-como-fueron-cayendo-uno-a-uno-los-comandantes-en-jefe-por-el-fraude-en-el-ejercito/IVKUSHEYJBDYHMSYZ4R3KZXQE4/"/>
-    <hyperlink ref="T11" r:id="rId13" location="" tooltip="" display="https://www.chiletransparente.cl/caso-sqm/"/>
-    <hyperlink ref="T12" r:id="rId14" location="" tooltip="" display="https://www.ciperchile.cl/2018/04/02/los-negocios-ilicitos-de-juan-castro-el-ex-alcalde-de-talca-que-llego-al-senado/"/>
-    <hyperlink ref="T13" r:id="rId15" location="" tooltip="" display="https://www.meganoticias.cl/nacional/402950-malversacion-10-mil-millones-educacion-sergio-echeverria-exalcalde-san-joaquin-19-01-2023.html"/>
-    <hyperlink ref="T14" r:id="rId16" location="" tooltip="" display="https://www.elciudadano.com/politica/los-18-emblematicos-alcaldes-corruptos-de-la-derecha-historias-de-un-tsunami-delictual/06/22/"/>
-    <hyperlink ref="T15" r:id="rId17" location="" tooltip="" display="https://www.aduana.cl/megafraude-tributario-investigacion-de-aduanas-fue-clave-para/aduana/2023-12-21/174405.html"/>
-    <hyperlink ref="T16" r:id="rId18" location="" tooltip="" display="https://www.latercera.com/la-tercera-pm/noticia/estafa-fraude-y-falsificacion-el-avance-en-la-investigacion-penal-en-las-condes-que-remece-a-la-administracion-penaloza/X7ZBPJAYLRA47LINUR5COTA5HY/"/>
-    <hyperlink ref="U16" r:id="rId19" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/las-investigaciones-que-envuelven-al-municipio-de-las-condes-y-a-su-alcaldesa-daniela-penaloza/GYYWEXRFXNGJVKFJPOEWRQUB7I/"/>
-    <hyperlink ref="T17" r:id="rId20" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-metropolitana/2022/01/31/presentan-querella-contra-exalcaldesa-de-lampa-por-millonaria-deuda-de-cotizaciones.shtml"/>
-    <hyperlink ref="T18" r:id="rId21" location="" tooltip="" display="https://www.diarioconstitucional.cl/2021/04/17/detalles-del-caso-corpesca-tercer-tribunal-de-juicio-oral-en-lo-penal-de-santiago-condeno-al-exsenador-jaime-orpis-a-la-pena-unica-de-5-anos-y-un-dia-de-presidio-efectivo-en-calidad-de-autor-de-seis/"/>
-    <hyperlink ref="U18" r:id="rId22" location="" tooltip="" display="https://contracarga.cl/reportajes/caso-corpesca-explicado/"/>
-    <hyperlink ref="V18" r:id="rId23" location="" tooltip="" display="https://www.ciperchile.cl/2016/08/17/el-articulo-de-la-ley-de-pesca-que-le-ahorro-4-670-millones-a-corpesca/"/>
-    <hyperlink ref="T19" r:id="rId24" location="" tooltip="" display="https://www.latercera.com/la-tercera-sabado/noticia/cientos-de-depositos-en-efectivo-y-una-cuenta-con-2300-millones-las-pruebas-que-complican-al-tronco-torrealba/LH674LXDYVBR3J5IDIFUCMRIXE/"/>
-    <hyperlink ref="U19" r:id="rId25" location="" tooltip="" display="https://www.ciperchile.cl/2023/05/20/caso-torrealba-detalles-de-gastos-de-campana-de-rn-que-fueron-financiados-con-dineros-de-vitacura/"/>
-    <hyperlink ref="V19" r:id="rId26" location="" tooltip="" display="https://www.elmostrador.cl/noticias/pais/2023/08/08/53-dias-tras-las-rejas-rechazan-solicitud-de-raul-torrealba-y-seguira-en-prision-preventiva/"/>
-    <hyperlink ref="W19" r:id="rId27" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/vitacura-contraloria-objeta-mas-de-4500-millones-a-administracion-de-alcalde-torrealba-en-dos-anos/GK3X6GQBOVB5BFGOV4N52T3PXI/"/>
-    <hyperlink ref="T20" r:id="rId28" location="" tooltip="" display="https://interferencia.cl/articulos/contraloria-realiza-sumario-en-estacion-central-por-deficit-de-4300-millones-detectado"/>
-    <hyperlink ref="T21" r:id="rId29" location="" tooltip="" display="https://www.elrancaguino.cl/2024/01/18/hasta-35-anos-de-carcel-y-el-pago-de-2-mil-millones-de-pesos-en-multas-arriesga-el-ex-alcalde-san-fernando-luis-berwart/"/>
-    <hyperlink ref="T22" r:id="rId30" location="" tooltip="" display="https://www.diarioantofagasta.cl/investigacion/198120/caso-canastas-las-claves-del-que-podria-ser-uno-de-los-mayores-casos-de-corrupcion-en-la-historia-reciente-de-antofagasta/"/>
-    <hyperlink ref="U22" r:id="rId31" location="" tooltip="" display="https://estapasando.cl/caso-canasta-el-caso-de-corrupcion-que-sacude-antofagasta/"/>
-    <hyperlink ref="T23" r:id="rId32" location="" tooltip="" display="https://www.biobiochile.cl/noticias/2015/01/24/cinco-casos-de-corrupcion-que-mancharon-la-politica-antes-de-penta-en-los-ultimos-15-anos.shtml"/>
-    <hyperlink ref="U23" r:id="rId33" location="" tooltip="" display="https://www.df.cl/aniversario/caso-inverlink-el-escandalo-que-amenazo-la-estabilidad-del-mercado"/>
-    <hyperlink ref="T24" r:id="rId34" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
-    <hyperlink ref="U24" r:id="rId35" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2023/07/06/1100220/fundacion-el-desarrollo-de-organizaciones.html"/>
-    <hyperlink ref="T25" r:id="rId36" location="" tooltip="" display="https://www.elmostrador.cl/destacado/2023/02/06/los-2-500-millones-de-la-corporacion-municipal-de-la-florida-que-carter-no-termina-de-explicar/"/>
-    <hyperlink ref="U25" r:id="rId37" location="" tooltip="" display="https://www.biobiochile.cl/especial/bbcl-investiga/noticias/articulos/2023/01/27/detectan-diferencias-por-mas-de-4-600-millones-en-cuentas-bancarias-de-educacion-de-la-florida.shtml"/>
-    <hyperlink ref="V25" r:id="rId38" location="" tooltip="" display="https://www.adnradio.cl/2024/09/14/denuncian-a-alcalde-carter-por-asociacion-ilicita-apropiacion-indebida-y-fraude-habria-entregado-millonaria-suma-sin-licitacion/"/>
-    <hyperlink ref="T26" r:id="rId39" location="" tooltip="" display="https://www.latercera.com/earlyaccess/noticia/las-millonarias-transacciones-que-complican-al-alcalde-de-rancagua/GY4SPWLFPJDODKTTXDN7FR74B4/"/>
-    <hyperlink ref="U26" r:id="rId40" location="" tooltip="" display="https://radio.uchile.cl/2023/03/04/tras-allanamiento-a-alcalde-de-rancagua-expertos-en-transparencia-llaman-a-fortalecer-los-mecanismos-para-perseguir-la-corrupcion/"/>
-    <hyperlink ref="V26" r:id="rId41" location="" tooltip="" display="https://www.meganoticias.cl/nacional/442934-alcalde-rancagua-formalizacion-abril-delitos-corrupcion-juan-ramon-godoy-21-03-2024.html"/>
-    <hyperlink ref="W26" r:id="rId42" location="" tooltip="" display="https://www.cde.cl/cde-interpone-querella-criminal-contra-el-alcalde-de-rancagua-por-delitos-asociados-a-hechos-de-corrupcion/"/>
-    <hyperlink ref="U27" r:id="rId43" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-la-araucania/2024/01/07/imputado-en-arista-caso-convenios-gobernador-de-la-araucania-luciano-rivas-confirma-su-repostulacion.shtml"/>
-    <hyperlink ref="V27" r:id="rId44" location="" tooltip="" display="https://www.cnnchile.com/pais/caso-convenios-fundacion-la-araucania-sueldo_20240901/"/>
-    <hyperlink ref="T28" r:id="rId45" location="" tooltip="" display="https://www.cnnchile.com/pais/destitucion-alcalde-rinconada-contraloria-irregularidades_20230606/"/>
-    <hyperlink ref="U28" r:id="rId46" location="" tooltip="" display="https://munirinconada.cl/alcalde-juan-galdames-se-refiere-a-juicio-de-cuentas-que-ordena-la-restitucion-de-300-millones/"/>
-    <hyperlink ref="T29" r:id="rId47" location="" tooltip="" display="https://www.chiletransparente.cl/caso-larrainvial/"/>
-    <hyperlink ref="T30" r:id="rId48" location="" tooltip="" display="https://www.elcomunal.cl/comunales/2024/03/25/15-demandas-1-querella-y-17-solicitudes-de-arresto-por-deudas-de-1500-millones-del-municipio-de-la-higuera-sacuden-a-yerko-galleguillos/"/>
-    <hyperlink ref="U30" r:id="rId49" location="" tooltip="" display="https://www.elcomunal.cl/comunales/2024/10/04/contraloria-detecta-graves-irregularidades-en-municipalidad-de-la-higuera-y-envia-antecedentes-a-fiscalia/"/>
-    <hyperlink ref="T31" r:id="rId50" location="" tooltip="" display="https://www.ovejeronoticias.cl/2023/12/puerto-natales-ex-alcalde-udi-fernando-paredes-continua-con-reclusion-domiciliaria-total/"/>
-    <hyperlink ref="U31" r:id="rId51" location="" tooltip="" display="https://www.elciudadano.com/politica/los-18-emblematicos-alcaldes-corruptos-de-la-derecha-historias-de-un-tsunami-delictual/06/22/"/>
-    <hyperlink ref="V31" r:id="rId52" location="" tooltip="" display="https://www.elciudadano.com/justicia/trama-de-corrupcion-en-puerto-natales-envian-a-prision-al-exalcalde-jose-fernando-paredes-mansilla-por-red-de-cohecho/02/22/"/>
-    <hyperlink ref="T32" r:id="rId53" location="" tooltip="" display="https://www.chiletransparente.cl/caso-luminarias/"/>
-    <hyperlink ref="T33" r:id="rId54" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2023/08/04/fundacion-kimun-el-incumplido-contrato-por-1-200-millones/"/>
-    <hyperlink ref="T34" r:id="rId55" location="" tooltip="" display="https://www.t13.cl/noticia/politica/decretan-suspension-condicional-causa-malversacion-fondos-fundador-rd-21-12-2022"/>
-    <hyperlink ref="T35" r:id="rId56" location="" tooltip="" display="https://www.elciudadano.com/justicia/caso-riggs-corte-confirma-fraude-fiscal-de-pinochet-y-multa-millonaria-para-su-familia/10/02/"/>
-    <hyperlink ref="U35" r:id="rId57" location="" tooltip="" display="https://www.biobiochile.cl/especial/bbcl-investiga/noticias/articulos/2024/10/01/reves-para-los-pinochet-corte-confirma-declaracion-maliciosa-de-impuestos-por-operaciones-en-el-riggs.shtml"/>
-    <hyperlink ref="T36" r:id="rId58" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/judicial/denuncias-de-corrupcion/de-que-se-acusa-exactamente-a-daniel-jadue/2024-06-03/202306.html"/>
-    <hyperlink ref="U36" r:id="rId59" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/politica/municipales/jadue-sospecha-de-doble-intencionalidad-de-proveedor-que-litiga-contra/2022-02-18/092208.html"/>
-    <hyperlink ref="V36" r:id="rId60" location="" tooltip="" display="https://www.pjud.cl/prensa-y-comunicaciones/noticias-del-poder-judicial/110088"/>
-    <hyperlink ref="T37" r:id="rId61" location="" tooltip="" display="https://www.biobiochile.cl/noticias/2015/01/24/cinco-casos-de-corrupcion-que-mancharon-la-politica-antes-de-penta-en-los-ultimos-15-anos.shtml"/>
-    <hyperlink ref="U37" r:id="rId62" location="" tooltip="" display="https://es.wikipedia.org/wiki/Corrupción_en_Chile#El_caso_MOP-GATE"/>
-    <hyperlink ref="T38" r:id="rId63" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2023/08/04/fundacion-kimun-el-incumplido-contrato-por-1-200-millones/"/>
-    <hyperlink ref="T39" r:id="rId64" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/03/los-14-detenidos-en-todo-chile-por-el-caso-convenios/"/>
-    <hyperlink ref="U39" r:id="rId65" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2023/08/04/fundacion-kimun-el-incumplido-contrato-por-1-200-millones/"/>
-    <hyperlink ref="T40" r:id="rId66" location="" tooltip="" display="https://www.meganoticias.cl/amp/nacional/442953-mantencion-de-areas-verdes-alcalde-de-arica-firmo-trato-directo-por-1100-millones-con-empresa-creada-14-dias-antes.html"/>
-    <hyperlink ref="U40" r:id="rId67" location="" tooltip="" display="https://conecta2tv.cl/denuncian-ante-la-fiscalia-al-alcalde-de-arica-gerardo-espindola-por-posible-malversacion-de-caudales-publicos/"/>
-    <hyperlink ref="T41" r:id="rId68" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2023/12/10/justicia-admite-querella-contra-alcaldesa-de-rio-bueno-por-malversacion-de-caudales-y-fraude-al-fisco.shtml"/>
-    <hyperlink ref="T42" r:id="rId69" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/judicial/denuncias-de-corrupcion/detenido-el-alcalde-de-algarrobo-se-entrego-frente-a-un-motel/2023-11-23/072824.html"/>
-    <hyperlink ref="U42" r:id="rId70" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-valparaiso/2024/06/04/desfalco-algarrobo-criptomonedas-propiedaes-estados-unidos.shtml"/>
-    <hyperlink ref="T43" r:id="rId71" location="" tooltip="" display="https://www.biobiochile.cl/noticias/2015/01/24/cinco-casos-de-corrupcion-que-mancharon-la-politica-antes-de-penta-en-los-ultimos-15-anos.shtml"/>
-    <hyperlink ref="T44" r:id="rId72" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/chile/2024/03/19/milicogate-dictan-procesamiento-contra-general-y-coroneles-r-por-presunto-fraude-de-519-millones.shtml"/>
-    <hyperlink ref="T46" r:id="rId73" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
-    <hyperlink ref="U46" r:id="rId74" location="" tooltip="" display="https://radio.uchile.cl/2023/11/18/cde-se-querello-contra-fundaciones-en-la-araucania-por-fraude-al-gore/"/>
-    <hyperlink ref="V46" r:id="rId75" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2023/12/29/caso-manicure/"/>
-    <hyperlink ref="W46" r:id="rId76" location="" tooltip="" display="https://www.cnnchile.com/pais/caso-convenios-corte-suprema-confirma-desafuero-de-diputado-mauricio-ojeda_20240930/"/>
-    <hyperlink ref="T47" r:id="rId77" location="" tooltip="" display="https://www.meganoticias.cl/nacional/403342-contraloria-cifra-en-680-millones-posible-fraude-al-fisco-bajo-el-mandato-del-exintendente-guevara.html"/>
-    <hyperlink ref="U47" r:id="rId78" location="" tooltip="" display="https://cronicas.americatransparente.org/los-otros-programas-vita-41-mil-millones-transferidos-a-entidades-privadas-de-lo-barnechea/"/>
-    <hyperlink ref="V47" r:id="rId79" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/politica/contraloria-envio-a-fiscalia-caso-de-millonarios-contratos-con/2023-01-23/152629.html"/>
-    <hyperlink ref="T48" r:id="rId80" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-del-maule/2024/03/11/pdi-allano-gobernacion-del-maule-en-medio-de-investigaciones-por-traspasos-a-urbanismo-social.shtml"/>
-    <hyperlink ref="U48" r:id="rId81" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-del-maule/2024/03/12/caso-convenios-jefe-de-control-interno-del-gore-maule-declaro-por-traspasos-a-urbanismo-social.shtml"/>
-    <hyperlink ref="T49" r:id="rId82" location="" tooltip="" display="https://www.latercera.com/campuslt/noticia/luminarias-juzgado-de-garantia-de-iquique-condena-a-exconcejal-felipe-arenas-por-fraude-al-fisco-y-cohecho/OR3BBHZLARCULI7J5A22A66CSU/"/>
-    <hyperlink ref="U49" r:id="rId83" location="" tooltip="" display="https://iquiquetv.cl/2024/07/02/caso-luminarias-led-condenan-a-ex-concejal-felipe-arenas-por-cohecho-y-fraude-al-fisco/"/>
-    <hyperlink ref="T50" r:id="rId84" location="" tooltip="" display="https://www.latercera.com/earlyaccess/noticia/pintar-fachadas-turismo-creativo-y-ayuda-contra-el-suicidio-los-diversos-rubros-de-procultura-la-fundacion-con-mas-convenios-en-la-mira-de-fiscalia/PE7YFQCVMBAOTPHJPTUBEHVPUU/"/>
-    <hyperlink ref="U50" r:id="rId85" location="" tooltip="" display="https://www.ex-ante.cl/perfil-lo-que-hay-que-saber-de-alberto-larrain-sus-vinculos-politicos-y-las-indagaciones-a-la-fundacion-procultura-que-creo/"/>
-    <hyperlink ref="T51" r:id="rId86" location="" tooltip="" display="https://www.eldesconcierto.cl/reportajes/2024/01/23/municipio-se-querella-por-multa-de-500-millones-acusan-a-exalcalde-de-melipilla-por-fraude-al-fisco.html"/>
-    <hyperlink ref="U51" r:id="rId87" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/municipalidad-de-melipilla-presenta-querella-por-fraude-al-fisco-contra-el-exalcalde-ivan-campos/P6XRT2X73NAHJIEMIZWPRX6VEU/"/>
-    <hyperlink ref="T52" r:id="rId88" location="" tooltip="" display="https://www.elmostrador.cl/noticias/pais/2019/05/05/las-vueltas-de-la-vida-rn-elige-a-claudio-eguiluz-condenado-por-caso-sqm-como-su-presidente-regional-en-el-biobio/"/>
-    <hyperlink ref="T53" r:id="rId89" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
-    <hyperlink ref="U53" r:id="rId90" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-antofagasta/2024/09/03/caso-convenios-formalizan-a-carlos-contreras-por-tres-delitos-de-fraude-al-fisco.shtml"/>
-    <hyperlink ref="T54" r:id="rId91" location="" tooltip="" display="https://radionuevomundo.cl/2023/07/18/gobernador-rivas-suma-al-caso-fundacion-local-traspasos-arbitrarios-a-coihue-y-a-universidades-de-la-araucania/"/>
-    <hyperlink ref="U54" r:id="rId92" location="" tooltip="" display="https://www.elciudadano.com/actualidad/el-entramado-de-ilicitos-de-platas-que-exploto-en-el-gore-araucania-y-que-repercute-en-renovacion-nacional/12/29/"/>
-    <hyperlink ref="V54" r:id="rId93" location="" tooltip="" display="https://resumen.cl/articulos/la-derecha-de-la-araucania-en-el-caso-fundaciones-las-irregularidades-de-espacio-coigue-que-llevaron-al-ministerio-de-justicia-a-solicitar-su-cierre"/>
-    <hyperlink ref="T55" r:id="rId94" location="" tooltip="" display="https://www.elmostrador.cl/dia/2023/03/31/exsubsecretaria-martorell-declaro-como-imputada-por-corrupcion-en-caso-motorola/"/>
-    <hyperlink ref="T56" r:id="rId95" location="" tooltip="" display="https://www.chilevision.cl/noticias/nacional/golborne-paga-11-4-millones-y-logra-salida-alternativa-del-caso-penta"/>
-    <hyperlink ref="U56" r:id="rId96" location="" tooltip="" display="https://www.latercera.com/la-tercera-pm/noticia/golborne-sale-del-caso-penta-tras-pagar-114-millones/906364/"/>
-    <hyperlink ref="T57" r:id="rId97" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-del-bio-bio/2024/03/13/caso-convenios-allanan-empresa-que-facturo-356-millones-en-convenios-del-gore-bio-bio-y-bonhomia.shtml"/>
-    <hyperlink ref="U57" r:id="rId98" location="" tooltip="" display="https://resumen.cl/articulos/fundacion-contrato-con-dineros-del-gore-biobio-a-empresas-de-coordinador-de-programa-y-a-firma-donde-trabaja-su-hermano-y-su-madre-excandidata-republicana"/>
-    <hyperlink ref="V57" r:id="rId99" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/region-del-biobio/detienen-a-lider-de-empresa-en-allanamiento-por-caso-convenios-pdi/2024-03-13/123002.html"/>
-    <hyperlink ref="T58" r:id="rId100" location="" tooltip="" display="http://www.fiscaliadechile.cl/Fiscalia/sala_prensa/noticias_regional_det.do?id=22739"/>
-    <hyperlink ref="U58" r:id="rId101" location="" tooltip="" display="https://resumen.cl/articulos/exalcalde-pasara-10-anos-en-carcel-por-apropiarse-de-351-millones-de-la-municipalidad-y-de-empresa-electrica"/>
-    <hyperlink ref="T59" r:id="rId102" location="" tooltip="" display="https://www.24horas.cl/actualidad/politica/que-se-le-acusa-a-karina-oliva-emitir-boletas-falsas-defraudar-290-millones"/>
-    <hyperlink ref="T60" r:id="rId103" location="" tooltip="" display="https://www.fastcheck.cl/2021/11/18/yasna-provoste-se-robo-600-millones-de-dolares-del-ministerio-de-educacion-falso/"/>
-    <hyperlink ref="T61" r:id="rId104" location="" tooltip="" display="https://www.elciudadano.com/politica/los-18-emblematicos-alcaldes-corruptos-de-la-derecha-historias-de-un-tsunami-delictual/06/22/"/>
-    <hyperlink ref="T63" r:id="rId105" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
-    <hyperlink ref="T64" r:id="rId106" location="" tooltip="" display="https://radio.uchile.cl/2021/04/16/a-la-carcel-ex-senador-udi-jaime-orpis-es-condenado-a-prision-por-cohecho-y-fraude-al-fisco/"/>
-    <hyperlink ref="T65" r:id="rId107" location="" tooltip="" display="https://radio.uchile.cl/2023/11/28/755094/"/>
-    <hyperlink ref="U65" r:id="rId108" location="" tooltip="" display="https://elpais.com/chile/2023-08-05/caso-lenceria-la-telenovelesca-arista-de-la-trama-de-corrupcion-que-hace-temblar-la-politica-chilena.html"/>
-    <hyperlink ref="V65" r:id="rId109" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/03/los-14-detenidos-en-todo-chile-por-el-caso-convenios/"/>
-    <hyperlink ref="T66" r:id="rId110" location="" tooltip="" display="https://www.latercera.com/opinion/noticia/columna-de-daniel-matamala-cual-elefante/EOAKP2PXWJHSFDBAKRXGVVS5ZA/"/>
-    <hyperlink ref="T67" r:id="rId111" location="" tooltip="" display="https://www.ciperchile.cl/2023/05/10/caso-itelecom-detectan-66-pagos-en-efectivo-a-principal-asesor-de-german-codina-por-203-millones/"/>
-    <hyperlink ref="U67" r:id="rId112" location="" tooltip="" display="https://www.elciudadano.com/politica/los-18-emblematicos-alcaldes-corruptos-de-la-derecha-historias-de-un-tsunami-delictual/06/22/"/>
-    <hyperlink ref="T68" r:id="rId113" location="" tooltip="" display="https://eltipografo.cl/2022/08/presentan-nueva-querella-por-fraude-al-fisco-contra-ex-alcalde-de-mostazal-sergio-medel-a"/>
-    <hyperlink ref="U68" r:id="rId114" location="" tooltip="" display="https://eltipografo.cl/2023/03/deficit-de-8-mil-millones-en-el-municipio-y-querellas-por-fraude-al-fisco-enfrenta-ex-alcalde-de-mostazal"/>
-    <hyperlink ref="V68" r:id="rId115" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-ohiggins/2022/08/11/municipio-prepara-querellas-tras-millonarias-irregularidades-en-san-francisco-de-mostazal.shtml"/>
-    <hyperlink ref="T69" r:id="rId116" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/mas-de-200-millones-para-sanar-deudas-de-achifarp-y-pagos-a-funcionarios-fantasma-los-hitos-que-marcaron-el-primer-dia-de-formalizacion-del-alcalde-de-recoleta/YGFDCRRVJNFSXAA7KWM3YEIIUQ/"/>
-    <hyperlink ref="T70" r:id="rId117" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/29/quien-es-daniel-agusto-perez-el-exalcalde-formalizado-por-fraude-al-fisco/"/>
-    <hyperlink ref="U70" r:id="rId118" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-antofagasta/2024/01/24/son-11-casos-de-karen-rojo-formalizaron-a-exdelegado-de-pinera-en-antofagasta-por-fraude-al-fisco.shtml"/>
-    <hyperlink ref="T71" r:id="rId119" location="" tooltip="" display="https://www.elciudadano.com/politica/los-18-emblematicos-alcaldes-corruptos-de-la-derecha-historias-de-un-tsunami-delictual/06/22/"/>
-    <hyperlink ref="T72" r:id="rId120" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/exalcalde-de-nunoa-andres-zarhi-queda-con-arresto-domiciliario-nocturno-tras-formalizacion-por-fraude-al-fisco/64LJ53FVUJA4BIGCC4DMKIJWRU/"/>
-    <hyperlink ref="U72" r:id="rId121" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/27/1123065/decretan-arresto-domiciliario-nocturno-andreszarhi.html"/>
-    <hyperlink ref="T73" r:id="rId122" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/formalizan-a-exdirector-general-de-la-pdi-hector-espinosa-fiscalia-le-imputa-apropiacion-de-dineros-de-gastos-reservados-de-la-institucion/IBGS7P3IPVGU3MQU4A7GJDH4UA/"/>
-    <hyperlink ref="U73" r:id="rId123" location="" tooltip="" display="https://www.chvnoticias.cl/exclusivo-chv/todas-las-pruebas-fiscalia-hector-espinosa-pdi_20220828/"/>
-    <hyperlink ref="T74" r:id="rId124" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/region-del-maule/contraloria-ordeno-sumarios-contra-municipio-de-linares-rincon-acusa/2022-06-22/174906.html"/>
-    <hyperlink ref="T75" r:id="rId125" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/caso-convenios-ministerio-publico-indaga-traspasos-a-fundaciones-por-mas-de-14-mil-millones-en-ocho-regiones/XUWDKEDIWNDXTOU3RCMSIVQZE4/"/>
-    <hyperlink ref="U75" r:id="rId126" location="" tooltip="" display="https://www.meganoticias.cl/nacional/420687-nexos-politicos-gore-arica-fundacion-comprometidos-280-millones-25-7-2023.html"/>
-    <hyperlink ref="T76" r:id="rId127" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-la-araucania/2024/01/25/caso-cuentas-corrientes-contraloria-ordena-al-municipio-de-lautaro-restituir-cerca-de-80-millones.shtml"/>
-    <hyperlink ref="T77" r:id="rId128" location="" tooltip="" display="https://www.theclinic.cl/2024/02/27/pdi-acorrala-al-circulo-de-virginia-reginato-udi-acusa-a-exadministrador-municipal-de-millonarios-gastos-en-restaurantes-y-licorerias/"/>
-    <hyperlink ref="U77" r:id="rId129" location="" tooltip="" display="https://www.soychile.cl/valparaiso/sociedad/2024/01/22/844669/formalizacion-vina-boisier-fisco-reacciones.html"/>
-    <hyperlink ref="T78" r:id="rId130" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/contraloria-detecta-dos-nuevos-municipios-involucrados-en-el-caso-cuentas-corrientes-y-deriva-antecedentes-a-la-fiscalia/5C3ZRUU3WFF4BFYSN4BG4GD7QE/"/>
-    <hyperlink ref="U78" r:id="rId131" location="" tooltip="" display="https://www.elsancarlino.cl/2024/06/contraloria-detecta-dos-nuevos.html"/>
-    <hyperlink ref="T79" r:id="rId132" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-atacama/2020/08/01/alcalde-suplente-tierra-amarilla-quedo-prision-preventiva-tras-formalizacion-fraudes.shtml"/>
-    <hyperlink ref="T80" r:id="rId133" location="" tooltip="" display="https://www.diarioconstitucional.cl/2023/06/20/ex-administrador-municipal-que-aprobo-el-financiamiento-para-que-alcalde-concejales-y-funcionarios-publicos-de-tierra-amarilla-emprendieran-viaje-turistico-a-la-habana-y-varadero-incurre-en-el-delit/"/>
-    <hyperlink ref="U80" r:id="rId134" location="" tooltip="" display="https://www.cde.cl/cde-valora-condena-a-exadministrador-municipal-de-tierra-amarilla-en-caso-concejales-on-tour/#:~:text=(23.03.2023)"/>
-    <hyperlink ref="T81" r:id="rId135" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2024/02/15/cuentas-corrientes-rio-bueno-debera-restituir-76-millones-por-pagos-improcedentes-a-gestion-global.shtml"/>
-    <hyperlink ref="U81" r:id="rId136" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-rios/2023/09/24/caso-cuentas-corrientes-exalcalde-de-rio-bueno-declara-en-fiscalia-por-contratacion-de-gestion-global.shtml"/>
-    <hyperlink ref="T82" r:id="rId137" location="" tooltip="" display="https://www.canal9.cl/episodios/noticias/2024/07/26/alcalde-de-coronel-y-concejal-araya-seran-formalizados-por-caso-puerto-coronel"/>
-    <hyperlink ref="U82" r:id="rId138" location="" tooltip="" display="https://www.cooperativa.cl/noticias/pais/region-del-biobio/formalizaran-por-delitos-de-corrupcion-al-alcalde-de-coronel-y-a-otras/2024-07-26/084551.html"/>
-    <hyperlink ref="V82" r:id="rId139" location="" tooltip="" display="https://www.meganoticias.cl/nacional/459252-querella-alcalde-coronel-boris-chamorro-cohecho-pago-coimas-17-09-2024.html"/>
-    <hyperlink ref="W82" r:id="rId140" location="" tooltip="" display="https://sabes.cl/2024/09/17/cde-se-suma-al-caso-puerto-coronel-se-querella-contra-alcalde-boris-chamorro-por-delitos-ligados-a-corrupcion/"/>
-    <hyperlink ref="T83" r:id="rId141" location="" tooltip="" display="https://www.latercera.com/politica/noticia/caso-penta-ex-subsecretario-pablo-wagner-condenado-delitos-tributarios-absuelto-cohecho/233126/"/>
-    <hyperlink ref="T84" r:id="rId142" location="" tooltip="" display="https://www.elciudadano.com/politica/los-18-emblematicos-alcaldes-corruptos-de-la-derecha-historias-de-un-tsunami-delictual/06/22/"/>
-    <hyperlink ref="T85" r:id="rId143" location="" tooltip="" display="https://www.latercera.com/nacional/noticia/contraloria-detecta-dos-nuevos-municipios-involucrados-en-el-caso-cuentas-corrientes-y-deriva-antecedentes-a-la-fiscalia/5C3ZRUU3WFF4BFYSN4BG4GD7QE/"/>
-    <hyperlink ref="T86" r:id="rId144" location="" tooltip="" display="https://www.chiletransparente.cl/caso-ceresita/"/>
-    <hyperlink ref="T87" r:id="rId145" location="" tooltip="" display="https://www.diarioviregion.cl/index.php/noticias/27551-ex-alcalde-de-san-fernando-juan-paulo-molina-condenado-por-fraude-al-fisco-reiterado"/>
-    <hyperlink ref="T88" r:id="rId146" location="" tooltip="" display="https://www.biobiochile.cl/noticias/2015/01/24/cinco-casos-de-corrupcion-que-mancharon-la-politica-antes-de-penta-en-los-ultimos-15-anos.shtml"/>
-    <hyperlink ref="U88" r:id="rId147" location="" tooltip="" display="https://es.wikipedia.org/wiki/Caso_Coimas"/>
-    <hyperlink ref="T89" r:id="rId148" location="" tooltip="" display="https://www.latercera.com/reportajes/noticia/la-excesiva-demora-contraloria-salvo-josefa-errazuriz/613135/"/>
-    <hyperlink ref="T91" r:id="rId149" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/region-de-antofagasta/ex-alcaldesa-karen-rojo-condenada-a-cinco-anos-de-carcel-por-fraude-al/2022-03-24/135330.html"/>
-    <hyperlink ref="U91" r:id="rId150" location="" tooltip="" display="https://cooperativa.cl/noticias/pais/region-de-antofagasta/suprema-rechazo-recurso-de-nulidad-y-karen-rojo-debera-cumplir-pena-en/2022-03-23/155942.html"/>
-    <hyperlink ref="V91" r:id="rId151" location="" tooltip="" display="https://chile.as.com/actualidad/detencion-de-karen-rojo-a-que-partido-pertenecia-cuanto-dinero-robo-y-por-que-estaba-en-holanda-n/"/>
-    <hyperlink ref="T92" r:id="rId152" location="" tooltip="" display="https://www.biobiochile.cl/noticias/2015/01/24/cinco-casos-de-corrupcion-que-mancharon-la-politica-antes-de-penta-en-los-ultimos-15-anos.shtml"/>
-    <hyperlink ref="U92" r:id="rId153" location="" tooltip="" display="https://www.emol.com/noticias/nacional/2014/10/23/686503/caso-efe-corte-ratifica-condena-en-contra-de-luis-ajenjo-por-fraude-al-fisco.html"/>
-    <hyperlink ref="T93" r:id="rId154" location="" tooltip="" display="https://www.eldinamo.cl/pais/2013/08/28/sol-letelier-uso-23-millones-de-pesos-de-recoleta-para-su-campana-municipal/"/>
-    <hyperlink ref="T94" r:id="rId155" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-los-lagos/2023/09/13/causa-por-corrupcion-y-lavado-de-activos-fiscal-explica-allanamiento-en-municipio-de-puerto-montt.shtml"/>
-    <hyperlink ref="U94" r:id="rId156" location="" tooltip="" display="https://www.diariodepuertomontt.cl/noticia/politica/2024/08/ter-ordena-la-remocion-del-alcalde-de-puerto-montt"/>
-    <hyperlink ref="V94" r:id="rId157" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/08/23/1140650/remueven-alcalde-de-puerto-montt.html"/>
-    <hyperlink ref="W94" r:id="rId158" location="" tooltip="" display="https://www.24horas.cl/regiones/zona-sur/los-lagos/alcalde-de-puerto-montt-destituido-notable-abandono-deberes"/>
-    <hyperlink ref="T95" r:id="rId159" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2023/11/15/1112897/daniel-jadue-declaracion-farmacias-populares.html"/>
-    <hyperlink ref="U95" r:id="rId160" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/chile/2024/04/02/fiscalia-formalizara-a-daniel-jadue-por-cohecho-administracion-desleal-fraude-al-fisco-y-estafa.shtml"/>
-    <hyperlink ref="T96" r:id="rId161" location="" tooltip="" display="https://www.elciudadano.com/politica/los-18-emblematicos-alcaldes-corruptos-de-la-derecha-historias-de-un-tsunami-delictual/06/22/"/>
-    <hyperlink ref="T98" r:id="rId162" location="" tooltip="" display="https://www.malaespinacheck.cl/pais/2024/01/03/los-14-detenidos-en-todo-chile-por-el-caso-convenios/"/>
-    <hyperlink ref="U98" r:id="rId163" location="" tooltip="" display="https://www.elciudadano.com/actualidad/el-entramado-de-ilicitos-de-platas-que-exploto-en-el-gore-araucania-y-que-repercute-en-renovacion-nacional/12/29/"/>
-    <hyperlink ref="V98" r:id="rId164" location="" tooltip="" display="https://elperiodico.cl/contraloria-corrobora-participacion-de-exfuncionaria-del-gore-araucania-en-comision-que-aprobo-proyecto-de-fundacion-que-posteriormente-la-contrato/"/>
-    <hyperlink ref="T99" r:id="rId165" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/07/10/1136142/suprema-revoca-prision-preventiva.html"/>
-    <hyperlink ref="U99" r:id="rId166" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/06/07/1133101/cronologia-delitos-fiscal-puerto-natales.html"/>
-    <hyperlink ref="T100" r:id="rId167" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/20/1122268/contraloria-caso-convenios-minvu-serviu.html"/>
-    <hyperlink ref="U100" r:id="rId168" location="" tooltip="" display="https://www.ex-ante.cl/confidencial-las-47-fundaciones-indagadas-por-justicia-en-el-caso-convenios/"/>
-    <hyperlink ref="V101" r:id="rId169" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/10/15/cuentas-corrientes-tesorero-municipal-acusado-de-cohecho-logra-salida-alternativa-tras-donar-200-mil.shtml"/>
-    <hyperlink ref="W101" r:id="rId170" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/25/causa-por-corrupcion-mantienen-prision-preventiva-para-alcalde-de-san-ignacio-y-un-operador-politico.shtml"/>
-    <hyperlink ref="U102" r:id="rId171" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/15/1121826/caso-cuentas-corrientes.html"/>
-    <hyperlink ref="T103" r:id="rId172" location="" tooltip="" display="https://www.emol.com/noticias/Nacional/2024/02/15/1121826/caso-cuentas-corrientes.html"/>
-    <hyperlink ref="U103" r:id="rId173" location="" tooltip="" display="https://radio.uchile.cl/2024/02/13/caso-cuentas-corrientes-detienen-a-alcalde-de-bulnes-por-delitos-economicos/"/>
-    <hyperlink ref="T104" r:id="rId174" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/19/ex-udi-y-exasesor-de-sauerbaum-quien-es-el-operador-politico-investigado-por-corrupcion-en-nuble.shtml"/>
-    <hyperlink ref="U104" r:id="rId175" location="" tooltip="" display="https://www.biobiochile.cl/noticias/nacional/region-de-nuble/2023/04/25/causa-por-corrupcion-mantienen-prision-preventiva-para-alcalde-de-san-ignacio-y-un-operador-politico.shtml"/>
+    <hyperlink ref="T3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="T4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="U4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="V4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="T5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="U5" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="V5" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="T6" r:id="rId8" location="Investigaci%C3%B3n_y_sentencias" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="T8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="T9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="T10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="U10" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="T11" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="T12" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="T13" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="T14" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="T15" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="T16" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="U16" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="T17" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="T18" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="U18" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="V18" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="T19" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="U19" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="V19" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="W19" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="T20" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="T21" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="T22" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="U22" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="T23" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="U23" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="T24" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="U24" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="T25" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="U25" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="V25" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="T26" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="U26" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="V26" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="W26" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="U27" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="V27" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="T28" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="U28" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="T29" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="T30" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="U30" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="T31" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="U31" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="V31" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="T32" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="T33" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="T34" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="T35" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="U35" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="T36" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="U36" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="V36" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="T37" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="U37" r:id="rId62" location="El_caso_MOP-GATE" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="T38" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="T39" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="U39" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="T40" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="U40" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="T41" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="T42" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="U42" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="T43" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="T44" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="T46" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="U46" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="V46" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="W46" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="T47" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="U47" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="V47" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="T48" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="U48" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="T49" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="U49" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="T50" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="U50" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="T51" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="U51" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="T52" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="T53" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="U53" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="T54" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="U54" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="V54" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="T55" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="T56" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="U56" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="T57" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="U57" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="V57" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="T58" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="U58" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="T59" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="T60" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="T61" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="T63" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="T64" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="T65" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="U65" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="V65" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="T66" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="T67" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="U67" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="T68" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="U68" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="V68" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="T69" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="T70" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="U70" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="T71" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="T72" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="U72" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="T73" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="U73" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="T74" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="T75" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="U75" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="T76" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="T77" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="U77" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="T78" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="U78" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="T79" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="T80" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="U80" r:id="rId134" location=":~:text=(23.03.2023)" display="https://www.cde.cl/cde-valora-condena-a-exadministrador-municipal-de-tierra-amarilla-en-caso-concejales-on-tour/#:~:text=(23.03.2023)" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="T81" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="U81" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="T82" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="U82" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="V82" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="W82" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="T83" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="T84" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="T85" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="T86" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="T87" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="T88" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="U88" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="T89" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="T91" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="U91" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="V91" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="T92" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="U92" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="T93" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="T94" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="U94" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="V94" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="W94" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="T95" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="U95" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="T96" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="T98" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="U98" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="V98" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="T99" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="U99" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="T100" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="U100" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="V101" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="W101" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="U102" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="T103" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="U103" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="T104" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="U104" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
   </hyperlinks>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
